--- a/template.xlsx
+++ b/template.xlsx
@@ -1,37 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A414A5-1DED-4929-A73E-CA186C708A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E338926-2F79-4FDC-906B-0F38DB9FF4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" xr2:uid="{27465798-F3B3-4AB2-AA5D-2EABD83C4153}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requisições 2026" sheetId="1" r:id="rId1"/>
     <sheet name="DADOS" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="171027"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -42,175 +23,175 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
+    <t xml:space="preserve"> Vermelho (Data Ultrapassada)</t>
+  </si>
+  <si>
+    <t>Laranja (Falta 1 dia)</t>
+  </si>
+  <si>
+    <t>Amarelo (Faltam 3 dias ou menos)</t>
+  </si>
+  <si>
+    <t>Cinzento (Faltam 7 dias ou menos)</t>
+  </si>
+  <si>
+    <t>PEDIDO</t>
+  </si>
+  <si>
+    <t>TÉCNICO*</t>
+  </si>
+  <si>
+    <t>PEDIDO*</t>
+  </si>
+  <si>
+    <t>REQUERENTE*</t>
+  </si>
+  <si>
+    <t>EMPRESA*</t>
+  </si>
+  <si>
+    <t>URGÊNCIA</t>
+  </si>
+  <si>
+    <t>VIA*</t>
+  </si>
+  <si>
+    <t>LOCAL/OBRA*</t>
+  </si>
+  <si>
+    <t>CONCELHO*</t>
+  </si>
+  <si>
+    <t>SERVIÇO*</t>
+  </si>
+  <si>
+    <t>OBSERVAÇAO</t>
+  </si>
+  <si>
+    <t>TIPO DE TRABALHO*</t>
+  </si>
+  <si>
+    <t>FREQUÊNCIA*</t>
+  </si>
+  <si>
+    <t>TEMPO DEDICADO AO TRABALHO (S/Deslocação)</t>
+  </si>
+  <si>
+    <t>LIMITE*</t>
+  </si>
+  <si>
     <t>DATA</t>
   </si>
   <si>
     <t>HORA</t>
   </si>
   <si>
+    <t>CCR ENG&amp;CONST</t>
+  </si>
+  <si>
+    <t>Chamada</t>
+  </si>
+  <si>
+    <t>Póvoa de Varzim</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Lev. Topográfico</t>
+  </si>
+  <si>
+    <t>Diária</t>
+  </si>
+  <si>
+    <t>WEST-VIEW</t>
+  </si>
+  <si>
+    <t>DECIBOLT</t>
+  </si>
+  <si>
+    <t>Vila do Conde</t>
+  </si>
+  <si>
+    <t>Gabinete / Estudos</t>
+  </si>
+  <si>
+    <t>CCR-INVEST</t>
+  </si>
+  <si>
+    <t>GROWNOR</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Maia</t>
+  </si>
+  <si>
     <t>VIA</t>
   </si>
   <si>
-    <t>PEDIDO</t>
-  </si>
-  <si>
-    <t>Chamada</t>
+    <t>CONCELHO</t>
+  </si>
+  <si>
+    <t>FREQUÊNCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE TRABALHO</t>
+  </si>
+  <si>
+    <t>EMPRESA</t>
   </si>
   <si>
     <t>SMS</t>
   </si>
   <si>
+    <t>Guimarães</t>
+  </si>
+  <si>
+    <t>Semanal</t>
+  </si>
+  <si>
+    <t>Monitorização</t>
+  </si>
+  <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>EMPRESA</t>
-  </si>
-  <si>
-    <t>Póvoa de Varzim</t>
-  </si>
-  <si>
-    <t>CONCELHO</t>
-  </si>
-  <si>
-    <t>Guimarães</t>
-  </si>
-  <si>
-    <t>Vila do Conde</t>
+    <t>Mensal</t>
   </si>
   <si>
     <t>Famalicão</t>
   </si>
   <si>
-    <t>FREQUÊNCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE TRABALHO</t>
-  </si>
-  <si>
-    <t>Lev. Topográfico</t>
-  </si>
-  <si>
-    <t>Monitorização</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>Gabinete / Estudos</t>
-  </si>
-  <si>
-    <t>Diária</t>
-  </si>
-  <si>
-    <t>Semanal</t>
-  </si>
-  <si>
-    <t>Mensal</t>
-  </si>
-  <si>
     <t>Trimestral</t>
   </si>
   <si>
+    <t>Whatsapp</t>
+  </si>
+  <si>
     <t>Semestral</t>
   </si>
   <si>
+    <t>GRAU-ON</t>
+  </si>
+  <si>
     <t>Anual</t>
   </si>
   <si>
+    <t>FERCAYO</t>
+  </si>
+  <si>
     <t>Continua</t>
   </si>
   <si>
-    <t>OBSERVAÇAO</t>
-  </si>
-  <si>
-    <t>Whatsapp</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Vermelho (Data Ultrapassada)</t>
-  </si>
-  <si>
-    <t>Laranja (Falta 1 dia)</t>
-  </si>
-  <si>
-    <t>Amarelo (Faltam 3 dias ou menos)</t>
-  </si>
-  <si>
-    <t>Cinzento (Faltam 7 dias ou menos)</t>
-  </si>
-  <si>
-    <t>TEMPO DEDICADO AO TRABALHO (S/Deslocação)</t>
-  </si>
-  <si>
-    <t>Maia</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>CCR ENG&amp;CONST</t>
-  </si>
-  <si>
-    <t>CCR-INVEST</t>
-  </si>
-  <si>
-    <t>GROWNOR</t>
-  </si>
-  <si>
-    <t>WEST-VIEW</t>
-  </si>
-  <si>
-    <t>GRAU-ON</t>
-  </si>
-  <si>
-    <t>FERCAYO</t>
-  </si>
-  <si>
-    <t>DECIBOLT</t>
-  </si>
-  <si>
     <t>INTERNO</t>
   </si>
   <si>
     <t>EXTERNO</t>
-  </si>
-  <si>
-    <t>TÉCNICO*</t>
-  </si>
-  <si>
-    <t>REQUERENTE*</t>
-  </si>
-  <si>
-    <t>EMPRESA*</t>
-  </si>
-  <si>
-    <t>VIA*</t>
-  </si>
-  <si>
-    <t>LOCAL/OBRA*</t>
-  </si>
-  <si>
-    <t>CONCELHO*</t>
-  </si>
-  <si>
-    <t>SERVIÇO*</t>
-  </si>
-  <si>
-    <t>TIPO DE TRABALHO*</t>
-  </si>
-  <si>
-    <t>FREQUÊNCIA*</t>
-  </si>
-  <si>
-    <t>LIMITE*</t>
-  </si>
-  <si>
-    <t>PEDIDO*</t>
-  </si>
-  <si>
-    <t>URGÊNCIA</t>
   </si>
 </sst>
 </file>
@@ -218,8 +199,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="165" formatCode="h:mm;@"/>
+    <numFmt numFmtId="164" formatCode="h:mm;@"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -259,7 +240,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -271,19 +258,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,6 +284,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -317,26 +313,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -347,17 +328,23 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -370,53 +357,35 @@
     <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="16">
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-9.9948118533890809E-2"/>
@@ -424,9 +393,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -434,9 +400,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor theme="5"/>
@@ -444,9 +407,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -454,14 +414,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-9.9948118533890809E-2"/>
@@ -469,9 +421,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -479,9 +428,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor theme="5"/>
@@ -489,9 +435,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -499,17 +442,63 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFF6600"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -817,150 +806,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9055C346-980C-4877-877D-9922F78D6991}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T250"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="16.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" style="1" customWidth="1"/>
     <col min="7" max="8" width="20.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.33203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="32.21875" style="1" customWidth="1"/>
     <col min="11" max="11" width="30.44140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="46" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="45.33203125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="28.109375" style="5" customWidth="1"/>
-    <col min="16" max="16" width="45.33203125" style="5" customWidth="1"/>
-    <col min="17" max="17" width="12.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.109375" style="3"/>
-    <col min="20" max="20" width="28.44140625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="46" style="1" customWidth="1"/>
+    <col min="13" max="14" width="45.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="28.109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="45.33203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.109375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.109375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9.109375" style="4" customWidth="1"/>
+    <col min="20" max="20" width="28.44140625" style="4" customWidth="1"/>
     <col min="21" max="21" width="100" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.109375" style="1"/>
+    <col min="22" max="22" width="9.109375" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="25"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="19"/>
+      <c r="K1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="20"/>
       <c r="T1" s="1"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
       <c r="T2" s="1"/>
     </row>
     <row r="3" spans="1:20" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="O3" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="R3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="21"/>
+      <c r="F3" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="21"/>
       <c r="T3" s="1"/>
     </row>
     <row r="4" spans="1:20" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="27"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="R4" s="16" t="s">
-        <v>1</v>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="T4" s="1"/>
     </row>
@@ -968,134 +952,107 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="E5" s="19"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="R5" s="19"/>
-      <c r="S5"/>
+      <c r="E5" s="8"/>
+      <c r="R5" s="8"/>
       <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6"/>
       <c r="T6" s="1"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
-      <c r="N7"/>
-      <c r="O7"/>
-      <c r="P7"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="18"/>
-      <c r="S7"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="10"/>
       <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="C8"/>
       <c r="T8" s="1"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C9"/>
       <c r="T9" s="1"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="C10"/>
       <c r="T10" s="1"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="C11"/>
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>8</v>
       </c>
-      <c r="C12"/>
       <c r="T12" s="1"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>9</v>
       </c>
-      <c r="C13"/>
       <c r="T13" s="1"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>10</v>
       </c>
-      <c r="C14"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="11"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="11"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>13</v>
       </c>
       <c r="T17" s="1"/>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>14</v>
       </c>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>15</v>
       </c>
       <c r="T19" s="1"/>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>16</v>
       </c>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>17</v>
       </c>
@@ -1118,59 +1075,59 @@
       <c r="S21" s="12"/>
       <c r="T21" s="1"/>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>18</v>
       </c>
       <c r="T22" s="1"/>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>19</v>
       </c>
       <c r="T23" s="1"/>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>28</v>
       </c>
@@ -2267,240 +2224,208 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="D3:E3"/>
     <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="K1:L2"/>
-    <mergeCell ref="I1:J2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:S250">
-    <cfRule type="expression" dxfId="9" priority="6" stopIfTrue="1">
+    <cfRule type="expression" priority="6" stopIfTrue="1">
       <formula>$Q5=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="15" priority="7">
       <formula>$Q5&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="14" priority="8">
       <formula>$Q5-TODAY()=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="13" priority="9">
       <formula>AND($Q5-TODAY()&gt;=0, $Q5-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="12" priority="10">
       <formula>AND($Q5-TODAY()&gt;=4, $Q5-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:H43">
-    <cfRule type="expression" dxfId="4" priority="16" stopIfTrue="1">
+    <cfRule type="expression" priority="16">
       <formula>$Q44=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="17">
+    <cfRule type="expression" dxfId="11" priority="17">
       <formula>$Q44&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18">
+    <cfRule type="expression" dxfId="10" priority="18">
       <formula>$Q44-TODAY()=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="19">
+    <cfRule type="expression" dxfId="9" priority="19">
       <formula>AND($Q44-TODAY()&gt;=0, $Q44-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="8" priority="20">
       <formula>AND($Q44-TODAY()&gt;=4, $Q44-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{24C15DCE-C92D-4202-ACD8-58C0287BC32E}">
-          <x14:formula1>
-            <xm:f>DADOS!$D$5:$D$23</xm:f>
-          </x14:formula1>
-          <xm:sqref>K21:K23 K5:K19</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A8BA25-7F51-4A4E-8C1E-CC5BB724F179}">
-          <x14:formula1>
-            <xm:f>DADOS!$H$5:$H$12</xm:f>
-          </x14:formula1>
-          <xm:sqref>N5:N19</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{0AA13D94-49AF-474D-9571-914120449489}">
-          <x14:formula1>
-            <xm:f>DADOS!$F$5:$F$12</xm:f>
-          </x14:formula1>
-          <xm:sqref>O21:O100 O5:O19</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1C60BA97-0F1A-43D1-A48F-BAAD3868EDA8}">
-          <x14:formula1>
-            <xm:f>DADOS!$J$5:$J$14</xm:f>
-          </x14:formula1>
-          <xm:sqref>G21:H100 G5:H19</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2153A2B5-7B2C-46A2-A191-41067C3B4C5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:J13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
     <col min="10" max="12" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>8</v>
+    <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
-        <v>4</v>
+      <c r="B5" t="s">
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>5</v>
+      <c r="B6" t="s">
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="9" t="s">
-        <v>6</v>
+      <c r="B7" t="s">
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="9" t="s">
-        <v>7</v>
+      <c r="B8" t="s">
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="s">
         <v>28</v>
       </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="10"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="9"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J13" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E338926-2F79-4FDC-906B-0F38DB9FF4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4845BD42-F568-4E4E-A2DF-89D47089ED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,100 +92,100 @@
     <t>Chamada</t>
   </si>
   <si>
+    <t>Vila do Conde</t>
+  </si>
+  <si>
+    <t>Gabinete / Estudos</t>
+  </si>
+  <si>
+    <t>Diária</t>
+  </si>
+  <si>
+    <t>GRAU-ON</t>
+  </si>
+  <si>
+    <t>Lev. Topográfico</t>
+  </si>
+  <si>
+    <t>CCR-INVEST</t>
+  </si>
+  <si>
     <t>Póvoa de Varzim</t>
   </si>
   <si>
+    <t>GROWNOR</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Maia</t>
+  </si>
+  <si>
+    <t>Guimarães</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>VIA</t>
+  </si>
+  <si>
+    <t>CONCELHO</t>
+  </si>
+  <si>
+    <t>FREQUÊNCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE TRABALHO</t>
+  </si>
+  <si>
+    <t>EMPRESA</t>
+  </si>
+  <si>
+    <t>SMS</t>
+  </si>
+  <si>
+    <t>Semanal</t>
+  </si>
+  <si>
+    <t>Monitorização</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Mensal</t>
+  </si>
+  <si>
+    <t>Trimestral</t>
+  </si>
+  <si>
+    <t>WEST-VIEW</t>
+  </si>
+  <si>
+    <t>Whatsapp</t>
+  </si>
+  <si>
+    <t>Semestral</t>
+  </si>
+  <si>
     <t>Porto</t>
   </si>
   <si>
-    <t>Lev. Topográfico</t>
-  </si>
-  <si>
-    <t>Diária</t>
-  </si>
-  <si>
-    <t>WEST-VIEW</t>
+    <t>Anual</t>
+  </si>
+  <si>
+    <t>FERCAYO</t>
+  </si>
+  <si>
+    <t>Continua</t>
   </si>
   <si>
     <t>DECIBOLT</t>
-  </si>
-  <si>
-    <t>Vila do Conde</t>
-  </si>
-  <si>
-    <t>Gabinete / Estudos</t>
-  </si>
-  <si>
-    <t>CCR-INVEST</t>
-  </si>
-  <si>
-    <t>GROWNOR</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Maia</t>
-  </si>
-  <si>
-    <t>VIA</t>
-  </si>
-  <si>
-    <t>CONCELHO</t>
-  </si>
-  <si>
-    <t>FREQUÊNCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE TRABALHO</t>
-  </si>
-  <si>
-    <t>EMPRESA</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>Guimarães</t>
-  </si>
-  <si>
-    <t>Semanal</t>
-  </si>
-  <si>
-    <t>Monitorização</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Mensal</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Trimestral</t>
-  </si>
-  <si>
-    <t>Whatsapp</t>
-  </si>
-  <si>
-    <t>Semestral</t>
-  </si>
-  <si>
-    <t>GRAU-ON</t>
-  </si>
-  <si>
-    <t>Anual</t>
-  </si>
-  <si>
-    <t>FERCAYO</t>
-  </si>
-  <si>
-    <t>Continua</t>
   </si>
   <si>
     <t>INTERNO</t>
@@ -317,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -338,6 +338,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -388,6 +391,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="2" tint="-9.9948118533890809E-2"/>
         </patternFill>
       </fill>
@@ -424,13 +434,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -833,113 +836,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="18" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20" t="s">
+      <c r="J1" s="20"/>
+      <c r="K1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="20"/>
+      <c r="L1" s="21"/>
       <c r="T1" s="1"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
       <c r="T2" s="1"/>
     </row>
     <row r="3" spans="1:20" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="22" t="s">
+      <c r="E3" s="22"/>
+      <c r="F3" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="23" t="s">
+      <c r="P3" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="Q3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="21"/>
+      <c r="R3" s="22"/>
       <c r="T3" s="1"/>
     </row>
     <row r="4" spans="1:20" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="24"/>
       <c r="Q4" s="6" t="s">
         <v>19</v>
       </c>
@@ -952,86 +955,110 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="R5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="9"/>
       <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>2</v>
       </c>
+      <c r="D6" s="8"/>
+      <c r="Q6" s="8"/>
       <c r="T6" s="1"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="11"/>
       <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>4</v>
       </c>
+      <c r="D8" s="8"/>
+      <c r="Q8" s="8"/>
       <c r="T8" s="1"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>5</v>
       </c>
+      <c r="D9" s="8"/>
+      <c r="Q9" s="8"/>
       <c r="T9" s="1"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>6</v>
       </c>
+      <c r="D10" s="8"/>
+      <c r="Q10" s="8"/>
       <c r="T10" s="1"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>7</v>
       </c>
+      <c r="D11" s="8"/>
+      <c r="Q11" s="8"/>
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>8</v>
       </c>
+      <c r="D12" s="8"/>
+      <c r="Q12" s="8"/>
       <c r="T12" s="1"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>9</v>
       </c>
+      <c r="D13" s="8"/>
+      <c r="Q13" s="8"/>
       <c r="T13" s="1"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>10</v>
       </c>
+      <c r="D14" s="8"/>
+      <c r="Q14" s="8"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="8"/>
+      <c r="Q15" s="8"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="8"/>
+      <c r="Q16" s="8"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>13</v>
       </c>
+      <c r="D17" s="8"/>
+      <c r="Q17" s="8"/>
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
@@ -1056,23 +1083,23 @@
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="12"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="13"/>
       <c r="T21" s="1"/>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
@@ -2248,16 +2275,16 @@
     <cfRule type="expression" priority="6" stopIfTrue="1">
       <formula>$Q5=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>$Q5&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="8">
-      <formula>$Q5-TODAY()=1</formula>
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>OR($Q5-TODAY()=0, $Q5-TODAY()=1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="9">
+    <cfRule type="expression" dxfId="6" priority="9">
       <formula>AND($Q5-TODAY()&gt;=0, $Q5-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="10">
+    <cfRule type="expression" dxfId="5" priority="10">
       <formula>AND($Q5-TODAY()&gt;=4, $Q5-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2265,16 +2292,16 @@
     <cfRule type="expression" priority="16">
       <formula>$Q44=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="17">
+    <cfRule type="expression" dxfId="4" priority="17">
       <formula>$Q44&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="18">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>$Q44-TODAY()=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="19">
+    <cfRule type="expression" dxfId="2" priority="19">
       <formula>AND($Q44-TODAY()&gt;=0, $Q44-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="20">
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>AND($Q44-TODAY()&gt;=4, $Q44-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2297,19 +2324,19 @@
   <sheetData>
     <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="17" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2318,13 +2345,13 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
         <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
       </c>
       <c r="J5" t="s">
         <v>21</v>
@@ -2335,83 +2362,83 @@
         <v>41</v>
       </c>
       <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
         <v>42</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>43</v>
       </c>
-      <c r="H6" t="s">
-        <v>44</v>
-      </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" t="s">
         <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
         <v>47</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
         <v>49</v>
       </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
         <v>52</v>
-      </c>
-      <c r="J10" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" t="s">
         <v>54</v>
-      </c>
-      <c r="J11" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4845BD42-F568-4E4E-A2DF-89D47089ED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0022C3-6551-4789-8132-948D8D70A619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t xml:space="preserve"> Vermelho (Data Ultrapassada)</t>
   </si>
@@ -74,9 +74,6 @@
     <t>FREQUÊNCIA*</t>
   </si>
   <si>
-    <t>TEMPO DEDICADO AO TRABALHO (S/Deslocação)</t>
-  </si>
-  <si>
     <t>LIMITE*</t>
   </si>
   <si>
@@ -192,6 +189,12 @@
   </si>
   <si>
     <t>EXTERNO</t>
+  </si>
+  <si>
+    <t>ESTADO</t>
+  </si>
+  <si>
+    <t>CONCLUSÃO</t>
   </si>
 </sst>
 </file>
@@ -202,7 +205,7 @@
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,7 +278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -313,11 +316,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -346,8 +375,6 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -362,6 +389,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -375,26 +408,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill>
@@ -413,27 +442,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -811,7 +819,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T250"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
@@ -825,17 +833,17 @@
     <col min="12" max="12" width="46" style="1" customWidth="1"/>
     <col min="13" max="14" width="45.33203125" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="45.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20.77734375" style="1" customWidth="1"/>
     <col min="17" max="17" width="12.109375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="9.109375" style="4" customWidth="1"/>
-    <col min="20" max="20" width="28.44140625" style="4" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.21875" style="4" customWidth="1"/>
+    <col min="20" max="20" width="16.88671875" style="4" customWidth="1"/>
     <col min="21" max="21" width="100" style="1" customWidth="1"/>
     <col min="22" max="22" width="9.109375" style="1" customWidth="1"/>
     <col min="23" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="14.4" customHeight="1">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -858,7 +866,7 @@
       <c r="L1" s="21"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="14.4" customHeight="1">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -873,85 +881,93 @@
       <c r="L2" s="21"/>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="23" t="s">
+    <row r="3" spans="1:20" ht="19.8" customHeight="1">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="22"/>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="23" t="s">
+      <c r="L3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="23" t="s">
+      <c r="N3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="23" t="s">
+      <c r="O3" s="17" t="s">
         <v>16</v>
       </c>
       <c r="P3" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="Q3" s="25"/>
+      <c r="R3" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3" s="22"/>
+    </row>
+    <row r="4" spans="1:20" ht="32.4" customHeight="1">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="22"/>
-      <c r="T3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="6" t="s">
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="R4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="T4" s="1"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="R4" s="7"/>
+      <c r="S4" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="T4" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -961,7 +977,7 @@
       <c r="R5" s="9"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -969,17 +985,17 @@
       <c r="Q6" s="8"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="11"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="9"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -987,7 +1003,7 @@
       <c r="Q8" s="8"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -995,7 +1011,7 @@
       <c r="Q9" s="8"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -1003,7 +1019,7 @@
       <c r="Q10" s="8"/>
       <c r="T10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -1011,7 +1027,7 @@
       <c r="Q11" s="8"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -1019,7 +1035,7 @@
       <c r="Q12" s="8"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -1027,7 +1043,7 @@
       <c r="Q13" s="8"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -1035,25 +1051,25 @@
       <c r="Q14" s="8"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="15" customHeight="1">
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="12"/>
+      <c r="C15" s="10"/>
       <c r="D15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="15" customHeight="1">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="12"/>
+      <c r="C16" s="10"/>
       <c r="D16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -1061,1197 +1077,1667 @@
       <c r="Q17" s="8"/>
       <c r="T17" s="1"/>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20">
       <c r="B18" s="1">
         <v>14</v>
       </c>
+      <c r="D18" s="8"/>
+      <c r="Q18" s="8"/>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20">
       <c r="B19" s="1">
         <v>15</v>
       </c>
+      <c r="D19" s="8"/>
+      <c r="Q19" s="8"/>
       <c r="T19" s="1"/>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20">
       <c r="B20" s="1">
         <v>16</v>
       </c>
+      <c r="D20" s="8"/>
+      <c r="Q20" s="8"/>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20">
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="13"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="11"/>
       <c r="T21" s="1"/>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20">
       <c r="B22" s="1">
         <v>18</v>
       </c>
+      <c r="D22" s="8"/>
+      <c r="Q22" s="8"/>
       <c r="T22" s="1"/>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20">
       <c r="B23" s="1">
         <v>19</v>
       </c>
+      <c r="D23" s="8"/>
+      <c r="Q23" s="8"/>
       <c r="T23" s="1"/>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20">
       <c r="B24" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D24" s="8"/>
+      <c r="Q24" s="8"/>
+    </row>
+    <row r="25" spans="2:20">
       <c r="B25" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D25" s="8"/>
+      <c r="Q25" s="8"/>
+    </row>
+    <row r="26" spans="2:20">
       <c r="B26" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D26" s="8"/>
+      <c r="Q26" s="8"/>
+    </row>
+    <row r="27" spans="2:20">
       <c r="B27" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D27" s="8"/>
+      <c r="Q27" s="8"/>
+    </row>
+    <row r="28" spans="2:20">
       <c r="B28" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D28" s="8"/>
+      <c r="Q28" s="8"/>
+    </row>
+    <row r="29" spans="2:20">
       <c r="B29" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D29" s="8"/>
+      <c r="Q29" s="8"/>
+    </row>
+    <row r="30" spans="2:20">
       <c r="B30" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D30" s="8"/>
+      <c r="Q30" s="8"/>
+    </row>
+    <row r="31" spans="2:20">
       <c r="B31" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D31" s="8"/>
+      <c r="Q31" s="8"/>
+    </row>
+    <row r="32" spans="2:20">
       <c r="B32" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D32" s="8"/>
+      <c r="Q32" s="8"/>
+    </row>
+    <row r="33" spans="2:17">
       <c r="B33" s="1">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D33" s="8"/>
+      <c r="Q33" s="8"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D34" s="8"/>
+      <c r="Q34" s="8"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="1">
         <v>31</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D35" s="8"/>
+      <c r="Q35" s="8"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="1">
         <v>32</v>
       </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D36" s="8"/>
+      <c r="Q36" s="8"/>
+    </row>
+    <row r="37" spans="2:17">
       <c r="B37" s="1">
         <v>33</v>
       </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D37" s="8"/>
+      <c r="Q37" s="8"/>
+    </row>
+    <row r="38" spans="2:17">
       <c r="B38" s="1">
         <v>34</v>
       </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D38" s="8"/>
+      <c r="Q38" s="8"/>
+    </row>
+    <row r="39" spans="2:17">
       <c r="B39" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D39" s="8"/>
+      <c r="Q39" s="8"/>
+    </row>
+    <row r="40" spans="2:17">
       <c r="B40" s="1">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D40" s="8"/>
+      <c r="Q40" s="8"/>
+    </row>
+    <row r="41" spans="2:17">
       <c r="B41" s="1">
         <v>37</v>
       </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D41" s="8"/>
+      <c r="Q41" s="8"/>
+    </row>
+    <row r="42" spans="2:17">
       <c r="B42" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D42" s="8"/>
+      <c r="Q42" s="8"/>
+    </row>
+    <row r="43" spans="2:17">
       <c r="B43" s="1">
         <v>39</v>
       </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D43" s="8"/>
+      <c r="Q43" s="8"/>
+    </row>
+    <row r="44" spans="2:17">
       <c r="B44" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D44" s="8"/>
+      <c r="Q44" s="8"/>
+    </row>
+    <row r="45" spans="2:17">
       <c r="B45" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D45" s="8"/>
+      <c r="Q45" s="8"/>
+    </row>
+    <row r="46" spans="2:17">
       <c r="B46" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D46" s="8"/>
+      <c r="Q46" s="8"/>
+    </row>
+    <row r="47" spans="2:17">
       <c r="B47" s="1">
         <v>43</v>
       </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D47" s="8"/>
+      <c r="Q47" s="8"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="1">
         <v>44</v>
       </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D48" s="8"/>
+      <c r="Q48" s="8"/>
+    </row>
+    <row r="49" spans="2:17">
       <c r="B49" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D49" s="8"/>
+      <c r="Q49" s="8"/>
+    </row>
+    <row r="50" spans="2:17">
       <c r="B50" s="1">
         <v>46</v>
       </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D50" s="8"/>
+      <c r="Q50" s="8"/>
+    </row>
+    <row r="51" spans="2:17">
       <c r="B51" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D51" s="8"/>
+      <c r="Q51" s="8"/>
+    </row>
+    <row r="52" spans="2:17">
       <c r="B52" s="1">
         <v>48</v>
       </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D52" s="8"/>
+      <c r="Q52" s="8"/>
+    </row>
+    <row r="53" spans="2:17">
       <c r="B53" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D53" s="8"/>
+      <c r="Q53" s="8"/>
+    </row>
+    <row r="54" spans="2:17">
       <c r="B54" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D54" s="8"/>
+      <c r="Q54" s="8"/>
+    </row>
+    <row r="55" spans="2:17">
       <c r="B55" s="1">
         <v>51</v>
       </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D55" s="8"/>
+      <c r="Q55" s="8"/>
+    </row>
+    <row r="56" spans="2:17">
       <c r="B56" s="1">
         <v>52</v>
       </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D56" s="8"/>
+      <c r="Q56" s="8"/>
+    </row>
+    <row r="57" spans="2:17">
       <c r="B57" s="1">
         <v>53</v>
       </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D57" s="8"/>
+      <c r="Q57" s="8"/>
+    </row>
+    <row r="58" spans="2:17">
       <c r="B58" s="1">
         <v>54</v>
       </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D58" s="8"/>
+      <c r="Q58" s="8"/>
+    </row>
+    <row r="59" spans="2:17">
       <c r="B59" s="1">
         <v>55</v>
       </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D59" s="8"/>
+      <c r="Q59" s="8"/>
+    </row>
+    <row r="60" spans="2:17">
       <c r="B60" s="1">
         <v>56</v>
       </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D60" s="8"/>
+      <c r="Q60" s="8"/>
+    </row>
+    <row r="61" spans="2:17">
       <c r="B61" s="1">
         <v>57</v>
       </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D61" s="8"/>
+      <c r="Q61" s="8"/>
+    </row>
+    <row r="62" spans="2:17">
       <c r="B62" s="1">
         <v>58</v>
       </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D62" s="8"/>
+      <c r="Q62" s="8"/>
+    </row>
+    <row r="63" spans="2:17">
       <c r="B63" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D63" s="8"/>
+      <c r="Q63" s="8"/>
+    </row>
+    <row r="64" spans="2:17">
       <c r="B64" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D64" s="8"/>
+      <c r="Q64" s="8"/>
+    </row>
+    <row r="65" spans="2:17">
       <c r="B65" s="1">
         <v>61</v>
       </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D65" s="8"/>
+      <c r="Q65" s="8"/>
+    </row>
+    <row r="66" spans="2:17">
       <c r="B66" s="1">
         <v>62</v>
       </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D66" s="8"/>
+      <c r="Q66" s="8"/>
+    </row>
+    <row r="67" spans="2:17">
       <c r="B67" s="1">
         <v>63</v>
       </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D67" s="8"/>
+      <c r="Q67" s="8"/>
+    </row>
+    <row r="68" spans="2:17">
       <c r="B68" s="1">
         <v>64</v>
       </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D68" s="8"/>
+      <c r="Q68" s="8"/>
+    </row>
+    <row r="69" spans="2:17">
       <c r="B69" s="1">
         <v>65</v>
       </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D69" s="8"/>
+      <c r="Q69" s="8"/>
+    </row>
+    <row r="70" spans="2:17">
       <c r="B70" s="1">
         <v>66</v>
       </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D70" s="8"/>
+      <c r="Q70" s="8"/>
+    </row>
+    <row r="71" spans="2:17">
       <c r="B71" s="1">
         <v>67</v>
       </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D71" s="8"/>
+      <c r="Q71" s="8"/>
+    </row>
+    <row r="72" spans="2:17">
       <c r="B72" s="1">
         <v>68</v>
       </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D72" s="8"/>
+      <c r="Q72" s="8"/>
+    </row>
+    <row r="73" spans="2:17">
       <c r="B73" s="1">
         <v>69</v>
       </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D73" s="8"/>
+      <c r="Q73" s="8"/>
+    </row>
+    <row r="74" spans="2:17">
       <c r="B74" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D74" s="8"/>
+      <c r="Q74" s="8"/>
+    </row>
+    <row r="75" spans="2:17">
       <c r="B75" s="1">
         <v>71</v>
       </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D75" s="8"/>
+      <c r="Q75" s="8"/>
+    </row>
+    <row r="76" spans="2:17">
       <c r="B76" s="1">
         <v>72</v>
       </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D76" s="8"/>
+      <c r="Q76" s="8"/>
+    </row>
+    <row r="77" spans="2:17">
       <c r="B77" s="1">
         <v>73</v>
       </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D77" s="8"/>
+      <c r="Q77" s="8"/>
+    </row>
+    <row r="78" spans="2:17">
       <c r="B78" s="1">
         <v>74</v>
       </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D78" s="8"/>
+      <c r="Q78" s="8"/>
+    </row>
+    <row r="79" spans="2:17">
       <c r="B79" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D79" s="8"/>
+      <c r="Q79" s="8"/>
+    </row>
+    <row r="80" spans="2:17">
       <c r="B80" s="1">
         <v>76</v>
       </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D80" s="8"/>
+      <c r="Q80" s="8"/>
+    </row>
+    <row r="81" spans="2:17">
       <c r="B81" s="1">
         <v>77</v>
       </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D81" s="8"/>
+      <c r="Q81" s="8"/>
+    </row>
+    <row r="82" spans="2:17">
       <c r="B82" s="1">
         <v>78</v>
       </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D82" s="8"/>
+      <c r="Q82" s="8"/>
+    </row>
+    <row r="83" spans="2:17">
       <c r="B83" s="1">
         <v>79</v>
       </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D83" s="8"/>
+      <c r="Q83" s="8"/>
+    </row>
+    <row r="84" spans="2:17">
       <c r="B84" s="1">
         <v>80</v>
       </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D84" s="8"/>
+      <c r="Q84" s="8"/>
+    </row>
+    <row r="85" spans="2:17">
       <c r="B85" s="1">
         <v>81</v>
       </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D85" s="8"/>
+      <c r="Q85" s="8"/>
+    </row>
+    <row r="86" spans="2:17">
       <c r="B86" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D86" s="8"/>
+      <c r="Q86" s="8"/>
+    </row>
+    <row r="87" spans="2:17">
       <c r="B87" s="1">
         <v>83</v>
       </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D87" s="8"/>
+      <c r="Q87" s="8"/>
+    </row>
+    <row r="88" spans="2:17">
       <c r="B88" s="1">
         <v>84</v>
       </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D88" s="8"/>
+      <c r="Q88" s="8"/>
+    </row>
+    <row r="89" spans="2:17">
       <c r="B89" s="1">
         <v>85</v>
       </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D89" s="8"/>
+      <c r="Q89" s="8"/>
+    </row>
+    <row r="90" spans="2:17">
       <c r="B90" s="1">
         <v>86</v>
       </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D90" s="8"/>
+      <c r="Q90" s="8"/>
+    </row>
+    <row r="91" spans="2:17">
       <c r="B91" s="1">
         <v>87</v>
       </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D91" s="8"/>
+      <c r="Q91" s="8"/>
+    </row>
+    <row r="92" spans="2:17">
       <c r="B92" s="1">
         <v>88</v>
       </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D92" s="8"/>
+      <c r="Q92" s="8"/>
+    </row>
+    <row r="93" spans="2:17">
       <c r="B93" s="1">
         <v>89</v>
       </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D93" s="8"/>
+      <c r="Q93" s="8"/>
+    </row>
+    <row r="94" spans="2:17">
       <c r="B94" s="1">
         <v>90</v>
       </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D94" s="8"/>
+      <c r="Q94" s="8"/>
+    </row>
+    <row r="95" spans="2:17">
       <c r="B95" s="1">
         <v>91</v>
       </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D95" s="8"/>
+      <c r="Q95" s="8"/>
+    </row>
+    <row r="96" spans="2:17">
       <c r="B96" s="1">
         <v>92</v>
       </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D96" s="8"/>
+      <c r="Q96" s="8"/>
+    </row>
+    <row r="97" spans="2:17">
       <c r="B97" s="1">
         <v>93</v>
       </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D97" s="8"/>
+      <c r="Q97" s="8"/>
+    </row>
+    <row r="98" spans="2:17">
       <c r="B98" s="1">
         <v>94</v>
       </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D98" s="8"/>
+      <c r="Q98" s="8"/>
+    </row>
+    <row r="99" spans="2:17">
       <c r="B99" s="1">
         <v>95</v>
       </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D99" s="8"/>
+      <c r="Q99" s="8"/>
+    </row>
+    <row r="100" spans="2:17">
       <c r="B100" s="1">
         <v>96</v>
       </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D100" s="8"/>
+      <c r="Q100" s="8"/>
+    </row>
+    <row r="101" spans="2:17">
       <c r="B101" s="1">
         <v>97</v>
       </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D101" s="8"/>
+      <c r="Q101" s="8"/>
+    </row>
+    <row r="102" spans="2:17">
       <c r="B102" s="1">
         <v>98</v>
       </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D102" s="8"/>
+      <c r="Q102" s="8"/>
+    </row>
+    <row r="103" spans="2:17">
       <c r="B103" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D103" s="8"/>
+      <c r="Q103" s="8"/>
+    </row>
+    <row r="104" spans="2:17">
       <c r="B104" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D104" s="8"/>
+      <c r="Q104" s="8"/>
+    </row>
+    <row r="105" spans="2:17">
       <c r="B105" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D105" s="8"/>
+      <c r="Q105" s="8"/>
+    </row>
+    <row r="106" spans="2:17">
       <c r="B106" s="1">
         <v>102</v>
       </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D106" s="8"/>
+      <c r="Q106" s="8"/>
+    </row>
+    <row r="107" spans="2:17">
       <c r="B107" s="1">
         <v>103</v>
       </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D107" s="8"/>
+      <c r="Q107" s="8"/>
+    </row>
+    <row r="108" spans="2:17">
       <c r="B108" s="1">
         <v>104</v>
       </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D108" s="8"/>
+      <c r="Q108" s="8"/>
+    </row>
+    <row r="109" spans="2:17">
       <c r="B109" s="1">
         <v>105</v>
       </c>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D109" s="8"/>
+      <c r="Q109" s="8"/>
+    </row>
+    <row r="110" spans="2:17">
       <c r="B110" s="1">
         <v>106</v>
       </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D110" s="8"/>
+      <c r="Q110" s="8"/>
+    </row>
+    <row r="111" spans="2:17">
       <c r="B111" s="1">
         <v>107</v>
       </c>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D111" s="8"/>
+      <c r="Q111" s="8"/>
+    </row>
+    <row r="112" spans="2:17">
       <c r="B112" s="1">
         <v>108</v>
       </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D112" s="8"/>
+      <c r="Q112" s="8"/>
+    </row>
+    <row r="113" spans="2:17">
       <c r="B113" s="1">
         <v>109</v>
       </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D113" s="8"/>
+      <c r="Q113" s="8"/>
+    </row>
+    <row r="114" spans="2:17">
       <c r="B114" s="1">
         <v>110</v>
       </c>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D114" s="8"/>
+      <c r="Q114" s="8"/>
+    </row>
+    <row r="115" spans="2:17">
       <c r="B115" s="1">
         <v>111</v>
       </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D115" s="8"/>
+      <c r="Q115" s="8"/>
+    </row>
+    <row r="116" spans="2:17">
       <c r="B116" s="1">
         <v>112</v>
       </c>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D116" s="8"/>
+      <c r="Q116" s="8"/>
+    </row>
+    <row r="117" spans="2:17">
       <c r="B117" s="1">
         <v>113</v>
       </c>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D117" s="8"/>
+      <c r="Q117" s="8"/>
+    </row>
+    <row r="118" spans="2:17">
       <c r="B118" s="1">
         <v>114</v>
       </c>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D118" s="8"/>
+      <c r="Q118" s="8"/>
+    </row>
+    <row r="119" spans="2:17">
       <c r="B119" s="1">
         <v>115</v>
       </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D119" s="8"/>
+      <c r="Q119" s="8"/>
+    </row>
+    <row r="120" spans="2:17">
       <c r="B120" s="1">
         <v>116</v>
       </c>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D120" s="8"/>
+      <c r="Q120" s="8"/>
+    </row>
+    <row r="121" spans="2:17">
       <c r="B121" s="1">
         <v>117</v>
       </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D121" s="8"/>
+      <c r="Q121" s="8"/>
+    </row>
+    <row r="122" spans="2:17">
       <c r="B122" s="1">
         <v>118</v>
       </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D122" s="8"/>
+      <c r="Q122" s="8"/>
+    </row>
+    <row r="123" spans="2:17">
       <c r="B123" s="1">
         <v>119</v>
       </c>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D123" s="8"/>
+      <c r="Q123" s="8"/>
+    </row>
+    <row r="124" spans="2:17">
       <c r="B124" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D124" s="8"/>
+      <c r="Q124" s="8"/>
+    </row>
+    <row r="125" spans="2:17">
       <c r="B125" s="1">
         <v>121</v>
       </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D125" s="8"/>
+      <c r="Q125" s="8"/>
+    </row>
+    <row r="126" spans="2:17">
       <c r="B126" s="1">
         <v>122</v>
       </c>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D126" s="8"/>
+      <c r="Q126" s="8"/>
+    </row>
+    <row r="127" spans="2:17">
       <c r="B127" s="1">
         <v>123</v>
       </c>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D127" s="8"/>
+      <c r="Q127" s="8"/>
+    </row>
+    <row r="128" spans="2:17">
       <c r="B128" s="1">
         <v>124</v>
       </c>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D128" s="8"/>
+      <c r="Q128" s="8"/>
+    </row>
+    <row r="129" spans="2:17">
       <c r="B129" s="1">
         <v>125</v>
       </c>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D129" s="8"/>
+      <c r="Q129" s="8"/>
+    </row>
+    <row r="130" spans="2:17">
       <c r="B130" s="1">
         <v>126</v>
       </c>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D130" s="8"/>
+      <c r="Q130" s="8"/>
+    </row>
+    <row r="131" spans="2:17">
       <c r="B131" s="1">
         <v>127</v>
       </c>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D131" s="8"/>
+      <c r="Q131" s="8"/>
+    </row>
+    <row r="132" spans="2:17">
       <c r="B132" s="1">
         <v>128</v>
       </c>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D132" s="8"/>
+      <c r="Q132" s="8"/>
+    </row>
+    <row r="133" spans="2:17">
       <c r="B133" s="1">
         <v>129</v>
       </c>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D133" s="8"/>
+      <c r="Q133" s="8"/>
+    </row>
+    <row r="134" spans="2:17">
       <c r="B134" s="1">
         <v>130</v>
       </c>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D134" s="8"/>
+      <c r="Q134" s="8"/>
+    </row>
+    <row r="135" spans="2:17">
       <c r="B135" s="1">
         <v>131</v>
       </c>
-    </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D135" s="8"/>
+      <c r="Q135" s="8"/>
+    </row>
+    <row r="136" spans="2:17">
       <c r="B136" s="1">
         <v>132</v>
       </c>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D136" s="8"/>
+      <c r="Q136" s="8"/>
+    </row>
+    <row r="137" spans="2:17">
       <c r="B137" s="1">
         <v>133</v>
       </c>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D137" s="8"/>
+      <c r="Q137" s="8"/>
+    </row>
+    <row r="138" spans="2:17">
       <c r="B138" s="1">
         <v>134</v>
       </c>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D138" s="8"/>
+      <c r="Q138" s="8"/>
+    </row>
+    <row r="139" spans="2:17">
       <c r="B139" s="1">
         <v>135</v>
       </c>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D139" s="8"/>
+      <c r="Q139" s="8"/>
+    </row>
+    <row r="140" spans="2:17">
       <c r="B140" s="1">
         <v>136</v>
       </c>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D140" s="8"/>
+      <c r="Q140" s="8"/>
+    </row>
+    <row r="141" spans="2:17">
       <c r="B141" s="1">
         <v>137</v>
       </c>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D141" s="8"/>
+      <c r="Q141" s="8"/>
+    </row>
+    <row r="142" spans="2:17">
       <c r="B142" s="1">
         <v>138</v>
       </c>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D142" s="8"/>
+      <c r="Q142" s="8"/>
+    </row>
+    <row r="143" spans="2:17">
       <c r="B143" s="1">
         <v>139</v>
       </c>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D143" s="8"/>
+      <c r="Q143" s="8"/>
+    </row>
+    <row r="144" spans="2:17">
       <c r="B144" s="1">
         <v>140</v>
       </c>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D144" s="8"/>
+      <c r="Q144" s="8"/>
+    </row>
+    <row r="145" spans="2:17">
       <c r="B145" s="1">
         <v>141</v>
       </c>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D145" s="8"/>
+      <c r="Q145" s="8"/>
+    </row>
+    <row r="146" spans="2:17">
       <c r="B146" s="1">
         <v>142</v>
       </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D146" s="8"/>
+      <c r="Q146" s="8"/>
+    </row>
+    <row r="147" spans="2:17">
       <c r="B147" s="1">
         <v>143</v>
       </c>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D147" s="8"/>
+      <c r="Q147" s="8"/>
+    </row>
+    <row r="148" spans="2:17">
       <c r="B148" s="1">
         <v>144</v>
       </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D148" s="8"/>
+      <c r="Q148" s="8"/>
+    </row>
+    <row r="149" spans="2:17">
       <c r="B149" s="1">
         <v>145</v>
       </c>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D149" s="8"/>
+      <c r="Q149" s="8"/>
+    </row>
+    <row r="150" spans="2:17">
       <c r="B150" s="1">
         <v>146</v>
       </c>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D150" s="8"/>
+      <c r="Q150" s="8"/>
+    </row>
+    <row r="151" spans="2:17">
       <c r="B151" s="1">
         <v>147</v>
       </c>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D151" s="8"/>
+      <c r="Q151" s="8"/>
+    </row>
+    <row r="152" spans="2:17">
       <c r="B152" s="1">
         <v>148</v>
       </c>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D152" s="8"/>
+      <c r="Q152" s="8"/>
+    </row>
+    <row r="153" spans="2:17">
       <c r="B153" s="1">
         <v>149</v>
       </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D153" s="8"/>
+      <c r="Q153" s="8"/>
+    </row>
+    <row r="154" spans="2:17">
       <c r="B154" s="1">
         <v>150</v>
       </c>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D154" s="8"/>
+      <c r="Q154" s="8"/>
+    </row>
+    <row r="155" spans="2:17">
       <c r="B155" s="1">
         <v>151</v>
       </c>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D155" s="8"/>
+      <c r="Q155" s="8"/>
+    </row>
+    <row r="156" spans="2:17">
       <c r="B156" s="1">
         <v>152</v>
       </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D156" s="8"/>
+      <c r="Q156" s="8"/>
+    </row>
+    <row r="157" spans="2:17">
       <c r="B157" s="1">
         <v>153</v>
       </c>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D157" s="8"/>
+      <c r="Q157" s="8"/>
+    </row>
+    <row r="158" spans="2:17">
       <c r="B158" s="1">
         <v>154</v>
       </c>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D158" s="8"/>
+      <c r="Q158" s="8"/>
+    </row>
+    <row r="159" spans="2:17">
       <c r="B159" s="1">
         <v>155</v>
       </c>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D159" s="8"/>
+      <c r="Q159" s="8"/>
+    </row>
+    <row r="160" spans="2:17">
       <c r="B160" s="1">
         <v>156</v>
       </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D160" s="8"/>
+      <c r="Q160" s="8"/>
+    </row>
+    <row r="161" spans="2:17">
       <c r="B161" s="1">
         <v>157</v>
       </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D161" s="8"/>
+      <c r="Q161" s="8"/>
+    </row>
+    <row r="162" spans="2:17">
       <c r="B162" s="1">
         <v>158</v>
       </c>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D162" s="8"/>
+      <c r="Q162" s="8"/>
+    </row>
+    <row r="163" spans="2:17">
       <c r="B163" s="1">
         <v>159</v>
       </c>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D163" s="8"/>
+      <c r="Q163" s="8"/>
+    </row>
+    <row r="164" spans="2:17">
       <c r="B164" s="1">
         <v>160</v>
       </c>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D164" s="8"/>
+      <c r="Q164" s="8"/>
+    </row>
+    <row r="165" spans="2:17">
       <c r="B165" s="1">
         <v>161</v>
       </c>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D165" s="8"/>
+      <c r="Q165" s="8"/>
+    </row>
+    <row r="166" spans="2:17">
       <c r="B166" s="1">
         <v>162</v>
       </c>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D166" s="8"/>
+      <c r="Q166" s="8"/>
+    </row>
+    <row r="167" spans="2:17">
       <c r="B167" s="1">
         <v>163</v>
       </c>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D167" s="8"/>
+      <c r="Q167" s="8"/>
+    </row>
+    <row r="168" spans="2:17">
       <c r="B168" s="1">
         <v>164</v>
       </c>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D168" s="8"/>
+      <c r="Q168" s="8"/>
+    </row>
+    <row r="169" spans="2:17">
       <c r="B169" s="1">
         <v>165</v>
       </c>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D169" s="8"/>
+      <c r="Q169" s="8"/>
+    </row>
+    <row r="170" spans="2:17">
       <c r="B170" s="1">
         <v>166</v>
       </c>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D170" s="8"/>
+      <c r="Q170" s="8"/>
+    </row>
+    <row r="171" spans="2:17">
       <c r="B171" s="1">
         <v>167</v>
       </c>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D171" s="8"/>
+      <c r="Q171" s="8"/>
+    </row>
+    <row r="172" spans="2:17">
       <c r="B172" s="1">
         <v>168</v>
       </c>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D172" s="8"/>
+      <c r="Q172" s="8"/>
+    </row>
+    <row r="173" spans="2:17">
       <c r="B173" s="1">
         <v>169</v>
       </c>
-    </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D173" s="8"/>
+      <c r="Q173" s="8"/>
+    </row>
+    <row r="174" spans="2:17">
       <c r="B174" s="1">
         <v>170</v>
       </c>
-    </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D174" s="8"/>
+      <c r="Q174" s="8"/>
+    </row>
+    <row r="175" spans="2:17">
       <c r="B175" s="1">
         <v>171</v>
       </c>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D175" s="8"/>
+      <c r="Q175" s="8"/>
+    </row>
+    <row r="176" spans="2:17">
       <c r="B176" s="1">
         <v>172</v>
       </c>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D176" s="8"/>
+      <c r="Q176" s="8"/>
+    </row>
+    <row r="177" spans="2:17">
       <c r="B177" s="1">
         <v>173</v>
       </c>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D177" s="8"/>
+      <c r="Q177" s="8"/>
+    </row>
+    <row r="178" spans="2:17">
       <c r="B178" s="1">
         <v>174</v>
       </c>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D178" s="8"/>
+      <c r="Q178" s="8"/>
+    </row>
+    <row r="179" spans="2:17">
       <c r="B179" s="1">
         <v>175</v>
       </c>
-    </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D179" s="8"/>
+      <c r="Q179" s="8"/>
+    </row>
+    <row r="180" spans="2:17">
       <c r="B180" s="1">
         <v>176</v>
       </c>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D180" s="8"/>
+      <c r="Q180" s="8"/>
+    </row>
+    <row r="181" spans="2:17">
       <c r="B181" s="1">
         <v>177</v>
       </c>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D181" s="8"/>
+      <c r="Q181" s="8"/>
+    </row>
+    <row r="182" spans="2:17">
       <c r="B182" s="1">
         <v>178</v>
       </c>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D182" s="8"/>
+      <c r="Q182" s="8"/>
+    </row>
+    <row r="183" spans="2:17">
       <c r="B183" s="1">
         <v>179</v>
       </c>
-    </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D183" s="8"/>
+      <c r="Q183" s="8"/>
+    </row>
+    <row r="184" spans="2:17">
       <c r="B184" s="1">
         <v>180</v>
       </c>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D184" s="8"/>
+      <c r="Q184" s="8"/>
+    </row>
+    <row r="185" spans="2:17">
       <c r="B185" s="1">
         <v>181</v>
       </c>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D185" s="8"/>
+      <c r="Q185" s="8"/>
+    </row>
+    <row r="186" spans="2:17">
       <c r="B186" s="1">
         <v>182</v>
       </c>
-    </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D186" s="8"/>
+      <c r="Q186" s="8"/>
+    </row>
+    <row r="187" spans="2:17">
       <c r="B187" s="1">
         <v>183</v>
       </c>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D187" s="8"/>
+      <c r="Q187" s="8"/>
+    </row>
+    <row r="188" spans="2:17">
       <c r="B188" s="1">
         <v>184</v>
       </c>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D188" s="8"/>
+      <c r="Q188" s="8"/>
+    </row>
+    <row r="189" spans="2:17">
       <c r="B189" s="1">
         <v>185</v>
       </c>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D189" s="8"/>
+      <c r="Q189" s="8"/>
+    </row>
+    <row r="190" spans="2:17">
       <c r="B190" s="1">
         <v>186</v>
       </c>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D190" s="8"/>
+      <c r="Q190" s="8"/>
+    </row>
+    <row r="191" spans="2:17">
       <c r="B191" s="1">
         <v>187</v>
       </c>
-    </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D191" s="8"/>
+      <c r="Q191" s="8"/>
+    </row>
+    <row r="192" spans="2:17">
       <c r="B192" s="1">
         <v>188</v>
       </c>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D192" s="8"/>
+      <c r="Q192" s="8"/>
+    </row>
+    <row r="193" spans="2:17">
       <c r="B193" s="1">
         <v>189</v>
       </c>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D193" s="8"/>
+      <c r="Q193" s="8"/>
+    </row>
+    <row r="194" spans="2:17">
       <c r="B194" s="1">
         <v>190</v>
       </c>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D194" s="8"/>
+      <c r="Q194" s="8"/>
+    </row>
+    <row r="195" spans="2:17">
       <c r="B195" s="1">
         <v>191</v>
       </c>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D195" s="8"/>
+      <c r="Q195" s="8"/>
+    </row>
+    <row r="196" spans="2:17">
       <c r="B196" s="1">
         <v>192</v>
       </c>
-    </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D196" s="8"/>
+      <c r="Q196" s="8"/>
+    </row>
+    <row r="197" spans="2:17">
       <c r="B197" s="1">
         <v>193</v>
       </c>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D197" s="8"/>
+      <c r="Q197" s="8"/>
+    </row>
+    <row r="198" spans="2:17">
       <c r="B198" s="1">
         <v>194</v>
       </c>
-    </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D198" s="8"/>
+      <c r="Q198" s="8"/>
+    </row>
+    <row r="199" spans="2:17">
       <c r="B199" s="1">
         <v>195</v>
       </c>
-    </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D199" s="8"/>
+      <c r="Q199" s="8"/>
+    </row>
+    <row r="200" spans="2:17">
       <c r="B200" s="1">
         <v>196</v>
       </c>
-    </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D200" s="8"/>
+      <c r="Q200" s="8"/>
+    </row>
+    <row r="201" spans="2:17">
       <c r="B201" s="1">
         <v>197</v>
       </c>
-    </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D201" s="8"/>
+      <c r="Q201" s="8"/>
+    </row>
+    <row r="202" spans="2:17">
       <c r="B202" s="1">
         <v>198</v>
       </c>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D202" s="8"/>
+      <c r="Q202" s="8"/>
+    </row>
+    <row r="203" spans="2:17">
       <c r="B203" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D203" s="8"/>
+      <c r="Q203" s="8"/>
+    </row>
+    <row r="204" spans="2:17">
       <c r="B204" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D204" s="8"/>
+      <c r="Q204" s="8"/>
+    </row>
+    <row r="205" spans="2:17">
       <c r="B205" s="1">
         <v>201</v>
       </c>
-    </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D205" s="8"/>
+      <c r="Q205" s="8"/>
+    </row>
+    <row r="206" spans="2:17">
       <c r="B206" s="1">
         <v>202</v>
       </c>
-    </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D206" s="8"/>
+      <c r="Q206" s="8"/>
+    </row>
+    <row r="207" spans="2:17">
       <c r="B207" s="1">
         <v>203</v>
       </c>
-    </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D207" s="8"/>
+      <c r="Q207" s="8"/>
+    </row>
+    <row r="208" spans="2:17">
       <c r="B208" s="1">
         <v>204</v>
       </c>
-    </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D208" s="8"/>
+      <c r="Q208" s="8"/>
+    </row>
+    <row r="209" spans="2:17">
       <c r="B209" s="1">
         <v>205</v>
       </c>
-    </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D209" s="8"/>
+      <c r="Q209" s="8"/>
+    </row>
+    <row r="210" spans="2:17">
       <c r="B210" s="1">
         <v>206</v>
       </c>
-    </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D210" s="8"/>
+      <c r="Q210" s="8"/>
+    </row>
+    <row r="211" spans="2:17">
       <c r="B211" s="1">
         <v>207</v>
       </c>
-    </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D211" s="8"/>
+      <c r="Q211" s="8"/>
+    </row>
+    <row r="212" spans="2:17">
       <c r="B212" s="1">
         <v>208</v>
       </c>
-    </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D212" s="8"/>
+      <c r="Q212" s="8"/>
+    </row>
+    <row r="213" spans="2:17">
       <c r="B213" s="1">
         <v>209</v>
       </c>
-    </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D213" s="8"/>
+      <c r="Q213" s="8"/>
+    </row>
+    <row r="214" spans="2:17">
       <c r="B214" s="1">
         <v>210</v>
       </c>
-    </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D214" s="8"/>
+      <c r="Q214" s="8"/>
+    </row>
+    <row r="215" spans="2:17">
       <c r="B215" s="1">
         <v>211</v>
       </c>
-    </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D215" s="8"/>
+      <c r="Q215" s="8"/>
+    </row>
+    <row r="216" spans="2:17">
       <c r="B216" s="1">
         <v>212</v>
       </c>
-    </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D216" s="8"/>
+      <c r="Q216" s="8"/>
+    </row>
+    <row r="217" spans="2:17">
       <c r="B217" s="1">
         <v>213</v>
       </c>
-    </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D217" s="8"/>
+      <c r="Q217" s="8"/>
+    </row>
+    <row r="218" spans="2:17">
       <c r="B218" s="1">
         <v>214</v>
       </c>
-    </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D218" s="8"/>
+      <c r="Q218" s="8"/>
+    </row>
+    <row r="219" spans="2:17">
       <c r="B219" s="1">
         <v>215</v>
       </c>
-    </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D219" s="8"/>
+      <c r="Q219" s="8"/>
+    </row>
+    <row r="220" spans="2:17">
       <c r="B220" s="1">
         <v>216</v>
       </c>
-    </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D220" s="8"/>
+      <c r="Q220" s="8"/>
+    </row>
+    <row r="221" spans="2:17">
       <c r="B221" s="1">
         <v>217</v>
       </c>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D221" s="8"/>
+      <c r="Q221" s="8"/>
+    </row>
+    <row r="222" spans="2:17">
       <c r="B222" s="1">
         <v>218</v>
       </c>
-    </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D222" s="8"/>
+      <c r="Q222" s="8"/>
+    </row>
+    <row r="223" spans="2:17">
       <c r="B223" s="1">
         <v>219</v>
       </c>
-    </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D223" s="8"/>
+      <c r="Q223" s="8"/>
+    </row>
+    <row r="224" spans="2:17">
       <c r="B224" s="1">
         <v>220</v>
       </c>
-    </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D224" s="8"/>
+      <c r="Q224" s="8"/>
+    </row>
+    <row r="225" spans="2:17">
       <c r="B225" s="1">
         <v>221</v>
       </c>
-    </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D225" s="8"/>
+      <c r="Q225" s="8"/>
+    </row>
+    <row r="226" spans="2:17">
       <c r="B226" s="1">
         <v>222</v>
       </c>
-    </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D226" s="8"/>
+      <c r="Q226" s="8"/>
+    </row>
+    <row r="227" spans="2:17">
       <c r="B227" s="1">
         <v>223</v>
       </c>
-    </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D227" s="8"/>
+      <c r="Q227" s="8"/>
+    </row>
+    <row r="228" spans="2:17">
       <c r="B228" s="1">
         <v>224</v>
       </c>
-    </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D228" s="8"/>
+      <c r="Q228" s="8"/>
+    </row>
+    <row r="229" spans="2:17">
       <c r="B229" s="1">
         <v>225</v>
       </c>
-    </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D229" s="8"/>
+      <c r="Q229" s="8"/>
+    </row>
+    <row r="230" spans="2:17">
       <c r="B230" s="1">
         <v>226</v>
       </c>
-    </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D230" s="8"/>
+      <c r="Q230" s="8"/>
+    </row>
+    <row r="231" spans="2:17">
       <c r="B231" s="1">
         <v>227</v>
       </c>
-    </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D231" s="8"/>
+      <c r="Q231" s="8"/>
+    </row>
+    <row r="232" spans="2:17">
       <c r="B232" s="1">
         <v>228</v>
       </c>
-    </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D232" s="8"/>
+      <c r="Q232" s="8"/>
+    </row>
+    <row r="233" spans="2:17">
       <c r="B233" s="1">
         <v>229</v>
       </c>
-    </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D233" s="8"/>
+      <c r="Q233" s="8"/>
+    </row>
+    <row r="234" spans="2:17">
       <c r="B234" s="1">
         <v>230</v>
       </c>
-    </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D234" s="8"/>
+      <c r="Q234" s="8"/>
+    </row>
+    <row r="235" spans="2:17">
       <c r="B235" s="1">
         <v>231</v>
       </c>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D235" s="8"/>
+      <c r="Q235" s="8"/>
+    </row>
+    <row r="236" spans="2:17">
       <c r="B236" s="1">
         <v>232</v>
       </c>
-    </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D236" s="8"/>
+      <c r="Q236" s="8"/>
+    </row>
+    <row r="237" spans="2:17">
       <c r="B237" s="1">
         <v>233</v>
       </c>
-    </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D237" s="8"/>
+      <c r="Q237" s="8"/>
+    </row>
+    <row r="238" spans="2:17">
       <c r="B238" s="1">
         <v>234</v>
       </c>
-    </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D238" s="8"/>
+      <c r="Q238" s="8"/>
+    </row>
+    <row r="239" spans="2:17">
       <c r="B239" s="1">
         <v>235</v>
       </c>
-    </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D239" s="8"/>
+      <c r="Q239" s="8"/>
+    </row>
+    <row r="240" spans="2:17">
       <c r="B240" s="1">
         <v>236</v>
       </c>
-    </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D240" s="8"/>
+      <c r="Q240" s="8"/>
+    </row>
+    <row r="241" spans="2:17">
       <c r="B241" s="1">
         <v>237</v>
       </c>
-    </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D241" s="8"/>
+      <c r="Q241" s="8"/>
+    </row>
+    <row r="242" spans="2:17">
       <c r="B242" s="1">
         <v>238</v>
       </c>
-    </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D242" s="8"/>
+      <c r="Q242" s="8"/>
+    </row>
+    <row r="243" spans="2:17">
       <c r="B243" s="1">
         <v>239</v>
       </c>
-    </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D243" s="8"/>
+      <c r="Q243" s="8"/>
+    </row>
+    <row r="244" spans="2:17">
       <c r="B244" s="1">
         <v>240</v>
       </c>
-    </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D244" s="8"/>
+      <c r="Q244" s="8"/>
+    </row>
+    <row r="245" spans="2:17">
       <c r="B245" s="1">
         <v>241</v>
       </c>
-    </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D245" s="8"/>
+      <c r="Q245" s="8"/>
+    </row>
+    <row r="246" spans="2:17">
       <c r="B246" s="1">
         <v>242</v>
       </c>
-    </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D246" s="8"/>
+      <c r="Q246" s="8"/>
+    </row>
+    <row r="247" spans="2:17">
       <c r="B247" s="1">
         <v>243</v>
       </c>
-    </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D247" s="8"/>
+      <c r="Q247" s="8"/>
+    </row>
+    <row r="248" spans="2:17">
       <c r="B248" s="1">
         <v>244</v>
       </c>
-    </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D248" s="8"/>
+      <c r="Q248" s="8"/>
+    </row>
+    <row r="249" spans="2:17">
       <c r="B249" s="1">
         <v>245</v>
       </c>
-    </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="D249" s="8"/>
+      <c r="Q249" s="8"/>
+    </row>
+    <row r="250" spans="2:17">
       <c r="B250" s="1">
         <v>246</v>
       </c>
+      <c r="D250" s="8"/>
+      <c r="Q250" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="D3:E3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="F3:F4"/>
@@ -2264,45 +2750,22 @@
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
-    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:S250">
     <cfRule type="expression" priority="6" stopIfTrue="1">
       <formula>$Q5=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="11" priority="7">
       <formula>$Q5&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="10" priority="8">
       <formula>OR($Q5-TODAY()=0, $Q5-TODAY()=1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>AND($Q5-TODAY()&gt;=0, $Q5-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="8" priority="10">
       <formula>AND($Q5-TODAY()&gt;=4, $Q5-TODAY()&lt;=7)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G43:H43">
-    <cfRule type="expression" priority="16">
-      <formula>$Q44=""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="17">
-      <formula>$Q44&lt;TODAY()</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="18">
-      <formula>$Q44-TODAY()=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="19">
-      <formula>AND($Q44-TODAY()&gt;=0, $Q44-TODAY()&lt;=3)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="20">
-      <formula>AND($Q44-TODAY()&gt;=4, $Q44-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2313,7 +2776,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:J13"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.109375" customWidth="1"/>
     <col min="4" max="4" width="15.88671875" customWidth="1"/>
@@ -2322,133 +2785,133 @@
     <col min="10" max="12" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="16" t="s">
+    <row r="3" spans="2:10" ht="15" customHeight="1"/>
+    <row r="4" spans="2:10" ht="15" customHeight="1">
+      <c r="B4" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="H4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="J4" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="17" t="s">
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" t="s">
         <v>29</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" t="s">
         <v>25</v>
       </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" t="s">
+    </row>
+    <row r="10" spans="2:10">
+      <c r="D10" t="s">
         <v>49</v>
       </c>
-      <c r="J9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>50</v>
       </c>
-      <c r="F10" t="s">
+      <c r="J10" t="s">
         <v>51</v>
       </c>
-      <c r="J10" t="s">
+    </row>
+    <row r="11" spans="2:10">
+      <c r="F11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F11" t="s">
+      <c r="J11" t="s">
         <v>53</v>
       </c>
-      <c r="J11" t="s">
+    </row>
+    <row r="12" spans="2:10">
+      <c r="J12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J12" t="s">
+    <row r="13" spans="2:10">
+      <c r="J13" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J13" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0022C3-6551-4789-8132-948D8D70A619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15D014C-F0C1-4195-8636-6904610B46D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,99 +77,105 @@
     <t>LIMITE*</t>
   </si>
   <si>
+    <t>ESTADO</t>
+  </si>
+  <si>
+    <t>CONCLUSÃO</t>
+  </si>
+  <si>
     <t>DATA</t>
   </si>
   <si>
     <t>HORA</t>
   </si>
   <si>
+    <t>CCR-INVEST</t>
+  </si>
+  <si>
+    <t>Chamada</t>
+  </si>
+  <si>
+    <t>Monitorização</t>
+  </si>
+  <si>
+    <t>Póvoa de Varzim</t>
+  </si>
+  <si>
+    <t>Lev. Topográfico</t>
+  </si>
+  <si>
+    <t>Diária</t>
+  </si>
+  <si>
+    <t>GROWNOR</t>
+  </si>
+  <si>
+    <t>WEST-VIEW</t>
+  </si>
+  <si>
     <t>CCR ENG&amp;CONST</t>
   </si>
   <si>
-    <t>Chamada</t>
+    <t>Guimarães</t>
+  </si>
+  <si>
+    <t>Presencial</t>
   </si>
   <si>
     <t>Vila do Conde</t>
   </si>
   <si>
+    <t>Implantação</t>
+  </si>
+  <si>
     <t>Gabinete / Estudos</t>
   </si>
   <si>
-    <t>Diária</t>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Maia</t>
+  </si>
+  <si>
+    <t>VIA</t>
+  </si>
+  <si>
+    <t>CONCELHO</t>
+  </si>
+  <si>
+    <t>FREQUÊNCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE TRABALHO</t>
+  </si>
+  <si>
+    <t>EMPRESA</t>
+  </si>
+  <si>
+    <t>SMS</t>
+  </si>
+  <si>
+    <t>Semanal</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Mensal</t>
+  </si>
+  <si>
+    <t>Trimestral</t>
+  </si>
+  <si>
+    <t>Whatsapp</t>
+  </si>
+  <si>
+    <t>Semestral</t>
   </si>
   <si>
     <t>GRAU-ON</t>
   </si>
   <si>
-    <t>Lev. Topográfico</t>
-  </si>
-  <si>
-    <t>CCR-INVEST</t>
-  </si>
-  <si>
-    <t>Póvoa de Varzim</t>
-  </si>
-  <si>
-    <t>GROWNOR</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Maia</t>
-  </si>
-  <si>
-    <t>Guimarães</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>VIA</t>
-  </si>
-  <si>
-    <t>CONCELHO</t>
-  </si>
-  <si>
-    <t>FREQUÊNCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE TRABALHO</t>
-  </si>
-  <si>
-    <t>EMPRESA</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>Semanal</t>
-  </si>
-  <si>
-    <t>Monitorização</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Mensal</t>
-  </si>
-  <si>
-    <t>Trimestral</t>
-  </si>
-  <si>
-    <t>WEST-VIEW</t>
-  </si>
-  <si>
-    <t>Whatsapp</t>
-  </si>
-  <si>
-    <t>Semestral</t>
-  </si>
-  <si>
     <t>Porto</t>
   </si>
   <si>
@@ -189,12 +195,6 @@
   </si>
   <si>
     <t>EXTERNO</t>
-  </si>
-  <si>
-    <t>ESTADO</t>
-  </si>
-  <si>
-    <t>CONCLUSÃO</t>
   </si>
 </sst>
 </file>
@@ -302,21 +302,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -342,11 +327,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -358,15 +358,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -387,36 +378,39 @@
     <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -834,9 +828,9 @@
     <col min="13" max="14" width="45.33203125" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.109375" style="1" customWidth="1"/>
     <col min="16" max="16" width="20.77734375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.109375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.21875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="12.109375" style="4" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" style="3" customWidth="1"/>
+    <col min="19" max="19" width="12.21875" style="5" customWidth="1"/>
     <col min="20" max="20" width="16.88671875" style="4" customWidth="1"/>
     <col min="21" max="21" width="100" style="1" customWidth="1"/>
     <col min="22" max="22" width="9.109375" style="1" customWidth="1"/>
@@ -844,1900 +838,1674 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="19" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="20" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21" t="s">
+      <c r="J1" s="17"/>
+      <c r="K1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="21"/>
-      <c r="T1" s="1"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="T2" s="1"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
     </row>
     <row r="3" spans="1:20" ht="19.8" customHeight="1">
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="20"/>
+      <c r="F3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="24" t="s">
+      <c r="P3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="S3" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="T3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" s="20"/>
     </row>
     <row r="4" spans="1:20" ht="32.4" customHeight="1">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" s="7"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" s="23"/>
       <c r="S4" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="T4" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="T4" s="23" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="9"/>
-      <c r="T5" s="1"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="P5" s="5"/>
+      <c r="R5" s="6"/>
     </row>
     <row r="6" spans="1:20">
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="T6" s="1"/>
+      <c r="D6" s="5"/>
+      <c r="P6" s="5"/>
     </row>
     <row r="7" spans="1:20">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="9"/>
-      <c r="T7" s="1"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="P7" s="5"/>
+      <c r="R7" s="6"/>
     </row>
     <row r="8" spans="1:20">
       <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="T8" s="1"/>
+      <c r="D8" s="5"/>
+      <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:20">
       <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="T9" s="1"/>
+      <c r="D9" s="5"/>
+      <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:20">
       <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="T10" s="1"/>
+      <c r="D10" s="5"/>
+      <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:20">
       <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="T11" s="1"/>
+      <c r="D11" s="5"/>
+      <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:20">
       <c r="B12" s="1">
         <v>8</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="T12" s="1"/>
+      <c r="D12" s="5"/>
+      <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:20">
       <c r="B13" s="1">
         <v>9</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="T13" s="1"/>
+      <c r="D13" s="5"/>
+      <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:20">
       <c r="B14" s="1">
         <v>10</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="T14" s="1"/>
+      <c r="D14" s="5"/>
+      <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1">
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="T15" s="1"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="5"/>
+      <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="T16" s="1"/>
-    </row>
-    <row r="17" spans="2:20">
+      <c r="C16" s="7"/>
+      <c r="D16" s="5"/>
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" spans="2:19">
       <c r="B17" s="1">
         <v>13</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="T17" s="1"/>
-    </row>
-    <row r="18" spans="2:20">
+      <c r="D17" s="5"/>
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="2:19">
       <c r="B18" s="1">
         <v>14</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="T18" s="1"/>
-    </row>
-    <row r="19" spans="2:20">
+      <c r="D18" s="5"/>
+      <c r="P18" s="5"/>
+    </row>
+    <row r="19" spans="2:19">
       <c r="B19" s="1">
         <v>15</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="T19" s="1"/>
-    </row>
-    <row r="20" spans="2:20">
+      <c r="D19" s="5"/>
+      <c r="P19" s="5"/>
+    </row>
+    <row r="20" spans="2:19">
       <c r="B20" s="1">
         <v>16</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="T20" s="1"/>
-    </row>
-    <row r="21" spans="2:20">
+      <c r="D20" s="5"/>
+      <c r="P20" s="5"/>
+    </row>
+    <row r="21" spans="2:19">
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="1"/>
-    </row>
-    <row r="22" spans="2:20">
+      <c r="C21" s="8"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="9"/>
+    </row>
+    <row r="22" spans="2:19">
       <c r="B22" s="1">
         <v>18</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="T22" s="1"/>
-    </row>
-    <row r="23" spans="2:20">
+      <c r="D22" s="5"/>
+      <c r="P22" s="5"/>
+    </row>
+    <row r="23" spans="2:19">
       <c r="B23" s="1">
         <v>19</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="T23" s="1"/>
-    </row>
-    <row r="24" spans="2:20">
+      <c r="D23" s="5"/>
+      <c r="P23" s="5"/>
+    </row>
+    <row r="24" spans="2:19">
       <c r="B24" s="1">
         <v>20</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="Q24" s="8"/>
-    </row>
-    <row r="25" spans="2:20">
+      <c r="D24" s="5"/>
+      <c r="P24" s="5"/>
+    </row>
+    <row r="25" spans="2:19">
       <c r="B25" s="1">
         <v>21</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="Q25" s="8"/>
-    </row>
-    <row r="26" spans="2:20">
+      <c r="D25" s="5"/>
+      <c r="P25" s="5"/>
+    </row>
+    <row r="26" spans="2:19">
       <c r="B26" s="1">
         <v>22</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="Q26" s="8"/>
-    </row>
-    <row r="27" spans="2:20">
+      <c r="D26" s="5"/>
+      <c r="P26" s="5"/>
+    </row>
+    <row r="27" spans="2:19">
       <c r="B27" s="1">
         <v>23</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="Q27" s="8"/>
-    </row>
-    <row r="28" spans="2:20">
+      <c r="D27" s="5"/>
+      <c r="P27" s="5"/>
+    </row>
+    <row r="28" spans="2:19">
       <c r="B28" s="1">
         <v>24</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="Q28" s="8"/>
-    </row>
-    <row r="29" spans="2:20">
+      <c r="D28" s="5"/>
+      <c r="P28" s="5"/>
+    </row>
+    <row r="29" spans="2:19">
       <c r="B29" s="1">
         <v>25</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="Q29" s="8"/>
-    </row>
-    <row r="30" spans="2:20">
+      <c r="D29" s="5"/>
+      <c r="P29" s="5"/>
+    </row>
+    <row r="30" spans="2:19">
       <c r="B30" s="1">
         <v>26</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="Q30" s="8"/>
-    </row>
-    <row r="31" spans="2:20">
+      <c r="D30" s="5"/>
+      <c r="P30" s="5"/>
+    </row>
+    <row r="31" spans="2:19">
       <c r="B31" s="1">
         <v>27</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="Q31" s="8"/>
-    </row>
-    <row r="32" spans="2:20">
+      <c r="D31" s="5"/>
+      <c r="P31" s="5"/>
+    </row>
+    <row r="32" spans="2:19">
       <c r="B32" s="1">
         <v>28</v>
       </c>
-      <c r="D32" s="8"/>
-      <c r="Q32" s="8"/>
-    </row>
-    <row r="33" spans="2:17">
+      <c r="D32" s="5"/>
+      <c r="P32" s="5"/>
+    </row>
+    <row r="33" spans="2:4">
       <c r="B33" s="1">
         <v>29</v>
       </c>
-      <c r="D33" s="8"/>
-      <c r="Q33" s="8"/>
-    </row>
-    <row r="34" spans="2:17">
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="2:4">
       <c r="B34" s="1">
         <v>30</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="Q34" s="8"/>
-    </row>
-    <row r="35" spans="2:17">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="2:4">
       <c r="B35" s="1">
         <v>31</v>
       </c>
-      <c r="D35" s="8"/>
-      <c r="Q35" s="8"/>
-    </row>
-    <row r="36" spans="2:17">
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="2:4">
       <c r="B36" s="1">
         <v>32</v>
       </c>
-      <c r="D36" s="8"/>
-      <c r="Q36" s="8"/>
-    </row>
-    <row r="37" spans="2:17">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="2:4">
       <c r="B37" s="1">
         <v>33</v>
       </c>
-      <c r="D37" s="8"/>
-      <c r="Q37" s="8"/>
-    </row>
-    <row r="38" spans="2:17">
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="2:4">
       <c r="B38" s="1">
         <v>34</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="Q38" s="8"/>
-    </row>
-    <row r="39" spans="2:17">
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="2:4">
       <c r="B39" s="1">
         <v>35</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="Q39" s="8"/>
-    </row>
-    <row r="40" spans="2:17">
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="2:4">
       <c r="B40" s="1">
         <v>36</v>
       </c>
-      <c r="D40" s="8"/>
-      <c r="Q40" s="8"/>
-    </row>
-    <row r="41" spans="2:17">
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="2:4">
       <c r="B41" s="1">
         <v>37</v>
       </c>
-      <c r="D41" s="8"/>
-      <c r="Q41" s="8"/>
-    </row>
-    <row r="42" spans="2:17">
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="2:4">
       <c r="B42" s="1">
         <v>38</v>
       </c>
-      <c r="D42" s="8"/>
-      <c r="Q42" s="8"/>
-    </row>
-    <row r="43" spans="2:17">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="2:4">
       <c r="B43" s="1">
         <v>39</v>
       </c>
-      <c r="D43" s="8"/>
-      <c r="Q43" s="8"/>
-    </row>
-    <row r="44" spans="2:17">
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="2:4">
       <c r="B44" s="1">
         <v>40</v>
       </c>
-      <c r="D44" s="8"/>
-      <c r="Q44" s="8"/>
-    </row>
-    <row r="45" spans="2:17">
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="2:4">
       <c r="B45" s="1">
         <v>41</v>
       </c>
-      <c r="D45" s="8"/>
-      <c r="Q45" s="8"/>
-    </row>
-    <row r="46" spans="2:17">
+      <c r="D45" s="5"/>
+    </row>
+    <row r="46" spans="2:4">
       <c r="B46" s="1">
         <v>42</v>
       </c>
-      <c r="D46" s="8"/>
-      <c r="Q46" s="8"/>
-    </row>
-    <row r="47" spans="2:17">
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="2:4">
       <c r="B47" s="1">
         <v>43</v>
       </c>
-      <c r="D47" s="8"/>
-      <c r="Q47" s="8"/>
-    </row>
-    <row r="48" spans="2:17">
+      <c r="D47" s="5"/>
+    </row>
+    <row r="48" spans="2:4">
       <c r="B48" s="1">
         <v>44</v>
       </c>
-      <c r="D48" s="8"/>
-      <c r="Q48" s="8"/>
-    </row>
-    <row r="49" spans="2:17">
+      <c r="D48" s="5"/>
+    </row>
+    <row r="49" spans="2:4">
       <c r="B49" s="1">
         <v>45</v>
       </c>
-      <c r="D49" s="8"/>
-      <c r="Q49" s="8"/>
-    </row>
-    <row r="50" spans="2:17">
+      <c r="D49" s="5"/>
+    </row>
+    <row r="50" spans="2:4">
       <c r="B50" s="1">
         <v>46</v>
       </c>
-      <c r="D50" s="8"/>
-      <c r="Q50" s="8"/>
-    </row>
-    <row r="51" spans="2:17">
+      <c r="D50" s="5"/>
+    </row>
+    <row r="51" spans="2:4">
       <c r="B51" s="1">
         <v>47</v>
       </c>
-      <c r="D51" s="8"/>
-      <c r="Q51" s="8"/>
-    </row>
-    <row r="52" spans="2:17">
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="2:4">
       <c r="B52" s="1">
         <v>48</v>
       </c>
-      <c r="D52" s="8"/>
-      <c r="Q52" s="8"/>
-    </row>
-    <row r="53" spans="2:17">
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="2:4">
       <c r="B53" s="1">
         <v>49</v>
       </c>
-      <c r="D53" s="8"/>
-      <c r="Q53" s="8"/>
-    </row>
-    <row r="54" spans="2:17">
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="2:4">
       <c r="B54" s="1">
         <v>50</v>
       </c>
-      <c r="D54" s="8"/>
-      <c r="Q54" s="8"/>
-    </row>
-    <row r="55" spans="2:17">
+      <c r="D54" s="5"/>
+    </row>
+    <row r="55" spans="2:4">
       <c r="B55" s="1">
         <v>51</v>
       </c>
-      <c r="D55" s="8"/>
-      <c r="Q55" s="8"/>
-    </row>
-    <row r="56" spans="2:17">
+      <c r="D55" s="5"/>
+    </row>
+    <row r="56" spans="2:4">
       <c r="B56" s="1">
         <v>52</v>
       </c>
-      <c r="D56" s="8"/>
-      <c r="Q56" s="8"/>
-    </row>
-    <row r="57" spans="2:17">
+      <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="2:4">
       <c r="B57" s="1">
         <v>53</v>
       </c>
-      <c r="D57" s="8"/>
-      <c r="Q57" s="8"/>
-    </row>
-    <row r="58" spans="2:17">
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="2:4">
       <c r="B58" s="1">
         <v>54</v>
       </c>
-      <c r="D58" s="8"/>
-      <c r="Q58" s="8"/>
-    </row>
-    <row r="59" spans="2:17">
+      <c r="D58" s="5"/>
+    </row>
+    <row r="59" spans="2:4">
       <c r="B59" s="1">
         <v>55</v>
       </c>
-      <c r="D59" s="8"/>
-      <c r="Q59" s="8"/>
-    </row>
-    <row r="60" spans="2:17">
+      <c r="D59" s="5"/>
+    </row>
+    <row r="60" spans="2:4">
       <c r="B60" s="1">
         <v>56</v>
       </c>
-      <c r="D60" s="8"/>
-      <c r="Q60" s="8"/>
-    </row>
-    <row r="61" spans="2:17">
+      <c r="D60" s="5"/>
+    </row>
+    <row r="61" spans="2:4">
       <c r="B61" s="1">
         <v>57</v>
       </c>
-      <c r="D61" s="8"/>
-      <c r="Q61" s="8"/>
-    </row>
-    <row r="62" spans="2:17">
+      <c r="D61" s="5"/>
+    </row>
+    <row r="62" spans="2:4">
       <c r="B62" s="1">
         <v>58</v>
       </c>
-      <c r="D62" s="8"/>
-      <c r="Q62" s="8"/>
-    </row>
-    <row r="63" spans="2:17">
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63" spans="2:4">
       <c r="B63" s="1">
         <v>59</v>
       </c>
-      <c r="D63" s="8"/>
-      <c r="Q63" s="8"/>
-    </row>
-    <row r="64" spans="2:17">
+      <c r="D63" s="5"/>
+    </row>
+    <row r="64" spans="2:4">
       <c r="B64" s="1">
         <v>60</v>
       </c>
-      <c r="D64" s="8"/>
-      <c r="Q64" s="8"/>
-    </row>
-    <row r="65" spans="2:17">
+      <c r="D64" s="5"/>
+    </row>
+    <row r="65" spans="2:4">
       <c r="B65" s="1">
         <v>61</v>
       </c>
-      <c r="D65" s="8"/>
-      <c r="Q65" s="8"/>
-    </row>
-    <row r="66" spans="2:17">
+      <c r="D65" s="5"/>
+    </row>
+    <row r="66" spans="2:4">
       <c r="B66" s="1">
         <v>62</v>
       </c>
-      <c r="D66" s="8"/>
-      <c r="Q66" s="8"/>
-    </row>
-    <row r="67" spans="2:17">
+      <c r="D66" s="5"/>
+    </row>
+    <row r="67" spans="2:4">
       <c r="B67" s="1">
         <v>63</v>
       </c>
-      <c r="D67" s="8"/>
-      <c r="Q67" s="8"/>
-    </row>
-    <row r="68" spans="2:17">
+      <c r="D67" s="5"/>
+    </row>
+    <row r="68" spans="2:4">
       <c r="B68" s="1">
         <v>64</v>
       </c>
-      <c r="D68" s="8"/>
-      <c r="Q68" s="8"/>
-    </row>
-    <row r="69" spans="2:17">
+      <c r="D68" s="5"/>
+    </row>
+    <row r="69" spans="2:4">
       <c r="B69" s="1">
         <v>65</v>
       </c>
-      <c r="D69" s="8"/>
-      <c r="Q69" s="8"/>
-    </row>
-    <row r="70" spans="2:17">
+      <c r="D69" s="5"/>
+    </row>
+    <row r="70" spans="2:4">
       <c r="B70" s="1">
         <v>66</v>
       </c>
-      <c r="D70" s="8"/>
-      <c r="Q70" s="8"/>
-    </row>
-    <row r="71" spans="2:17">
+      <c r="D70" s="5"/>
+    </row>
+    <row r="71" spans="2:4">
       <c r="B71" s="1">
         <v>67</v>
       </c>
-      <c r="D71" s="8"/>
-      <c r="Q71" s="8"/>
-    </row>
-    <row r="72" spans="2:17">
+      <c r="D71" s="5"/>
+    </row>
+    <row r="72" spans="2:4">
       <c r="B72" s="1">
         <v>68</v>
       </c>
-      <c r="D72" s="8"/>
-      <c r="Q72" s="8"/>
-    </row>
-    <row r="73" spans="2:17">
+      <c r="D72" s="5"/>
+    </row>
+    <row r="73" spans="2:4">
       <c r="B73" s="1">
         <v>69</v>
       </c>
-      <c r="D73" s="8"/>
-      <c r="Q73" s="8"/>
-    </row>
-    <row r="74" spans="2:17">
+      <c r="D73" s="5"/>
+    </row>
+    <row r="74" spans="2:4">
       <c r="B74" s="1">
         <v>70</v>
       </c>
-      <c r="D74" s="8"/>
-      <c r="Q74" s="8"/>
-    </row>
-    <row r="75" spans="2:17">
+      <c r="D74" s="5"/>
+    </row>
+    <row r="75" spans="2:4">
       <c r="B75" s="1">
         <v>71</v>
       </c>
-      <c r="D75" s="8"/>
-      <c r="Q75" s="8"/>
-    </row>
-    <row r="76" spans="2:17">
+      <c r="D75" s="5"/>
+    </row>
+    <row r="76" spans="2:4">
       <c r="B76" s="1">
         <v>72</v>
       </c>
-      <c r="D76" s="8"/>
-      <c r="Q76" s="8"/>
-    </row>
-    <row r="77" spans="2:17">
+      <c r="D76" s="5"/>
+    </row>
+    <row r="77" spans="2:4">
       <c r="B77" s="1">
         <v>73</v>
       </c>
-      <c r="D77" s="8"/>
-      <c r="Q77" s="8"/>
-    </row>
-    <row r="78" spans="2:17">
+      <c r="D77" s="5"/>
+    </row>
+    <row r="78" spans="2:4">
       <c r="B78" s="1">
         <v>74</v>
       </c>
-      <c r="D78" s="8"/>
-      <c r="Q78" s="8"/>
-    </row>
-    <row r="79" spans="2:17">
+      <c r="D78" s="5"/>
+    </row>
+    <row r="79" spans="2:4">
       <c r="B79" s="1">
         <v>75</v>
       </c>
-      <c r="D79" s="8"/>
-      <c r="Q79" s="8"/>
-    </row>
-    <row r="80" spans="2:17">
+      <c r="D79" s="5"/>
+    </row>
+    <row r="80" spans="2:4">
       <c r="B80" s="1">
         <v>76</v>
       </c>
-      <c r="D80" s="8"/>
-      <c r="Q80" s="8"/>
-    </row>
-    <row r="81" spans="2:17">
+      <c r="D80" s="5"/>
+    </row>
+    <row r="81" spans="2:4">
       <c r="B81" s="1">
         <v>77</v>
       </c>
-      <c r="D81" s="8"/>
-      <c r="Q81" s="8"/>
-    </row>
-    <row r="82" spans="2:17">
+      <c r="D81" s="5"/>
+    </row>
+    <row r="82" spans="2:4">
       <c r="B82" s="1">
         <v>78</v>
       </c>
-      <c r="D82" s="8"/>
-      <c r="Q82" s="8"/>
-    </row>
-    <row r="83" spans="2:17">
+      <c r="D82" s="5"/>
+    </row>
+    <row r="83" spans="2:4">
       <c r="B83" s="1">
         <v>79</v>
       </c>
-      <c r="D83" s="8"/>
-      <c r="Q83" s="8"/>
-    </row>
-    <row r="84" spans="2:17">
+      <c r="D83" s="5"/>
+    </row>
+    <row r="84" spans="2:4">
       <c r="B84" s="1">
         <v>80</v>
       </c>
-      <c r="D84" s="8"/>
-      <c r="Q84" s="8"/>
-    </row>
-    <row r="85" spans="2:17">
+      <c r="D84" s="5"/>
+    </row>
+    <row r="85" spans="2:4">
       <c r="B85" s="1">
         <v>81</v>
       </c>
-      <c r="D85" s="8"/>
-      <c r="Q85" s="8"/>
-    </row>
-    <row r="86" spans="2:17">
+      <c r="D85" s="5"/>
+    </row>
+    <row r="86" spans="2:4">
       <c r="B86" s="1">
         <v>82</v>
       </c>
-      <c r="D86" s="8"/>
-      <c r="Q86" s="8"/>
-    </row>
-    <row r="87" spans="2:17">
+      <c r="D86" s="5"/>
+    </row>
+    <row r="87" spans="2:4">
       <c r="B87" s="1">
         <v>83</v>
       </c>
-      <c r="D87" s="8"/>
-      <c r="Q87" s="8"/>
-    </row>
-    <row r="88" spans="2:17">
+      <c r="D87" s="5"/>
+    </row>
+    <row r="88" spans="2:4">
       <c r="B88" s="1">
         <v>84</v>
       </c>
-      <c r="D88" s="8"/>
-      <c r="Q88" s="8"/>
-    </row>
-    <row r="89" spans="2:17">
+      <c r="D88" s="5"/>
+    </row>
+    <row r="89" spans="2:4">
       <c r="B89" s="1">
         <v>85</v>
       </c>
-      <c r="D89" s="8"/>
-      <c r="Q89" s="8"/>
-    </row>
-    <row r="90" spans="2:17">
+      <c r="D89" s="5"/>
+    </row>
+    <row r="90" spans="2:4">
       <c r="B90" s="1">
         <v>86</v>
       </c>
-      <c r="D90" s="8"/>
-      <c r="Q90" s="8"/>
-    </row>
-    <row r="91" spans="2:17">
+      <c r="D90" s="5"/>
+    </row>
+    <row r="91" spans="2:4">
       <c r="B91" s="1">
         <v>87</v>
       </c>
-      <c r="D91" s="8"/>
-      <c r="Q91" s="8"/>
-    </row>
-    <row r="92" spans="2:17">
+      <c r="D91" s="5"/>
+    </row>
+    <row r="92" spans="2:4">
       <c r="B92" s="1">
         <v>88</v>
       </c>
-      <c r="D92" s="8"/>
-      <c r="Q92" s="8"/>
-    </row>
-    <row r="93" spans="2:17">
+      <c r="D92" s="5"/>
+    </row>
+    <row r="93" spans="2:4">
       <c r="B93" s="1">
         <v>89</v>
       </c>
-      <c r="D93" s="8"/>
-      <c r="Q93" s="8"/>
-    </row>
-    <row r="94" spans="2:17">
+      <c r="D93" s="5"/>
+    </row>
+    <row r="94" spans="2:4">
       <c r="B94" s="1">
         <v>90</v>
       </c>
-      <c r="D94" s="8"/>
-      <c r="Q94" s="8"/>
-    </row>
-    <row r="95" spans="2:17">
+      <c r="D94" s="5"/>
+    </row>
+    <row r="95" spans="2:4">
       <c r="B95" s="1">
         <v>91</v>
       </c>
-      <c r="D95" s="8"/>
-      <c r="Q95" s="8"/>
-    </row>
-    <row r="96" spans="2:17">
+      <c r="D95" s="5"/>
+    </row>
+    <row r="96" spans="2:4">
       <c r="B96" s="1">
         <v>92</v>
       </c>
-      <c r="D96" s="8"/>
-      <c r="Q96" s="8"/>
-    </row>
-    <row r="97" spans="2:17">
+      <c r="D96" s="5"/>
+    </row>
+    <row r="97" spans="2:4">
       <c r="B97" s="1">
         <v>93</v>
       </c>
-      <c r="D97" s="8"/>
-      <c r="Q97" s="8"/>
-    </row>
-    <row r="98" spans="2:17">
+      <c r="D97" s="5"/>
+    </row>
+    <row r="98" spans="2:4">
       <c r="B98" s="1">
         <v>94</v>
       </c>
-      <c r="D98" s="8"/>
-      <c r="Q98" s="8"/>
-    </row>
-    <row r="99" spans="2:17">
+      <c r="D98" s="5"/>
+    </row>
+    <row r="99" spans="2:4">
       <c r="B99" s="1">
         <v>95</v>
       </c>
-      <c r="D99" s="8"/>
-      <c r="Q99" s="8"/>
-    </row>
-    <row r="100" spans="2:17">
+      <c r="D99" s="5"/>
+    </row>
+    <row r="100" spans="2:4">
       <c r="B100" s="1">
         <v>96</v>
       </c>
-      <c r="D100" s="8"/>
-      <c r="Q100" s="8"/>
-    </row>
-    <row r="101" spans="2:17">
+      <c r="D100" s="5"/>
+    </row>
+    <row r="101" spans="2:4">
       <c r="B101" s="1">
         <v>97</v>
       </c>
-      <c r="D101" s="8"/>
-      <c r="Q101" s="8"/>
-    </row>
-    <row r="102" spans="2:17">
+      <c r="D101" s="5"/>
+    </row>
+    <row r="102" spans="2:4">
       <c r="B102" s="1">
         <v>98</v>
       </c>
-      <c r="D102" s="8"/>
-      <c r="Q102" s="8"/>
-    </row>
-    <row r="103" spans="2:17">
+      <c r="D102" s="5"/>
+    </row>
+    <row r="103" spans="2:4">
       <c r="B103" s="1">
         <v>99</v>
       </c>
-      <c r="D103" s="8"/>
-      <c r="Q103" s="8"/>
-    </row>
-    <row r="104" spans="2:17">
+      <c r="D103" s="5"/>
+    </row>
+    <row r="104" spans="2:4">
       <c r="B104" s="1">
         <v>100</v>
       </c>
-      <c r="D104" s="8"/>
-      <c r="Q104" s="8"/>
-    </row>
-    <row r="105" spans="2:17">
+      <c r="D104" s="5"/>
+    </row>
+    <row r="105" spans="2:4">
       <c r="B105" s="1">
         <v>101</v>
       </c>
-      <c r="D105" s="8"/>
-      <c r="Q105" s="8"/>
-    </row>
-    <row r="106" spans="2:17">
+      <c r="D105" s="5"/>
+    </row>
+    <row r="106" spans="2:4">
       <c r="B106" s="1">
         <v>102</v>
       </c>
-      <c r="D106" s="8"/>
-      <c r="Q106" s="8"/>
-    </row>
-    <row r="107" spans="2:17">
+      <c r="D106" s="5"/>
+    </row>
+    <row r="107" spans="2:4">
       <c r="B107" s="1">
         <v>103</v>
       </c>
-      <c r="D107" s="8"/>
-      <c r="Q107" s="8"/>
-    </row>
-    <row r="108" spans="2:17">
+      <c r="D107" s="5"/>
+    </row>
+    <row r="108" spans="2:4">
       <c r="B108" s="1">
         <v>104</v>
       </c>
-      <c r="D108" s="8"/>
-      <c r="Q108" s="8"/>
-    </row>
-    <row r="109" spans="2:17">
+      <c r="D108" s="5"/>
+    </row>
+    <row r="109" spans="2:4">
       <c r="B109" s="1">
         <v>105</v>
       </c>
-      <c r="D109" s="8"/>
-      <c r="Q109" s="8"/>
-    </row>
-    <row r="110" spans="2:17">
+      <c r="D109" s="5"/>
+    </row>
+    <row r="110" spans="2:4">
       <c r="B110" s="1">
         <v>106</v>
       </c>
-      <c r="D110" s="8"/>
-      <c r="Q110" s="8"/>
-    </row>
-    <row r="111" spans="2:17">
+      <c r="D110" s="5"/>
+    </row>
+    <row r="111" spans="2:4">
       <c r="B111" s="1">
         <v>107</v>
       </c>
-      <c r="D111" s="8"/>
-      <c r="Q111" s="8"/>
-    </row>
-    <row r="112" spans="2:17">
+      <c r="D111" s="5"/>
+    </row>
+    <row r="112" spans="2:4">
       <c r="B112" s="1">
         <v>108</v>
       </c>
-      <c r="D112" s="8"/>
-      <c r="Q112" s="8"/>
-    </row>
-    <row r="113" spans="2:17">
+      <c r="D112" s="5"/>
+    </row>
+    <row r="113" spans="2:4">
       <c r="B113" s="1">
         <v>109</v>
       </c>
-      <c r="D113" s="8"/>
-      <c r="Q113" s="8"/>
-    </row>
-    <row r="114" spans="2:17">
+      <c r="D113" s="5"/>
+    </row>
+    <row r="114" spans="2:4">
       <c r="B114" s="1">
         <v>110</v>
       </c>
-      <c r="D114" s="8"/>
-      <c r="Q114" s="8"/>
-    </row>
-    <row r="115" spans="2:17">
+      <c r="D114" s="5"/>
+    </row>
+    <row r="115" spans="2:4">
       <c r="B115" s="1">
         <v>111</v>
       </c>
-      <c r="D115" s="8"/>
-      <c r="Q115" s="8"/>
-    </row>
-    <row r="116" spans="2:17">
+      <c r="D115" s="5"/>
+    </row>
+    <row r="116" spans="2:4">
       <c r="B116" s="1">
         <v>112</v>
       </c>
-      <c r="D116" s="8"/>
-      <c r="Q116" s="8"/>
-    </row>
-    <row r="117" spans="2:17">
+      <c r="D116" s="5"/>
+    </row>
+    <row r="117" spans="2:4">
       <c r="B117" s="1">
         <v>113</v>
       </c>
-      <c r="D117" s="8"/>
-      <c r="Q117" s="8"/>
-    </row>
-    <row r="118" spans="2:17">
+      <c r="D117" s="5"/>
+    </row>
+    <row r="118" spans="2:4">
       <c r="B118" s="1">
         <v>114</v>
       </c>
-      <c r="D118" s="8"/>
-      <c r="Q118" s="8"/>
-    </row>
-    <row r="119" spans="2:17">
+      <c r="D118" s="5"/>
+    </row>
+    <row r="119" spans="2:4">
       <c r="B119" s="1">
         <v>115</v>
       </c>
-      <c r="D119" s="8"/>
-      <c r="Q119" s="8"/>
-    </row>
-    <row r="120" spans="2:17">
+      <c r="D119" s="5"/>
+    </row>
+    <row r="120" spans="2:4">
       <c r="B120" s="1">
         <v>116</v>
       </c>
-      <c r="D120" s="8"/>
-      <c r="Q120" s="8"/>
-    </row>
-    <row r="121" spans="2:17">
+      <c r="D120" s="5"/>
+    </row>
+    <row r="121" spans="2:4">
       <c r="B121" s="1">
         <v>117</v>
       </c>
-      <c r="D121" s="8"/>
-      <c r="Q121" s="8"/>
-    </row>
-    <row r="122" spans="2:17">
+      <c r="D121" s="5"/>
+    </row>
+    <row r="122" spans="2:4">
       <c r="B122" s="1">
         <v>118</v>
       </c>
-      <c r="D122" s="8"/>
-      <c r="Q122" s="8"/>
-    </row>
-    <row r="123" spans="2:17">
+      <c r="D122" s="5"/>
+    </row>
+    <row r="123" spans="2:4">
       <c r="B123" s="1">
         <v>119</v>
       </c>
-      <c r="D123" s="8"/>
-      <c r="Q123" s="8"/>
-    </row>
-    <row r="124" spans="2:17">
+      <c r="D123" s="5"/>
+    </row>
+    <row r="124" spans="2:4">
       <c r="B124" s="1">
         <v>120</v>
       </c>
-      <c r="D124" s="8"/>
-      <c r="Q124" s="8"/>
-    </row>
-    <row r="125" spans="2:17">
+      <c r="D124" s="5"/>
+    </row>
+    <row r="125" spans="2:4">
       <c r="B125" s="1">
         <v>121</v>
       </c>
-      <c r="D125" s="8"/>
-      <c r="Q125" s="8"/>
-    </row>
-    <row r="126" spans="2:17">
+      <c r="D125" s="5"/>
+    </row>
+    <row r="126" spans="2:4">
       <c r="B126" s="1">
         <v>122</v>
       </c>
-      <c r="D126" s="8"/>
-      <c r="Q126" s="8"/>
-    </row>
-    <row r="127" spans="2:17">
+      <c r="D126" s="5"/>
+    </row>
+    <row r="127" spans="2:4">
       <c r="B127" s="1">
         <v>123</v>
       </c>
-      <c r="D127" s="8"/>
-      <c r="Q127" s="8"/>
-    </row>
-    <row r="128" spans="2:17">
+      <c r="D127" s="5"/>
+    </row>
+    <row r="128" spans="2:4">
       <c r="B128" s="1">
         <v>124</v>
       </c>
-      <c r="D128" s="8"/>
-      <c r="Q128" s="8"/>
-    </row>
-    <row r="129" spans="2:17">
+      <c r="D128" s="5"/>
+    </row>
+    <row r="129" spans="2:4">
       <c r="B129" s="1">
         <v>125</v>
       </c>
-      <c r="D129" s="8"/>
-      <c r="Q129" s="8"/>
-    </row>
-    <row r="130" spans="2:17">
+      <c r="D129" s="5"/>
+    </row>
+    <row r="130" spans="2:4">
       <c r="B130" s="1">
         <v>126</v>
       </c>
-      <c r="D130" s="8"/>
-      <c r="Q130" s="8"/>
-    </row>
-    <row r="131" spans="2:17">
+      <c r="D130" s="5"/>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131" s="1">
         <v>127</v>
       </c>
-      <c r="D131" s="8"/>
-      <c r="Q131" s="8"/>
-    </row>
-    <row r="132" spans="2:17">
+      <c r="D131" s="5"/>
+    </row>
+    <row r="132" spans="2:4">
       <c r="B132" s="1">
         <v>128</v>
       </c>
-      <c r="D132" s="8"/>
-      <c r="Q132" s="8"/>
-    </row>
-    <row r="133" spans="2:17">
+      <c r="D132" s="5"/>
+    </row>
+    <row r="133" spans="2:4">
       <c r="B133" s="1">
         <v>129</v>
       </c>
-      <c r="D133" s="8"/>
-      <c r="Q133" s="8"/>
-    </row>
-    <row r="134" spans="2:17">
+      <c r="D133" s="5"/>
+    </row>
+    <row r="134" spans="2:4">
       <c r="B134" s="1">
         <v>130</v>
       </c>
-      <c r="D134" s="8"/>
-      <c r="Q134" s="8"/>
-    </row>
-    <row r="135" spans="2:17">
+      <c r="D134" s="5"/>
+    </row>
+    <row r="135" spans="2:4">
       <c r="B135" s="1">
         <v>131</v>
       </c>
-      <c r="D135" s="8"/>
-      <c r="Q135" s="8"/>
-    </row>
-    <row r="136" spans="2:17">
+      <c r="D135" s="5"/>
+    </row>
+    <row r="136" spans="2:4">
       <c r="B136" s="1">
         <v>132</v>
       </c>
-      <c r="D136" s="8"/>
-      <c r="Q136" s="8"/>
-    </row>
-    <row r="137" spans="2:17">
+      <c r="D136" s="5"/>
+    </row>
+    <row r="137" spans="2:4">
       <c r="B137" s="1">
         <v>133</v>
       </c>
-      <c r="D137" s="8"/>
-      <c r="Q137" s="8"/>
-    </row>
-    <row r="138" spans="2:17">
+      <c r="D137" s="5"/>
+    </row>
+    <row r="138" spans="2:4">
       <c r="B138" s="1">
         <v>134</v>
       </c>
-      <c r="D138" s="8"/>
-      <c r="Q138" s="8"/>
-    </row>
-    <row r="139" spans="2:17">
+      <c r="D138" s="5"/>
+    </row>
+    <row r="139" spans="2:4">
       <c r="B139" s="1">
         <v>135</v>
       </c>
-      <c r="D139" s="8"/>
-      <c r="Q139" s="8"/>
-    </row>
-    <row r="140" spans="2:17">
+      <c r="D139" s="5"/>
+    </row>
+    <row r="140" spans="2:4">
       <c r="B140" s="1">
         <v>136</v>
       </c>
-      <c r="D140" s="8"/>
-      <c r="Q140" s="8"/>
-    </row>
-    <row r="141" spans="2:17">
+      <c r="D140" s="5"/>
+    </row>
+    <row r="141" spans="2:4">
       <c r="B141" s="1">
         <v>137</v>
       </c>
-      <c r="D141" s="8"/>
-      <c r="Q141" s="8"/>
-    </row>
-    <row r="142" spans="2:17">
+      <c r="D141" s="5"/>
+    </row>
+    <row r="142" spans="2:4">
       <c r="B142" s="1">
         <v>138</v>
       </c>
-      <c r="D142" s="8"/>
-      <c r="Q142" s="8"/>
-    </row>
-    <row r="143" spans="2:17">
+      <c r="D142" s="5"/>
+    </row>
+    <row r="143" spans="2:4">
       <c r="B143" s="1">
         <v>139</v>
       </c>
-      <c r="D143" s="8"/>
-      <c r="Q143" s="8"/>
-    </row>
-    <row r="144" spans="2:17">
+      <c r="D143" s="5"/>
+    </row>
+    <row r="144" spans="2:4">
       <c r="B144" s="1">
         <v>140</v>
       </c>
-      <c r="D144" s="8"/>
-      <c r="Q144" s="8"/>
-    </row>
-    <row r="145" spans="2:17">
+      <c r="D144" s="5"/>
+    </row>
+    <row r="145" spans="2:4">
       <c r="B145" s="1">
         <v>141</v>
       </c>
-      <c r="D145" s="8"/>
-      <c r="Q145" s="8"/>
-    </row>
-    <row r="146" spans="2:17">
+      <c r="D145" s="5"/>
+    </row>
+    <row r="146" spans="2:4">
       <c r="B146" s="1">
         <v>142</v>
       </c>
-      <c r="D146" s="8"/>
-      <c r="Q146" s="8"/>
-    </row>
-    <row r="147" spans="2:17">
+      <c r="D146" s="5"/>
+    </row>
+    <row r="147" spans="2:4">
       <c r="B147" s="1">
         <v>143</v>
       </c>
-      <c r="D147" s="8"/>
-      <c r="Q147" s="8"/>
-    </row>
-    <row r="148" spans="2:17">
+      <c r="D147" s="5"/>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="1">
         <v>144</v>
       </c>
-      <c r="D148" s="8"/>
-      <c r="Q148" s="8"/>
-    </row>
-    <row r="149" spans="2:17">
+      <c r="D148" s="5"/>
+    </row>
+    <row r="149" spans="2:4">
       <c r="B149" s="1">
         <v>145</v>
       </c>
-      <c r="D149" s="8"/>
-      <c r="Q149" s="8"/>
-    </row>
-    <row r="150" spans="2:17">
+      <c r="D149" s="5"/>
+    </row>
+    <row r="150" spans="2:4">
       <c r="B150" s="1">
         <v>146</v>
       </c>
-      <c r="D150" s="8"/>
-      <c r="Q150" s="8"/>
-    </row>
-    <row r="151" spans="2:17">
+      <c r="D150" s="5"/>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="1">
         <v>147</v>
       </c>
-      <c r="D151" s="8"/>
-      <c r="Q151" s="8"/>
-    </row>
-    <row r="152" spans="2:17">
+      <c r="D151" s="5"/>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="1">
         <v>148</v>
       </c>
-      <c r="D152" s="8"/>
-      <c r="Q152" s="8"/>
-    </row>
-    <row r="153" spans="2:17">
+      <c r="D152" s="5"/>
+    </row>
+    <row r="153" spans="2:4">
       <c r="B153" s="1">
         <v>149</v>
       </c>
-      <c r="D153" s="8"/>
-      <c r="Q153" s="8"/>
-    </row>
-    <row r="154" spans="2:17">
+      <c r="D153" s="5"/>
+    </row>
+    <row r="154" spans="2:4">
       <c r="B154" s="1">
         <v>150</v>
       </c>
-      <c r="D154" s="8"/>
-      <c r="Q154" s="8"/>
-    </row>
-    <row r="155" spans="2:17">
+      <c r="D154" s="5"/>
+    </row>
+    <row r="155" spans="2:4">
       <c r="B155" s="1">
         <v>151</v>
       </c>
-      <c r="D155" s="8"/>
-      <c r="Q155" s="8"/>
-    </row>
-    <row r="156" spans="2:17">
+      <c r="D155" s="5"/>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="1">
         <v>152</v>
       </c>
-      <c r="D156" s="8"/>
-      <c r="Q156" s="8"/>
-    </row>
-    <row r="157" spans="2:17">
+      <c r="D156" s="5"/>
+    </row>
+    <row r="157" spans="2:4">
       <c r="B157" s="1">
         <v>153</v>
       </c>
-      <c r="D157" s="8"/>
-      <c r="Q157" s="8"/>
-    </row>
-    <row r="158" spans="2:17">
+      <c r="D157" s="5"/>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="1">
         <v>154</v>
       </c>
-      <c r="D158" s="8"/>
-      <c r="Q158" s="8"/>
-    </row>
-    <row r="159" spans="2:17">
+      <c r="D158" s="5"/>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="1">
         <v>155</v>
       </c>
-      <c r="D159" s="8"/>
-      <c r="Q159" s="8"/>
-    </row>
-    <row r="160" spans="2:17">
+      <c r="D159" s="5"/>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="1">
         <v>156</v>
       </c>
-      <c r="D160" s="8"/>
-      <c r="Q160" s="8"/>
-    </row>
-    <row r="161" spans="2:17">
+      <c r="D160" s="5"/>
+    </row>
+    <row r="161" spans="2:4">
       <c r="B161" s="1">
         <v>157</v>
       </c>
-      <c r="D161" s="8"/>
-      <c r="Q161" s="8"/>
-    </row>
-    <row r="162" spans="2:17">
+      <c r="D161" s="5"/>
+    </row>
+    <row r="162" spans="2:4">
       <c r="B162" s="1">
         <v>158</v>
       </c>
-      <c r="D162" s="8"/>
-      <c r="Q162" s="8"/>
-    </row>
-    <row r="163" spans="2:17">
+      <c r="D162" s="5"/>
+    </row>
+    <row r="163" spans="2:4">
       <c r="B163" s="1">
         <v>159</v>
       </c>
-      <c r="D163" s="8"/>
-      <c r="Q163" s="8"/>
-    </row>
-    <row r="164" spans="2:17">
+      <c r="D163" s="5"/>
+    </row>
+    <row r="164" spans="2:4">
       <c r="B164" s="1">
         <v>160</v>
       </c>
-      <c r="D164" s="8"/>
-      <c r="Q164" s="8"/>
-    </row>
-    <row r="165" spans="2:17">
+      <c r="D164" s="5"/>
+    </row>
+    <row r="165" spans="2:4">
       <c r="B165" s="1">
         <v>161</v>
       </c>
-      <c r="D165" s="8"/>
-      <c r="Q165" s="8"/>
-    </row>
-    <row r="166" spans="2:17">
+      <c r="D165" s="5"/>
+    </row>
+    <row r="166" spans="2:4">
       <c r="B166" s="1">
         <v>162</v>
       </c>
-      <c r="D166" s="8"/>
-      <c r="Q166" s="8"/>
-    </row>
-    <row r="167" spans="2:17">
+      <c r="D166" s="5"/>
+    </row>
+    <row r="167" spans="2:4">
       <c r="B167" s="1">
         <v>163</v>
       </c>
-      <c r="D167" s="8"/>
-      <c r="Q167" s="8"/>
-    </row>
-    <row r="168" spans="2:17">
+      <c r="D167" s="5"/>
+    </row>
+    <row r="168" spans="2:4">
       <c r="B168" s="1">
         <v>164</v>
       </c>
-      <c r="D168" s="8"/>
-      <c r="Q168" s="8"/>
-    </row>
-    <row r="169" spans="2:17">
+      <c r="D168" s="5"/>
+    </row>
+    <row r="169" spans="2:4">
       <c r="B169" s="1">
         <v>165</v>
       </c>
-      <c r="D169" s="8"/>
-      <c r="Q169" s="8"/>
-    </row>
-    <row r="170" spans="2:17">
+      <c r="D169" s="5"/>
+    </row>
+    <row r="170" spans="2:4">
       <c r="B170" s="1">
         <v>166</v>
       </c>
-      <c r="D170" s="8"/>
-      <c r="Q170" s="8"/>
-    </row>
-    <row r="171" spans="2:17">
+      <c r="D170" s="5"/>
+    </row>
+    <row r="171" spans="2:4">
       <c r="B171" s="1">
         <v>167</v>
       </c>
-      <c r="D171" s="8"/>
-      <c r="Q171" s="8"/>
-    </row>
-    <row r="172" spans="2:17">
+      <c r="D171" s="5"/>
+    </row>
+    <row r="172" spans="2:4">
       <c r="B172" s="1">
         <v>168</v>
       </c>
-      <c r="D172" s="8"/>
-      <c r="Q172" s="8"/>
-    </row>
-    <row r="173" spans="2:17">
+      <c r="D172" s="5"/>
+    </row>
+    <row r="173" spans="2:4">
       <c r="B173" s="1">
         <v>169</v>
       </c>
-      <c r="D173" s="8"/>
-      <c r="Q173" s="8"/>
-    </row>
-    <row r="174" spans="2:17">
+      <c r="D173" s="5"/>
+    </row>
+    <row r="174" spans="2:4">
       <c r="B174" s="1">
         <v>170</v>
       </c>
-      <c r="D174" s="8"/>
-      <c r="Q174" s="8"/>
-    </row>
-    <row r="175" spans="2:17">
+      <c r="D174" s="5"/>
+    </row>
+    <row r="175" spans="2:4">
       <c r="B175" s="1">
         <v>171</v>
       </c>
-      <c r="D175" s="8"/>
-      <c r="Q175" s="8"/>
-    </row>
-    <row r="176" spans="2:17">
+      <c r="D175" s="5"/>
+    </row>
+    <row r="176" spans="2:4">
       <c r="B176" s="1">
         <v>172</v>
       </c>
-      <c r="D176" s="8"/>
-      <c r="Q176" s="8"/>
-    </row>
-    <row r="177" spans="2:17">
+      <c r="D176" s="5"/>
+    </row>
+    <row r="177" spans="2:4">
       <c r="B177" s="1">
         <v>173</v>
       </c>
-      <c r="D177" s="8"/>
-      <c r="Q177" s="8"/>
-    </row>
-    <row r="178" spans="2:17">
+      <c r="D177" s="5"/>
+    </row>
+    <row r="178" spans="2:4">
       <c r="B178" s="1">
         <v>174</v>
       </c>
-      <c r="D178" s="8"/>
-      <c r="Q178" s="8"/>
-    </row>
-    <row r="179" spans="2:17">
+      <c r="D178" s="5"/>
+    </row>
+    <row r="179" spans="2:4">
       <c r="B179" s="1">
         <v>175</v>
       </c>
-      <c r="D179" s="8"/>
-      <c r="Q179" s="8"/>
-    </row>
-    <row r="180" spans="2:17">
+      <c r="D179" s="5"/>
+    </row>
+    <row r="180" spans="2:4">
       <c r="B180" s="1">
         <v>176</v>
       </c>
-      <c r="D180" s="8"/>
-      <c r="Q180" s="8"/>
-    </row>
-    <row r="181" spans="2:17">
+      <c r="D180" s="5"/>
+    </row>
+    <row r="181" spans="2:4">
       <c r="B181" s="1">
         <v>177</v>
       </c>
-      <c r="D181" s="8"/>
-      <c r="Q181" s="8"/>
-    </row>
-    <row r="182" spans="2:17">
+      <c r="D181" s="5"/>
+    </row>
+    <row r="182" spans="2:4">
       <c r="B182" s="1">
         <v>178</v>
       </c>
-      <c r="D182" s="8"/>
-      <c r="Q182" s="8"/>
-    </row>
-    <row r="183" spans="2:17">
+      <c r="D182" s="5"/>
+    </row>
+    <row r="183" spans="2:4">
       <c r="B183" s="1">
         <v>179</v>
       </c>
-      <c r="D183" s="8"/>
-      <c r="Q183" s="8"/>
-    </row>
-    <row r="184" spans="2:17">
+      <c r="D183" s="5"/>
+    </row>
+    <row r="184" spans="2:4">
       <c r="B184" s="1">
         <v>180</v>
       </c>
-      <c r="D184" s="8"/>
-      <c r="Q184" s="8"/>
-    </row>
-    <row r="185" spans="2:17">
+      <c r="D184" s="5"/>
+    </row>
+    <row r="185" spans="2:4">
       <c r="B185" s="1">
         <v>181</v>
       </c>
-      <c r="D185" s="8"/>
-      <c r="Q185" s="8"/>
-    </row>
-    <row r="186" spans="2:17">
+      <c r="D185" s="5"/>
+    </row>
+    <row r="186" spans="2:4">
       <c r="B186" s="1">
         <v>182</v>
       </c>
-      <c r="D186" s="8"/>
-      <c r="Q186" s="8"/>
-    </row>
-    <row r="187" spans="2:17">
+      <c r="D186" s="5"/>
+    </row>
+    <row r="187" spans="2:4">
       <c r="B187" s="1">
         <v>183</v>
       </c>
-      <c r="D187" s="8"/>
-      <c r="Q187" s="8"/>
-    </row>
-    <row r="188" spans="2:17">
+      <c r="D187" s="5"/>
+    </row>
+    <row r="188" spans="2:4">
       <c r="B188" s="1">
         <v>184</v>
       </c>
-      <c r="D188" s="8"/>
-      <c r="Q188" s="8"/>
-    </row>
-    <row r="189" spans="2:17">
+      <c r="D188" s="5"/>
+    </row>
+    <row r="189" spans="2:4">
       <c r="B189" s="1">
         <v>185</v>
       </c>
-      <c r="D189" s="8"/>
-      <c r="Q189" s="8"/>
-    </row>
-    <row r="190" spans="2:17">
+      <c r="D189" s="5"/>
+    </row>
+    <row r="190" spans="2:4">
       <c r="B190" s="1">
         <v>186</v>
       </c>
-      <c r="D190" s="8"/>
-      <c r="Q190" s="8"/>
-    </row>
-    <row r="191" spans="2:17">
+      <c r="D190" s="5"/>
+    </row>
+    <row r="191" spans="2:4">
       <c r="B191" s="1">
         <v>187</v>
       </c>
-      <c r="D191" s="8"/>
-      <c r="Q191" s="8"/>
-    </row>
-    <row r="192" spans="2:17">
+      <c r="D191" s="5"/>
+    </row>
+    <row r="192" spans="2:4">
       <c r="B192" s="1">
         <v>188</v>
       </c>
-      <c r="D192" s="8"/>
-      <c r="Q192" s="8"/>
-    </row>
-    <row r="193" spans="2:17">
+      <c r="D192" s="5"/>
+    </row>
+    <row r="193" spans="2:4">
       <c r="B193" s="1">
         <v>189</v>
       </c>
-      <c r="D193" s="8"/>
-      <c r="Q193" s="8"/>
-    </row>
-    <row r="194" spans="2:17">
+      <c r="D193" s="5"/>
+    </row>
+    <row r="194" spans="2:4">
       <c r="B194" s="1">
         <v>190</v>
       </c>
-      <c r="D194" s="8"/>
-      <c r="Q194" s="8"/>
-    </row>
-    <row r="195" spans="2:17">
+      <c r="D194" s="5"/>
+    </row>
+    <row r="195" spans="2:4">
       <c r="B195" s="1">
         <v>191</v>
       </c>
-      <c r="D195" s="8"/>
-      <c r="Q195" s="8"/>
-    </row>
-    <row r="196" spans="2:17">
+      <c r="D195" s="5"/>
+    </row>
+    <row r="196" spans="2:4">
       <c r="B196" s="1">
         <v>192</v>
       </c>
-      <c r="D196" s="8"/>
-      <c r="Q196" s="8"/>
-    </row>
-    <row r="197" spans="2:17">
+      <c r="D196" s="5"/>
+    </row>
+    <row r="197" spans="2:4">
       <c r="B197" s="1">
         <v>193</v>
       </c>
-      <c r="D197" s="8"/>
-      <c r="Q197" s="8"/>
-    </row>
-    <row r="198" spans="2:17">
+      <c r="D197" s="5"/>
+    </row>
+    <row r="198" spans="2:4">
       <c r="B198" s="1">
         <v>194</v>
       </c>
-      <c r="D198" s="8"/>
-      <c r="Q198" s="8"/>
-    </row>
-    <row r="199" spans="2:17">
+      <c r="D198" s="5"/>
+    </row>
+    <row r="199" spans="2:4">
       <c r="B199" s="1">
         <v>195</v>
       </c>
-      <c r="D199" s="8"/>
-      <c r="Q199" s="8"/>
-    </row>
-    <row r="200" spans="2:17">
+      <c r="D199" s="5"/>
+    </row>
+    <row r="200" spans="2:4">
       <c r="B200" s="1">
         <v>196</v>
       </c>
-      <c r="D200" s="8"/>
-      <c r="Q200" s="8"/>
-    </row>
-    <row r="201" spans="2:17">
+      <c r="D200" s="5"/>
+    </row>
+    <row r="201" spans="2:4">
       <c r="B201" s="1">
         <v>197</v>
       </c>
-      <c r="D201" s="8"/>
-      <c r="Q201" s="8"/>
-    </row>
-    <row r="202" spans="2:17">
+      <c r="D201" s="5"/>
+    </row>
+    <row r="202" spans="2:4">
       <c r="B202" s="1">
         <v>198</v>
       </c>
-      <c r="D202" s="8"/>
-      <c r="Q202" s="8"/>
-    </row>
-    <row r="203" spans="2:17">
+      <c r="D202" s="5"/>
+    </row>
+    <row r="203" spans="2:4">
       <c r="B203" s="1">
         <v>199</v>
       </c>
-      <c r="D203" s="8"/>
-      <c r="Q203" s="8"/>
-    </row>
-    <row r="204" spans="2:17">
+      <c r="D203" s="5"/>
+    </row>
+    <row r="204" spans="2:4">
       <c r="B204" s="1">
         <v>200</v>
       </c>
-      <c r="D204" s="8"/>
-      <c r="Q204" s="8"/>
-    </row>
-    <row r="205" spans="2:17">
+      <c r="D204" s="5"/>
+    </row>
+    <row r="205" spans="2:4">
       <c r="B205" s="1">
         <v>201</v>
       </c>
-      <c r="D205" s="8"/>
-      <c r="Q205" s="8"/>
-    </row>
-    <row r="206" spans="2:17">
+      <c r="D205" s="5"/>
+    </row>
+    <row r="206" spans="2:4">
       <c r="B206" s="1">
         <v>202</v>
       </c>
-      <c r="D206" s="8"/>
-      <c r="Q206" s="8"/>
-    </row>
-    <row r="207" spans="2:17">
+      <c r="D206" s="5"/>
+    </row>
+    <row r="207" spans="2:4">
       <c r="B207" s="1">
         <v>203</v>
       </c>
-      <c r="D207" s="8"/>
-      <c r="Q207" s="8"/>
-    </row>
-    <row r="208" spans="2:17">
+      <c r="D207" s="5"/>
+    </row>
+    <row r="208" spans="2:4">
       <c r="B208" s="1">
         <v>204</v>
       </c>
-      <c r="D208" s="8"/>
-      <c r="Q208" s="8"/>
-    </row>
-    <row r="209" spans="2:17">
+      <c r="D208" s="5"/>
+    </row>
+    <row r="209" spans="2:4">
       <c r="B209" s="1">
         <v>205</v>
       </c>
-      <c r="D209" s="8"/>
-      <c r="Q209" s="8"/>
-    </row>
-    <row r="210" spans="2:17">
+      <c r="D209" s="5"/>
+    </row>
+    <row r="210" spans="2:4">
       <c r="B210" s="1">
         <v>206</v>
       </c>
-      <c r="D210" s="8"/>
-      <c r="Q210" s="8"/>
-    </row>
-    <row r="211" spans="2:17">
+      <c r="D210" s="5"/>
+    </row>
+    <row r="211" spans="2:4">
       <c r="B211" s="1">
         <v>207</v>
       </c>
-      <c r="D211" s="8"/>
-      <c r="Q211" s="8"/>
-    </row>
-    <row r="212" spans="2:17">
+      <c r="D211" s="5"/>
+    </row>
+    <row r="212" spans="2:4">
       <c r="B212" s="1">
         <v>208</v>
       </c>
-      <c r="D212" s="8"/>
-      <c r="Q212" s="8"/>
-    </row>
-    <row r="213" spans="2:17">
+      <c r="D212" s="5"/>
+    </row>
+    <row r="213" spans="2:4">
       <c r="B213" s="1">
         <v>209</v>
       </c>
-      <c r="D213" s="8"/>
-      <c r="Q213" s="8"/>
-    </row>
-    <row r="214" spans="2:17">
+      <c r="D213" s="5"/>
+    </row>
+    <row r="214" spans="2:4">
       <c r="B214" s="1">
         <v>210</v>
       </c>
-      <c r="D214" s="8"/>
-      <c r="Q214" s="8"/>
-    </row>
-    <row r="215" spans="2:17">
+      <c r="D214" s="5"/>
+    </row>
+    <row r="215" spans="2:4">
       <c r="B215" s="1">
         <v>211</v>
       </c>
-      <c r="D215" s="8"/>
-      <c r="Q215" s="8"/>
-    </row>
-    <row r="216" spans="2:17">
+      <c r="D215" s="5"/>
+    </row>
+    <row r="216" spans="2:4">
       <c r="B216" s="1">
         <v>212</v>
       </c>
-      <c r="D216" s="8"/>
-      <c r="Q216" s="8"/>
-    </row>
-    <row r="217" spans="2:17">
+      <c r="D216" s="5"/>
+    </row>
+    <row r="217" spans="2:4">
       <c r="B217" s="1">
         <v>213</v>
       </c>
-      <c r="D217" s="8"/>
-      <c r="Q217" s="8"/>
-    </row>
-    <row r="218" spans="2:17">
+      <c r="D217" s="5"/>
+    </row>
+    <row r="218" spans="2:4">
       <c r="B218" s="1">
         <v>214</v>
       </c>
-      <c r="D218" s="8"/>
-      <c r="Q218" s="8"/>
-    </row>
-    <row r="219" spans="2:17">
+      <c r="D218" s="5"/>
+    </row>
+    <row r="219" spans="2:4">
       <c r="B219" s="1">
         <v>215</v>
       </c>
-      <c r="D219" s="8"/>
-      <c r="Q219" s="8"/>
-    </row>
-    <row r="220" spans="2:17">
+      <c r="D219" s="5"/>
+    </row>
+    <row r="220" spans="2:4">
       <c r="B220" s="1">
         <v>216</v>
       </c>
-      <c r="D220" s="8"/>
-      <c r="Q220" s="8"/>
-    </row>
-    <row r="221" spans="2:17">
+      <c r="D220" s="5"/>
+    </row>
+    <row r="221" spans="2:4">
       <c r="B221" s="1">
         <v>217</v>
       </c>
-      <c r="D221" s="8"/>
-      <c r="Q221" s="8"/>
-    </row>
-    <row r="222" spans="2:17">
+      <c r="D221" s="5"/>
+    </row>
+    <row r="222" spans="2:4">
       <c r="B222" s="1">
         <v>218</v>
       </c>
-      <c r="D222" s="8"/>
-      <c r="Q222" s="8"/>
-    </row>
-    <row r="223" spans="2:17">
+      <c r="D222" s="5"/>
+    </row>
+    <row r="223" spans="2:4">
       <c r="B223" s="1">
         <v>219</v>
       </c>
-      <c r="D223" s="8"/>
-      <c r="Q223" s="8"/>
-    </row>
-    <row r="224" spans="2:17">
+      <c r="D223" s="5"/>
+    </row>
+    <row r="224" spans="2:4">
       <c r="B224" s="1">
         <v>220</v>
       </c>
-      <c r="D224" s="8"/>
-      <c r="Q224" s="8"/>
-    </row>
-    <row r="225" spans="2:17">
+      <c r="D224" s="5"/>
+    </row>
+    <row r="225" spans="2:4">
       <c r="B225" s="1">
         <v>221</v>
       </c>
-      <c r="D225" s="8"/>
-      <c r="Q225" s="8"/>
-    </row>
-    <row r="226" spans="2:17">
+      <c r="D225" s="5"/>
+    </row>
+    <row r="226" spans="2:4">
       <c r="B226" s="1">
         <v>222</v>
       </c>
-      <c r="D226" s="8"/>
-      <c r="Q226" s="8"/>
-    </row>
-    <row r="227" spans="2:17">
+      <c r="D226" s="5"/>
+    </row>
+    <row r="227" spans="2:4">
       <c r="B227" s="1">
         <v>223</v>
       </c>
-      <c r="D227" s="8"/>
-      <c r="Q227" s="8"/>
-    </row>
-    <row r="228" spans="2:17">
+      <c r="D227" s="5"/>
+    </row>
+    <row r="228" spans="2:4">
       <c r="B228" s="1">
         <v>224</v>
       </c>
-      <c r="D228" s="8"/>
-      <c r="Q228" s="8"/>
-    </row>
-    <row r="229" spans="2:17">
+      <c r="D228" s="5"/>
+    </row>
+    <row r="229" spans="2:4">
       <c r="B229" s="1">
         <v>225</v>
       </c>
-      <c r="D229" s="8"/>
-      <c r="Q229" s="8"/>
-    </row>
-    <row r="230" spans="2:17">
+      <c r="D229" s="5"/>
+    </row>
+    <row r="230" spans="2:4">
       <c r="B230" s="1">
         <v>226</v>
       </c>
-      <c r="D230" s="8"/>
-      <c r="Q230" s="8"/>
-    </row>
-    <row r="231" spans="2:17">
+      <c r="D230" s="5"/>
+    </row>
+    <row r="231" spans="2:4">
       <c r="B231" s="1">
         <v>227</v>
       </c>
-      <c r="D231" s="8"/>
-      <c r="Q231" s="8"/>
-    </row>
-    <row r="232" spans="2:17">
+      <c r="D231" s="5"/>
+    </row>
+    <row r="232" spans="2:4">
       <c r="B232" s="1">
         <v>228</v>
       </c>
-      <c r="D232" s="8"/>
-      <c r="Q232" s="8"/>
-    </row>
-    <row r="233" spans="2:17">
+      <c r="D232" s="5"/>
+    </row>
+    <row r="233" spans="2:4">
       <c r="B233" s="1">
         <v>229</v>
       </c>
-      <c r="D233" s="8"/>
-      <c r="Q233" s="8"/>
-    </row>
-    <row r="234" spans="2:17">
+      <c r="D233" s="5"/>
+    </row>
+    <row r="234" spans="2:4">
       <c r="B234" s="1">
         <v>230</v>
       </c>
-      <c r="D234" s="8"/>
-      <c r="Q234" s="8"/>
-    </row>
-    <row r="235" spans="2:17">
+      <c r="D234" s="5"/>
+    </row>
+    <row r="235" spans="2:4">
       <c r="B235" s="1">
         <v>231</v>
       </c>
-      <c r="D235" s="8"/>
-      <c r="Q235" s="8"/>
-    </row>
-    <row r="236" spans="2:17">
+      <c r="D235" s="5"/>
+    </row>
+    <row r="236" spans="2:4">
       <c r="B236" s="1">
         <v>232</v>
       </c>
-      <c r="D236" s="8"/>
-      <c r="Q236" s="8"/>
-    </row>
-    <row r="237" spans="2:17">
+      <c r="D236" s="5"/>
+    </row>
+    <row r="237" spans="2:4">
       <c r="B237" s="1">
         <v>233</v>
       </c>
-      <c r="D237" s="8"/>
-      <c r="Q237" s="8"/>
-    </row>
-    <row r="238" spans="2:17">
+      <c r="D237" s="5"/>
+    </row>
+    <row r="238" spans="2:4">
       <c r="B238" s="1">
         <v>234</v>
       </c>
-      <c r="D238" s="8"/>
-      <c r="Q238" s="8"/>
-    </row>
-    <row r="239" spans="2:17">
+      <c r="D238" s="5"/>
+    </row>
+    <row r="239" spans="2:4">
       <c r="B239" s="1">
         <v>235</v>
       </c>
-      <c r="D239" s="8"/>
-      <c r="Q239" s="8"/>
-    </row>
-    <row r="240" spans="2:17">
+      <c r="D239" s="5"/>
+    </row>
+    <row r="240" spans="2:4">
       <c r="B240" s="1">
         <v>236</v>
       </c>
-      <c r="D240" s="8"/>
-      <c r="Q240" s="8"/>
-    </row>
-    <row r="241" spans="2:17">
+      <c r="D240" s="5"/>
+    </row>
+    <row r="241" spans="2:4">
       <c r="B241" s="1">
         <v>237</v>
       </c>
-      <c r="D241" s="8"/>
-      <c r="Q241" s="8"/>
-    </row>
-    <row r="242" spans="2:17">
+      <c r="D241" s="5"/>
+    </row>
+    <row r="242" spans="2:4">
       <c r="B242" s="1">
         <v>238</v>
       </c>
-      <c r="D242" s="8"/>
-      <c r="Q242" s="8"/>
-    </row>
-    <row r="243" spans="2:17">
+      <c r="D242" s="5"/>
+    </row>
+    <row r="243" spans="2:4">
       <c r="B243" s="1">
         <v>239</v>
       </c>
-      <c r="D243" s="8"/>
-      <c r="Q243" s="8"/>
-    </row>
-    <row r="244" spans="2:17">
+      <c r="D243" s="5"/>
+    </row>
+    <row r="244" spans="2:4">
       <c r="B244" s="1">
         <v>240</v>
       </c>
-      <c r="D244" s="8"/>
-      <c r="Q244" s="8"/>
-    </row>
-    <row r="245" spans="2:17">
+      <c r="D244" s="5"/>
+    </row>
+    <row r="245" spans="2:4">
       <c r="B245" s="1">
         <v>241</v>
       </c>
-      <c r="D245" s="8"/>
-      <c r="Q245" s="8"/>
-    </row>
-    <row r="246" spans="2:17">
+      <c r="D245" s="5"/>
+    </row>
+    <row r="246" spans="2:4">
       <c r="B246" s="1">
         <v>242</v>
       </c>
-      <c r="D246" s="8"/>
-      <c r="Q246" s="8"/>
-    </row>
-    <row r="247" spans="2:17">
+      <c r="D246" s="5"/>
+    </row>
+    <row r="247" spans="2:4">
       <c r="B247" s="1">
         <v>243</v>
       </c>
-      <c r="D247" s="8"/>
-      <c r="Q247" s="8"/>
-    </row>
-    <row r="248" spans="2:17">
+      <c r="D247" s="5"/>
+    </row>
+    <row r="248" spans="2:4">
       <c r="B248" s="1">
         <v>244</v>
       </c>
-      <c r="D248" s="8"/>
-      <c r="Q248" s="8"/>
-    </row>
-    <row r="249" spans="2:17">
+      <c r="D248" s="5"/>
+    </row>
+    <row r="249" spans="2:4">
       <c r="B249" s="1">
         <v>245</v>
       </c>
-      <c r="D249" s="8"/>
-      <c r="Q249" s="8"/>
-    </row>
-    <row r="250" spans="2:17">
+      <c r="D249" s="5"/>
+    </row>
+    <row r="250" spans="2:4">
       <c r="B250" s="1">
         <v>246</v>
       </c>
-      <c r="D250" s="8"/>
-      <c r="Q250" s="8"/>
+      <c r="D250" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="P3:Q3"/>
     <mergeCell ref="S3:T3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
-    <mergeCell ref="D3:E3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="F3:F4"/>
@@ -2750,22 +2518,27 @@
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:S250">
+  <conditionalFormatting sqref="B5:T250">
     <cfRule type="expression" priority="6" stopIfTrue="1">
-      <formula>$Q5=""</formula>
+      <formula>$P5=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="7">
-      <formula>$Q5&lt;TODAY()</formula>
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>$P5&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8">
-      <formula>OR($Q5-TODAY()=0, $Q5-TODAY()=1)</formula>
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>OR($P5-TODAY()=0, $P5-TODAY()=1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="9">
-      <formula>AND($Q5-TODAY()&gt;=0, $Q5-TODAY()&lt;=3)</formula>
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND($P5-TODAY()&gt;=0, $P5-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
-      <formula>AND($Q5-TODAY()&gt;=4, $Q5-TODAY()&lt;=7)</formula>
+    <cfRule type="expression" dxfId="4" priority="10">
+      <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2787,131 +2560,131 @@
   <sheetData>
     <row r="3" spans="2:10" ht="15" customHeight="1"/>
     <row r="4" spans="2:10" ht="15" customHeight="1">
-      <c r="B4" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="D4" s="11" t="s">
         <v>39</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
         <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="2:10">
       <c r="B6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:10">
       <c r="B7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="B8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="2:10">
       <c r="B9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="2:10">
       <c r="D10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="2:10">
       <c r="F11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="2:10">
       <c r="J12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="2:10">
       <c r="J13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15D014C-F0C1-4195-8636-6904610B46D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB091A07-861C-4969-94C1-E395357F18B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,124 +77,124 @@
     <t>LIMITE*</t>
   </si>
   <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>HORA</t>
+  </si>
+  <si>
+    <t>CCR ENG&amp;CONST</t>
+  </si>
+  <si>
+    <t>Chamada</t>
+  </si>
+  <si>
+    <t>Vila do Conde</t>
+  </si>
+  <si>
+    <t>Gabinete / Estudos</t>
+  </si>
+  <si>
+    <t>Diária</t>
+  </si>
+  <si>
+    <t>GRAU-ON</t>
+  </si>
+  <si>
+    <t>Lev. Topográfico</t>
+  </si>
+  <si>
+    <t>CCR-INVEST</t>
+  </si>
+  <si>
+    <t>Póvoa de Varzim</t>
+  </si>
+  <si>
+    <t>GROWNOR</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Maia</t>
+  </si>
+  <si>
+    <t>Guimarães</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>VIA</t>
+  </si>
+  <si>
+    <t>CONCELHO</t>
+  </si>
+  <si>
+    <t>FREQUÊNCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE TRABALHO</t>
+  </si>
+  <si>
+    <t>EMPRESA</t>
+  </si>
+  <si>
+    <t>SMS</t>
+  </si>
+  <si>
+    <t>Semanal</t>
+  </si>
+  <si>
+    <t>Monitorização</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Mensal</t>
+  </si>
+  <si>
+    <t>Trimestral</t>
+  </si>
+  <si>
+    <t>WEST-VIEW</t>
+  </si>
+  <si>
+    <t>Whatsapp</t>
+  </si>
+  <si>
+    <t>Semestral</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Anual</t>
+  </si>
+  <si>
+    <t>FERCAYO</t>
+  </si>
+  <si>
+    <t>Continua</t>
+  </si>
+  <si>
+    <t>DECIBOLT</t>
+  </si>
+  <si>
+    <t>INTERNO</t>
+  </si>
+  <si>
+    <t>EXTERNO</t>
+  </si>
+  <si>
     <t>ESTADO</t>
   </si>
   <si>
     <t>CONCLUSÃO</t>
-  </si>
-  <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>HORA</t>
-  </si>
-  <si>
-    <t>CCR-INVEST</t>
-  </si>
-  <si>
-    <t>Chamada</t>
-  </si>
-  <si>
-    <t>Monitorização</t>
-  </si>
-  <si>
-    <t>Póvoa de Varzim</t>
-  </si>
-  <si>
-    <t>Lev. Topográfico</t>
-  </si>
-  <si>
-    <t>Diária</t>
-  </si>
-  <si>
-    <t>GROWNOR</t>
-  </si>
-  <si>
-    <t>WEST-VIEW</t>
-  </si>
-  <si>
-    <t>CCR ENG&amp;CONST</t>
-  </si>
-  <si>
-    <t>Guimarães</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Vila do Conde</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>Gabinete / Estudos</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Maia</t>
-  </si>
-  <si>
-    <t>VIA</t>
-  </si>
-  <si>
-    <t>CONCELHO</t>
-  </si>
-  <si>
-    <t>FREQUÊNCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE TRABALHO</t>
-  </si>
-  <si>
-    <t>EMPRESA</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>Semanal</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Mensal</t>
-  </si>
-  <si>
-    <t>Trimestral</t>
-  </si>
-  <si>
-    <t>Whatsapp</t>
-  </si>
-  <si>
-    <t>Semestral</t>
-  </si>
-  <si>
-    <t>GRAU-ON</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Anual</t>
-  </si>
-  <si>
-    <t>FERCAYO</t>
-  </si>
-  <si>
-    <t>Continua</t>
-  </si>
-  <si>
-    <t>DECIBOLT</t>
-  </si>
-  <si>
-    <t>INTERNO</t>
-  </si>
-  <si>
-    <t>EXTERNO</t>
   </si>
 </sst>
 </file>
@@ -302,6 +302,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -327,42 +342,33 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -378,102 +384,52 @@
     <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -817,7 +773,7 @@
   <cols>
     <col min="1" max="2" width="9.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="25" customWidth="1"/>
     <col min="5" max="5" width="7.109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" style="1" customWidth="1"/>
     <col min="7" max="8" width="20.33203125" style="1" customWidth="1"/>
@@ -828,1684 +784,1400 @@
     <col min="13" max="14" width="45.33203125" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.109375" style="1" customWidth="1"/>
     <col min="16" max="16" width="20.77734375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.109375" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" style="3" customWidth="1"/>
-    <col min="19" max="19" width="12.21875" style="5" customWidth="1"/>
-    <col min="20" max="20" width="16.88671875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="12.109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.21875" style="7" customWidth="1"/>
+    <col min="20" max="20" width="16.88671875" style="3" customWidth="1"/>
     <col min="21" max="21" width="100" style="1" customWidth="1"/>
     <col min="22" max="22" width="9.109375" style="1" customWidth="1"/>
     <col min="23" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="15" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="17" t="s">
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="18" t="s">
+      <c r="J1" s="21"/>
+      <c r="K1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="18"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="19"/>
-      <c r="T2" s="19"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3" spans="1:20" ht="19.8" customHeight="1">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="L3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="M3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="N3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="20" t="s">
+      <c r="O3" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="P3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="23" t="s">
+      <c r="Q3" s="18"/>
+      <c r="R3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3" s="16"/>
+    </row>
+    <row r="4" spans="1:20" ht="32.4" customHeight="1">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="S3" s="20" t="s">
+      <c r="E4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="T3" s="20"/>
-    </row>
-    <row r="4" spans="1:20" ht="32.4" customHeight="1">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q4" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="T4" s="23" t="s">
-        <v>21</v>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" s="6"/>
+      <c r="S4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T4" s="15" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="P5" s="5"/>
-      <c r="R5" s="6"/>
+      <c r="R5" s="8"/>
     </row>
     <row r="6" spans="1:20">
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="P6" s="5"/>
     </row>
     <row r="7" spans="1:20">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="P7" s="5"/>
-      <c r="R7" s="6"/>
+      <c r="R7" s="8"/>
     </row>
     <row r="8" spans="1:20">
       <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:20">
       <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:20">
       <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:20">
       <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:20">
       <c r="B12" s="1">
         <v>8</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:20">
       <c r="B13" s="1">
         <v>9</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:20">
       <c r="B14" s="1">
         <v>10</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1">
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="5"/>
-      <c r="P15" s="5"/>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="5"/>
-      <c r="P16" s="5"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" spans="2:19">
       <c r="B17" s="1">
         <v>13</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="P17" s="5"/>
     </row>
     <row r="18" spans="2:19">
       <c r="B18" s="1">
         <v>14</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="P18" s="5"/>
     </row>
     <row r="19" spans="2:19">
       <c r="B19" s="1">
         <v>15</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="P19" s="5"/>
     </row>
     <row r="20" spans="2:19">
       <c r="B20" s="1">
         <v>16</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="P20" s="5"/>
     </row>
     <row r="21" spans="2:19">
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="27"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="11"/>
     </row>
     <row r="22" spans="2:19">
       <c r="B22" s="1">
         <v>18</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="P22" s="5"/>
     </row>
     <row r="23" spans="2:19">
       <c r="B23" s="1">
         <v>19</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="P23" s="5"/>
     </row>
     <row r="24" spans="2:19">
       <c r="B24" s="1">
         <v>20</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="P24" s="5"/>
     </row>
     <row r="25" spans="2:19">
       <c r="B25" s="1">
         <v>21</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="P25" s="5"/>
     </row>
     <row r="26" spans="2:19">
       <c r="B26" s="1">
         <v>22</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="P26" s="5"/>
     </row>
     <row r="27" spans="2:19">
       <c r="B27" s="1">
         <v>23</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="P27" s="5"/>
     </row>
     <row r="28" spans="2:19">
       <c r="B28" s="1">
         <v>24</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="P28" s="5"/>
     </row>
     <row r="29" spans="2:19">
       <c r="B29" s="1">
         <v>25</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="P29" s="5"/>
     </row>
     <row r="30" spans="2:19">
       <c r="B30" s="1">
         <v>26</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="P30" s="5"/>
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="1">
         <v>27</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="P31" s="5"/>
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="1">
         <v>28</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="P32" s="5"/>
-    </row>
-    <row r="33" spans="2:4">
+    </row>
+    <row r="33" spans="2:2">
       <c r="B33" s="1">
         <v>29</v>
       </c>
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="2:4">
+    </row>
+    <row r="34" spans="2:2">
       <c r="B34" s="1">
         <v>30</v>
       </c>
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="2:4">
+    </row>
+    <row r="35" spans="2:2">
       <c r="B35" s="1">
         <v>31</v>
       </c>
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="2:4">
+    </row>
+    <row r="36" spans="2:2">
       <c r="B36" s="1">
         <v>32</v>
       </c>
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="2:4">
+    </row>
+    <row r="37" spans="2:2">
       <c r="B37" s="1">
         <v>33</v>
       </c>
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="2:4">
+    </row>
+    <row r="38" spans="2:2">
       <c r="B38" s="1">
         <v>34</v>
       </c>
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="2:4">
+    </row>
+    <row r="39" spans="2:2">
       <c r="B39" s="1">
         <v>35</v>
       </c>
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" spans="2:4">
+    </row>
+    <row r="40" spans="2:2">
       <c r="B40" s="1">
         <v>36</v>
       </c>
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="2:4">
+    </row>
+    <row r="41" spans="2:2">
       <c r="B41" s="1">
         <v>37</v>
       </c>
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="2:4">
+    </row>
+    <row r="42" spans="2:2">
       <c r="B42" s="1">
         <v>38</v>
       </c>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="2:4">
+    </row>
+    <row r="43" spans="2:2">
       <c r="B43" s="1">
         <v>39</v>
       </c>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="2:4">
+    </row>
+    <row r="44" spans="2:2">
       <c r="B44" s="1">
         <v>40</v>
       </c>
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="2:4">
+    </row>
+    <row r="45" spans="2:2">
       <c r="B45" s="1">
         <v>41</v>
       </c>
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" spans="2:4">
+    </row>
+    <row r="46" spans="2:2">
       <c r="B46" s="1">
         <v>42</v>
       </c>
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="2:4">
+    </row>
+    <row r="47" spans="2:2">
       <c r="B47" s="1">
         <v>43</v>
       </c>
-      <c r="D47" s="5"/>
-    </row>
-    <row r="48" spans="2:4">
+    </row>
+    <row r="48" spans="2:2">
       <c r="B48" s="1">
         <v>44</v>
       </c>
-      <c r="D48" s="5"/>
-    </row>
-    <row r="49" spans="2:4">
+    </row>
+    <row r="49" spans="2:2">
       <c r="B49" s="1">
         <v>45</v>
       </c>
-      <c r="D49" s="5"/>
-    </row>
-    <row r="50" spans="2:4">
+    </row>
+    <row r="50" spans="2:2">
       <c r="B50" s="1">
         <v>46</v>
       </c>
-      <c r="D50" s="5"/>
-    </row>
-    <row r="51" spans="2:4">
+    </row>
+    <row r="51" spans="2:2">
       <c r="B51" s="1">
         <v>47</v>
       </c>
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="2:4">
+    </row>
+    <row r="52" spans="2:2">
       <c r="B52" s="1">
         <v>48</v>
       </c>
-      <c r="D52" s="5"/>
-    </row>
-    <row r="53" spans="2:4">
+    </row>
+    <row r="53" spans="2:2">
       <c r="B53" s="1">
         <v>49</v>
       </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="2:4">
+    </row>
+    <row r="54" spans="2:2">
       <c r="B54" s="1">
         <v>50</v>
       </c>
-      <c r="D54" s="5"/>
-    </row>
-    <row r="55" spans="2:4">
+    </row>
+    <row r="55" spans="2:2">
       <c r="B55" s="1">
         <v>51</v>
       </c>
-      <c r="D55" s="5"/>
-    </row>
-    <row r="56" spans="2:4">
+    </row>
+    <row r="56" spans="2:2">
       <c r="B56" s="1">
         <v>52</v>
       </c>
-      <c r="D56" s="5"/>
-    </row>
-    <row r="57" spans="2:4">
+    </row>
+    <row r="57" spans="2:2">
       <c r="B57" s="1">
         <v>53</v>
       </c>
-      <c r="D57" s="5"/>
-    </row>
-    <row r="58" spans="2:4">
+    </row>
+    <row r="58" spans="2:2">
       <c r="B58" s="1">
         <v>54</v>
       </c>
-      <c r="D58" s="5"/>
-    </row>
-    <row r="59" spans="2:4">
+    </row>
+    <row r="59" spans="2:2">
       <c r="B59" s="1">
         <v>55</v>
       </c>
-      <c r="D59" s="5"/>
-    </row>
-    <row r="60" spans="2:4">
+    </row>
+    <row r="60" spans="2:2">
       <c r="B60" s="1">
         <v>56</v>
       </c>
-      <c r="D60" s="5"/>
-    </row>
-    <row r="61" spans="2:4">
+    </row>
+    <row r="61" spans="2:2">
       <c r="B61" s="1">
         <v>57</v>
       </c>
-      <c r="D61" s="5"/>
-    </row>
-    <row r="62" spans="2:4">
+    </row>
+    <row r="62" spans="2:2">
       <c r="B62" s="1">
         <v>58</v>
       </c>
-      <c r="D62" s="5"/>
-    </row>
-    <row r="63" spans="2:4">
+    </row>
+    <row r="63" spans="2:2">
       <c r="B63" s="1">
         <v>59</v>
       </c>
-      <c r="D63" s="5"/>
-    </row>
-    <row r="64" spans="2:4">
+    </row>
+    <row r="64" spans="2:2">
       <c r="B64" s="1">
         <v>60</v>
       </c>
-      <c r="D64" s="5"/>
-    </row>
-    <row r="65" spans="2:4">
+    </row>
+    <row r="65" spans="2:2">
       <c r="B65" s="1">
         <v>61</v>
       </c>
-      <c r="D65" s="5"/>
-    </row>
-    <row r="66" spans="2:4">
+    </row>
+    <row r="66" spans="2:2">
       <c r="B66" s="1">
         <v>62</v>
       </c>
-      <c r="D66" s="5"/>
-    </row>
-    <row r="67" spans="2:4">
+    </row>
+    <row r="67" spans="2:2">
       <c r="B67" s="1">
         <v>63</v>
       </c>
-      <c r="D67" s="5"/>
-    </row>
-    <row r="68" spans="2:4">
+    </row>
+    <row r="68" spans="2:2">
       <c r="B68" s="1">
         <v>64</v>
       </c>
-      <c r="D68" s="5"/>
-    </row>
-    <row r="69" spans="2:4">
+    </row>
+    <row r="69" spans="2:2">
       <c r="B69" s="1">
         <v>65</v>
       </c>
-      <c r="D69" s="5"/>
-    </row>
-    <row r="70" spans="2:4">
+    </row>
+    <row r="70" spans="2:2">
       <c r="B70" s="1">
         <v>66</v>
       </c>
-      <c r="D70" s="5"/>
-    </row>
-    <row r="71" spans="2:4">
+    </row>
+    <row r="71" spans="2:2">
       <c r="B71" s="1">
         <v>67</v>
       </c>
-      <c r="D71" s="5"/>
-    </row>
-    <row r="72" spans="2:4">
+    </row>
+    <row r="72" spans="2:2">
       <c r="B72" s="1">
         <v>68</v>
       </c>
-      <c r="D72" s="5"/>
-    </row>
-    <row r="73" spans="2:4">
+    </row>
+    <row r="73" spans="2:2">
       <c r="B73" s="1">
         <v>69</v>
       </c>
-      <c r="D73" s="5"/>
-    </row>
-    <row r="74" spans="2:4">
+    </row>
+    <row r="74" spans="2:2">
       <c r="B74" s="1">
         <v>70</v>
       </c>
-      <c r="D74" s="5"/>
-    </row>
-    <row r="75" spans="2:4">
+    </row>
+    <row r="75" spans="2:2">
       <c r="B75" s="1">
         <v>71</v>
       </c>
-      <c r="D75" s="5"/>
-    </row>
-    <row r="76" spans="2:4">
+    </row>
+    <row r="76" spans="2:2">
       <c r="B76" s="1">
         <v>72</v>
       </c>
-      <c r="D76" s="5"/>
-    </row>
-    <row r="77" spans="2:4">
+    </row>
+    <row r="77" spans="2:2">
       <c r="B77" s="1">
         <v>73</v>
       </c>
-      <c r="D77" s="5"/>
-    </row>
-    <row r="78" spans="2:4">
+    </row>
+    <row r="78" spans="2:2">
       <c r="B78" s="1">
         <v>74</v>
       </c>
-      <c r="D78" s="5"/>
-    </row>
-    <row r="79" spans="2:4">
+    </row>
+    <row r="79" spans="2:2">
       <c r="B79" s="1">
         <v>75</v>
       </c>
-      <c r="D79" s="5"/>
-    </row>
-    <row r="80" spans="2:4">
+    </row>
+    <row r="80" spans="2:2">
       <c r="B80" s="1">
         <v>76</v>
       </c>
-      <c r="D80" s="5"/>
-    </row>
-    <row r="81" spans="2:4">
+    </row>
+    <row r="81" spans="2:2">
       <c r="B81" s="1">
         <v>77</v>
       </c>
-      <c r="D81" s="5"/>
-    </row>
-    <row r="82" spans="2:4">
+    </row>
+    <row r="82" spans="2:2">
       <c r="B82" s="1">
         <v>78</v>
       </c>
-      <c r="D82" s="5"/>
-    </row>
-    <row r="83" spans="2:4">
+    </row>
+    <row r="83" spans="2:2">
       <c r="B83" s="1">
         <v>79</v>
       </c>
-      <c r="D83" s="5"/>
-    </row>
-    <row r="84" spans="2:4">
+    </row>
+    <row r="84" spans="2:2">
       <c r="B84" s="1">
         <v>80</v>
       </c>
-      <c r="D84" s="5"/>
-    </row>
-    <row r="85" spans="2:4">
+    </row>
+    <row r="85" spans="2:2">
       <c r="B85" s="1">
         <v>81</v>
       </c>
-      <c r="D85" s="5"/>
-    </row>
-    <row r="86" spans="2:4">
+    </row>
+    <row r="86" spans="2:2">
       <c r="B86" s="1">
         <v>82</v>
       </c>
-      <c r="D86" s="5"/>
-    </row>
-    <row r="87" spans="2:4">
+    </row>
+    <row r="87" spans="2:2">
       <c r="B87" s="1">
         <v>83</v>
       </c>
-      <c r="D87" s="5"/>
-    </row>
-    <row r="88" spans="2:4">
+    </row>
+    <row r="88" spans="2:2">
       <c r="B88" s="1">
         <v>84</v>
       </c>
-      <c r="D88" s="5"/>
-    </row>
-    <row r="89" spans="2:4">
+    </row>
+    <row r="89" spans="2:2">
       <c r="B89" s="1">
         <v>85</v>
       </c>
-      <c r="D89" s="5"/>
-    </row>
-    <row r="90" spans="2:4">
+    </row>
+    <row r="90" spans="2:2">
       <c r="B90" s="1">
         <v>86</v>
       </c>
-      <c r="D90" s="5"/>
-    </row>
-    <row r="91" spans="2:4">
+    </row>
+    <row r="91" spans="2:2">
       <c r="B91" s="1">
         <v>87</v>
       </c>
-      <c r="D91" s="5"/>
-    </row>
-    <row r="92" spans="2:4">
+    </row>
+    <row r="92" spans="2:2">
       <c r="B92" s="1">
         <v>88</v>
       </c>
-      <c r="D92" s="5"/>
-    </row>
-    <row r="93" spans="2:4">
+    </row>
+    <row r="93" spans="2:2">
       <c r="B93" s="1">
         <v>89</v>
       </c>
-      <c r="D93" s="5"/>
-    </row>
-    <row r="94" spans="2:4">
+    </row>
+    <row r="94" spans="2:2">
       <c r="B94" s="1">
         <v>90</v>
       </c>
-      <c r="D94" s="5"/>
-    </row>
-    <row r="95" spans="2:4">
+    </row>
+    <row r="95" spans="2:2">
       <c r="B95" s="1">
         <v>91</v>
       </c>
-      <c r="D95" s="5"/>
-    </row>
-    <row r="96" spans="2:4">
+    </row>
+    <row r="96" spans="2:2">
       <c r="B96" s="1">
         <v>92</v>
       </c>
-      <c r="D96" s="5"/>
-    </row>
-    <row r="97" spans="2:4">
+    </row>
+    <row r="97" spans="2:2">
       <c r="B97" s="1">
         <v>93</v>
       </c>
-      <c r="D97" s="5"/>
-    </row>
-    <row r="98" spans="2:4">
+    </row>
+    <row r="98" spans="2:2">
       <c r="B98" s="1">
         <v>94</v>
       </c>
-      <c r="D98" s="5"/>
-    </row>
-    <row r="99" spans="2:4">
+    </row>
+    <row r="99" spans="2:2">
       <c r="B99" s="1">
         <v>95</v>
       </c>
-      <c r="D99" s="5"/>
-    </row>
-    <row r="100" spans="2:4">
+    </row>
+    <row r="100" spans="2:2">
       <c r="B100" s="1">
         <v>96</v>
       </c>
-      <c r="D100" s="5"/>
-    </row>
-    <row r="101" spans="2:4">
+    </row>
+    <row r="101" spans="2:2">
       <c r="B101" s="1">
         <v>97</v>
       </c>
-      <c r="D101" s="5"/>
-    </row>
-    <row r="102" spans="2:4">
+    </row>
+    <row r="102" spans="2:2">
       <c r="B102" s="1">
         <v>98</v>
       </c>
-      <c r="D102" s="5"/>
-    </row>
-    <row r="103" spans="2:4">
+    </row>
+    <row r="103" spans="2:2">
       <c r="B103" s="1">
         <v>99</v>
       </c>
-      <c r="D103" s="5"/>
-    </row>
-    <row r="104" spans="2:4">
+    </row>
+    <row r="104" spans="2:2">
       <c r="B104" s="1">
         <v>100</v>
       </c>
-      <c r="D104" s="5"/>
-    </row>
-    <row r="105" spans="2:4">
+    </row>
+    <row r="105" spans="2:2">
       <c r="B105" s="1">
         <v>101</v>
       </c>
-      <c r="D105" s="5"/>
-    </row>
-    <row r="106" spans="2:4">
+    </row>
+    <row r="106" spans="2:2">
       <c r="B106" s="1">
         <v>102</v>
       </c>
-      <c r="D106" s="5"/>
-    </row>
-    <row r="107" spans="2:4">
+    </row>
+    <row r="107" spans="2:2">
       <c r="B107" s="1">
         <v>103</v>
       </c>
-      <c r="D107" s="5"/>
-    </row>
-    <row r="108" spans="2:4">
+    </row>
+    <row r="108" spans="2:2">
       <c r="B108" s="1">
         <v>104</v>
       </c>
-      <c r="D108" s="5"/>
-    </row>
-    <row r="109" spans="2:4">
+    </row>
+    <row r="109" spans="2:2">
       <c r="B109" s="1">
         <v>105</v>
       </c>
-      <c r="D109" s="5"/>
-    </row>
-    <row r="110" spans="2:4">
+    </row>
+    <row r="110" spans="2:2">
       <c r="B110" s="1">
         <v>106</v>
       </c>
-      <c r="D110" s="5"/>
-    </row>
-    <row r="111" spans="2:4">
+    </row>
+    <row r="111" spans="2:2">
       <c r="B111" s="1">
         <v>107</v>
       </c>
-      <c r="D111" s="5"/>
-    </row>
-    <row r="112" spans="2:4">
+    </row>
+    <row r="112" spans="2:2">
       <c r="B112" s="1">
         <v>108</v>
       </c>
-      <c r="D112" s="5"/>
-    </row>
-    <row r="113" spans="2:4">
+    </row>
+    <row r="113" spans="2:2">
       <c r="B113" s="1">
         <v>109</v>
       </c>
-      <c r="D113" s="5"/>
-    </row>
-    <row r="114" spans="2:4">
+    </row>
+    <row r="114" spans="2:2">
       <c r="B114" s="1">
         <v>110</v>
       </c>
-      <c r="D114" s="5"/>
-    </row>
-    <row r="115" spans="2:4">
+    </row>
+    <row r="115" spans="2:2">
       <c r="B115" s="1">
         <v>111</v>
       </c>
-      <c r="D115" s="5"/>
-    </row>
-    <row r="116" spans="2:4">
+    </row>
+    <row r="116" spans="2:2">
       <c r="B116" s="1">
         <v>112</v>
       </c>
-      <c r="D116" s="5"/>
-    </row>
-    <row r="117" spans="2:4">
+    </row>
+    <row r="117" spans="2:2">
       <c r="B117" s="1">
         <v>113</v>
       </c>
-      <c r="D117" s="5"/>
-    </row>
-    <row r="118" spans="2:4">
+    </row>
+    <row r="118" spans="2:2">
       <c r="B118" s="1">
         <v>114</v>
       </c>
-      <c r="D118" s="5"/>
-    </row>
-    <row r="119" spans="2:4">
+    </row>
+    <row r="119" spans="2:2">
       <c r="B119" s="1">
         <v>115</v>
       </c>
-      <c r="D119" s="5"/>
-    </row>
-    <row r="120" spans="2:4">
+    </row>
+    <row r="120" spans="2:2">
       <c r="B120" s="1">
         <v>116</v>
       </c>
-      <c r="D120" s="5"/>
-    </row>
-    <row r="121" spans="2:4">
+    </row>
+    <row r="121" spans="2:2">
       <c r="B121" s="1">
         <v>117</v>
       </c>
-      <c r="D121" s="5"/>
-    </row>
-    <row r="122" spans="2:4">
+    </row>
+    <row r="122" spans="2:2">
       <c r="B122" s="1">
         <v>118</v>
       </c>
-      <c r="D122" s="5"/>
-    </row>
-    <row r="123" spans="2:4">
+    </row>
+    <row r="123" spans="2:2">
       <c r="B123" s="1">
         <v>119</v>
       </c>
-      <c r="D123" s="5"/>
-    </row>
-    <row r="124" spans="2:4">
+    </row>
+    <row r="124" spans="2:2">
       <c r="B124" s="1">
         <v>120</v>
       </c>
-      <c r="D124" s="5"/>
-    </row>
-    <row r="125" spans="2:4">
+    </row>
+    <row r="125" spans="2:2">
       <c r="B125" s="1">
         <v>121</v>
       </c>
-      <c r="D125" s="5"/>
-    </row>
-    <row r="126" spans="2:4">
+    </row>
+    <row r="126" spans="2:2">
       <c r="B126" s="1">
         <v>122</v>
       </c>
-      <c r="D126" s="5"/>
-    </row>
-    <row r="127" spans="2:4">
+    </row>
+    <row r="127" spans="2:2">
       <c r="B127" s="1">
         <v>123</v>
       </c>
-      <c r="D127" s="5"/>
-    </row>
-    <row r="128" spans="2:4">
+    </row>
+    <row r="128" spans="2:2">
       <c r="B128" s="1">
         <v>124</v>
       </c>
-      <c r="D128" s="5"/>
-    </row>
-    <row r="129" spans="2:4">
+    </row>
+    <row r="129" spans="2:2">
       <c r="B129" s="1">
         <v>125</v>
       </c>
-      <c r="D129" s="5"/>
-    </row>
-    <row r="130" spans="2:4">
+    </row>
+    <row r="130" spans="2:2">
       <c r="B130" s="1">
         <v>126</v>
       </c>
-      <c r="D130" s="5"/>
-    </row>
-    <row r="131" spans="2:4">
+    </row>
+    <row r="131" spans="2:2">
       <c r="B131" s="1">
         <v>127</v>
       </c>
-      <c r="D131" s="5"/>
-    </row>
-    <row r="132" spans="2:4">
+    </row>
+    <row r="132" spans="2:2">
       <c r="B132" s="1">
         <v>128</v>
       </c>
-      <c r="D132" s="5"/>
-    </row>
-    <row r="133" spans="2:4">
+    </row>
+    <row r="133" spans="2:2">
       <c r="B133" s="1">
         <v>129</v>
       </c>
-      <c r="D133" s="5"/>
-    </row>
-    <row r="134" spans="2:4">
+    </row>
+    <row r="134" spans="2:2">
       <c r="B134" s="1">
         <v>130</v>
       </c>
-      <c r="D134" s="5"/>
-    </row>
-    <row r="135" spans="2:4">
+    </row>
+    <row r="135" spans="2:2">
       <c r="B135" s="1">
         <v>131</v>
       </c>
-      <c r="D135" s="5"/>
-    </row>
-    <row r="136" spans="2:4">
+    </row>
+    <row r="136" spans="2:2">
       <c r="B136" s="1">
         <v>132</v>
       </c>
-      <c r="D136" s="5"/>
-    </row>
-    <row r="137" spans="2:4">
+    </row>
+    <row r="137" spans="2:2">
       <c r="B137" s="1">
         <v>133</v>
       </c>
-      <c r="D137" s="5"/>
-    </row>
-    <row r="138" spans="2:4">
+    </row>
+    <row r="138" spans="2:2">
       <c r="B138" s="1">
         <v>134</v>
       </c>
-      <c r="D138" s="5"/>
-    </row>
-    <row r="139" spans="2:4">
+    </row>
+    <row r="139" spans="2:2">
       <c r="B139" s="1">
         <v>135</v>
       </c>
-      <c r="D139" s="5"/>
-    </row>
-    <row r="140" spans="2:4">
+    </row>
+    <row r="140" spans="2:2">
       <c r="B140" s="1">
         <v>136</v>
       </c>
-      <c r="D140" s="5"/>
-    </row>
-    <row r="141" spans="2:4">
+    </row>
+    <row r="141" spans="2:2">
       <c r="B141" s="1">
         <v>137</v>
       </c>
-      <c r="D141" s="5"/>
-    </row>
-    <row r="142" spans="2:4">
+    </row>
+    <row r="142" spans="2:2">
       <c r="B142" s="1">
         <v>138</v>
       </c>
-      <c r="D142" s="5"/>
-    </row>
-    <row r="143" spans="2:4">
+    </row>
+    <row r="143" spans="2:2">
       <c r="B143" s="1">
         <v>139</v>
       </c>
-      <c r="D143" s="5"/>
-    </row>
-    <row r="144" spans="2:4">
+    </row>
+    <row r="144" spans="2:2">
       <c r="B144" s="1">
         <v>140</v>
       </c>
-      <c r="D144" s="5"/>
-    </row>
-    <row r="145" spans="2:4">
+    </row>
+    <row r="145" spans="2:2">
       <c r="B145" s="1">
         <v>141</v>
       </c>
-      <c r="D145" s="5"/>
-    </row>
-    <row r="146" spans="2:4">
+    </row>
+    <row r="146" spans="2:2">
       <c r="B146" s="1">
         <v>142</v>
       </c>
-      <c r="D146" s="5"/>
-    </row>
-    <row r="147" spans="2:4">
+    </row>
+    <row r="147" spans="2:2">
       <c r="B147" s="1">
         <v>143</v>
       </c>
-      <c r="D147" s="5"/>
-    </row>
-    <row r="148" spans="2:4">
+    </row>
+    <row r="148" spans="2:2">
       <c r="B148" s="1">
         <v>144</v>
       </c>
-      <c r="D148" s="5"/>
-    </row>
-    <row r="149" spans="2:4">
+    </row>
+    <row r="149" spans="2:2">
       <c r="B149" s="1">
         <v>145</v>
       </c>
-      <c r="D149" s="5"/>
-    </row>
-    <row r="150" spans="2:4">
+    </row>
+    <row r="150" spans="2:2">
       <c r="B150" s="1">
         <v>146</v>
       </c>
-      <c r="D150" s="5"/>
-    </row>
-    <row r="151" spans="2:4">
+    </row>
+    <row r="151" spans="2:2">
       <c r="B151" s="1">
         <v>147</v>
       </c>
-      <c r="D151" s="5"/>
-    </row>
-    <row r="152" spans="2:4">
+    </row>
+    <row r="152" spans="2:2">
       <c r="B152" s="1">
         <v>148</v>
       </c>
-      <c r="D152" s="5"/>
-    </row>
-    <row r="153" spans="2:4">
+    </row>
+    <row r="153" spans="2:2">
       <c r="B153" s="1">
         <v>149</v>
       </c>
-      <c r="D153" s="5"/>
-    </row>
-    <row r="154" spans="2:4">
+    </row>
+    <row r="154" spans="2:2">
       <c r="B154" s="1">
         <v>150</v>
       </c>
-      <c r="D154" s="5"/>
-    </row>
-    <row r="155" spans="2:4">
+    </row>
+    <row r="155" spans="2:2">
       <c r="B155" s="1">
         <v>151</v>
       </c>
-      <c r="D155" s="5"/>
-    </row>
-    <row r="156" spans="2:4">
+    </row>
+    <row r="156" spans="2:2">
       <c r="B156" s="1">
         <v>152</v>
       </c>
-      <c r="D156" s="5"/>
-    </row>
-    <row r="157" spans="2:4">
+    </row>
+    <row r="157" spans="2:2">
       <c r="B157" s="1">
         <v>153</v>
       </c>
-      <c r="D157" s="5"/>
-    </row>
-    <row r="158" spans="2:4">
+    </row>
+    <row r="158" spans="2:2">
       <c r="B158" s="1">
         <v>154</v>
       </c>
-      <c r="D158" s="5"/>
-    </row>
-    <row r="159" spans="2:4">
+    </row>
+    <row r="159" spans="2:2">
       <c r="B159" s="1">
         <v>155</v>
       </c>
-      <c r="D159" s="5"/>
-    </row>
-    <row r="160" spans="2:4">
+    </row>
+    <row r="160" spans="2:2">
       <c r="B160" s="1">
         <v>156</v>
       </c>
-      <c r="D160" s="5"/>
-    </row>
-    <row r="161" spans="2:4">
+    </row>
+    <row r="161" spans="2:2">
       <c r="B161" s="1">
         <v>157</v>
       </c>
-      <c r="D161" s="5"/>
-    </row>
-    <row r="162" spans="2:4">
+    </row>
+    <row r="162" spans="2:2">
       <c r="B162" s="1">
         <v>158</v>
       </c>
-      <c r="D162" s="5"/>
-    </row>
-    <row r="163" spans="2:4">
+    </row>
+    <row r="163" spans="2:2">
       <c r="B163" s="1">
         <v>159</v>
       </c>
-      <c r="D163" s="5"/>
-    </row>
-    <row r="164" spans="2:4">
+    </row>
+    <row r="164" spans="2:2">
       <c r="B164" s="1">
         <v>160</v>
       </c>
-      <c r="D164" s="5"/>
-    </row>
-    <row r="165" spans="2:4">
+    </row>
+    <row r="165" spans="2:2">
       <c r="B165" s="1">
         <v>161</v>
       </c>
-      <c r="D165" s="5"/>
-    </row>
-    <row r="166" spans="2:4">
+    </row>
+    <row r="166" spans="2:2">
       <c r="B166" s="1">
         <v>162</v>
       </c>
-      <c r="D166" s="5"/>
-    </row>
-    <row r="167" spans="2:4">
+    </row>
+    <row r="167" spans="2:2">
       <c r="B167" s="1">
         <v>163</v>
       </c>
-      <c r="D167" s="5"/>
-    </row>
-    <row r="168" spans="2:4">
+    </row>
+    <row r="168" spans="2:2">
       <c r="B168" s="1">
         <v>164</v>
       </c>
-      <c r="D168" s="5"/>
-    </row>
-    <row r="169" spans="2:4">
+    </row>
+    <row r="169" spans="2:2">
       <c r="B169" s="1">
         <v>165</v>
       </c>
-      <c r="D169" s="5"/>
-    </row>
-    <row r="170" spans="2:4">
+    </row>
+    <row r="170" spans="2:2">
       <c r="B170" s="1">
         <v>166</v>
       </c>
-      <c r="D170" s="5"/>
-    </row>
-    <row r="171" spans="2:4">
+    </row>
+    <row r="171" spans="2:2">
       <c r="B171" s="1">
         <v>167</v>
       </c>
-      <c r="D171" s="5"/>
-    </row>
-    <row r="172" spans="2:4">
+    </row>
+    <row r="172" spans="2:2">
       <c r="B172" s="1">
         <v>168</v>
       </c>
-      <c r="D172" s="5"/>
-    </row>
-    <row r="173" spans="2:4">
+    </row>
+    <row r="173" spans="2:2">
       <c r="B173" s="1">
         <v>169</v>
       </c>
-      <c r="D173" s="5"/>
-    </row>
-    <row r="174" spans="2:4">
+    </row>
+    <row r="174" spans="2:2">
       <c r="B174" s="1">
         <v>170</v>
       </c>
-      <c r="D174" s="5"/>
-    </row>
-    <row r="175" spans="2:4">
+    </row>
+    <row r="175" spans="2:2">
       <c r="B175" s="1">
         <v>171</v>
       </c>
-      <c r="D175" s="5"/>
-    </row>
-    <row r="176" spans="2:4">
+    </row>
+    <row r="176" spans="2:2">
       <c r="B176" s="1">
         <v>172</v>
       </c>
-      <c r="D176" s="5"/>
-    </row>
-    <row r="177" spans="2:4">
+    </row>
+    <row r="177" spans="2:2">
       <c r="B177" s="1">
         <v>173</v>
       </c>
-      <c r="D177" s="5"/>
-    </row>
-    <row r="178" spans="2:4">
+    </row>
+    <row r="178" spans="2:2">
       <c r="B178" s="1">
         <v>174</v>
       </c>
-      <c r="D178" s="5"/>
-    </row>
-    <row r="179" spans="2:4">
+    </row>
+    <row r="179" spans="2:2">
       <c r="B179" s="1">
         <v>175</v>
       </c>
-      <c r="D179" s="5"/>
-    </row>
-    <row r="180" spans="2:4">
+    </row>
+    <row r="180" spans="2:2">
       <c r="B180" s="1">
         <v>176</v>
       </c>
-      <c r="D180" s="5"/>
-    </row>
-    <row r="181" spans="2:4">
+    </row>
+    <row r="181" spans="2:2">
       <c r="B181" s="1">
         <v>177</v>
       </c>
-      <c r="D181" s="5"/>
-    </row>
-    <row r="182" spans="2:4">
+    </row>
+    <row r="182" spans="2:2">
       <c r="B182" s="1">
         <v>178</v>
       </c>
-      <c r="D182" s="5"/>
-    </row>
-    <row r="183" spans="2:4">
+    </row>
+    <row r="183" spans="2:2">
       <c r="B183" s="1">
         <v>179</v>
       </c>
-      <c r="D183" s="5"/>
-    </row>
-    <row r="184" spans="2:4">
+    </row>
+    <row r="184" spans="2:2">
       <c r="B184" s="1">
         <v>180</v>
       </c>
-      <c r="D184" s="5"/>
-    </row>
-    <row r="185" spans="2:4">
+    </row>
+    <row r="185" spans="2:2">
       <c r="B185" s="1">
         <v>181</v>
       </c>
-      <c r="D185" s="5"/>
-    </row>
-    <row r="186" spans="2:4">
+    </row>
+    <row r="186" spans="2:2">
       <c r="B186" s="1">
         <v>182</v>
       </c>
-      <c r="D186" s="5"/>
-    </row>
-    <row r="187" spans="2:4">
+    </row>
+    <row r="187" spans="2:2">
       <c r="B187" s="1">
         <v>183</v>
       </c>
-      <c r="D187" s="5"/>
-    </row>
-    <row r="188" spans="2:4">
+    </row>
+    <row r="188" spans="2:2">
       <c r="B188" s="1">
         <v>184</v>
       </c>
-      <c r="D188" s="5"/>
-    </row>
-    <row r="189" spans="2:4">
+    </row>
+    <row r="189" spans="2:2">
       <c r="B189" s="1">
         <v>185</v>
       </c>
-      <c r="D189" s="5"/>
-    </row>
-    <row r="190" spans="2:4">
+    </row>
+    <row r="190" spans="2:2">
       <c r="B190" s="1">
         <v>186</v>
       </c>
-      <c r="D190" s="5"/>
-    </row>
-    <row r="191" spans="2:4">
+    </row>
+    <row r="191" spans="2:2">
       <c r="B191" s="1">
         <v>187</v>
       </c>
-      <c r="D191" s="5"/>
-    </row>
-    <row r="192" spans="2:4">
+    </row>
+    <row r="192" spans="2:2">
       <c r="B192" s="1">
         <v>188</v>
       </c>
-      <c r="D192" s="5"/>
-    </row>
-    <row r="193" spans="2:4">
+    </row>
+    <row r="193" spans="2:2">
       <c r="B193" s="1">
         <v>189</v>
       </c>
-      <c r="D193" s="5"/>
-    </row>
-    <row r="194" spans="2:4">
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1">
         <v>190</v>
       </c>
-      <c r="D194" s="5"/>
-    </row>
-    <row r="195" spans="2:4">
+    </row>
+    <row r="195" spans="2:2">
       <c r="B195" s="1">
         <v>191</v>
       </c>
-      <c r="D195" s="5"/>
-    </row>
-    <row r="196" spans="2:4">
+    </row>
+    <row r="196" spans="2:2">
       <c r="B196" s="1">
         <v>192</v>
       </c>
-      <c r="D196" s="5"/>
-    </row>
-    <row r="197" spans="2:4">
+    </row>
+    <row r="197" spans="2:2">
       <c r="B197" s="1">
         <v>193</v>
       </c>
-      <c r="D197" s="5"/>
-    </row>
-    <row r="198" spans="2:4">
+    </row>
+    <row r="198" spans="2:2">
       <c r="B198" s="1">
         <v>194</v>
       </c>
-      <c r="D198" s="5"/>
-    </row>
-    <row r="199" spans="2:4">
+    </row>
+    <row r="199" spans="2:2">
       <c r="B199" s="1">
         <v>195</v>
       </c>
-      <c r="D199" s="5"/>
-    </row>
-    <row r="200" spans="2:4">
+    </row>
+    <row r="200" spans="2:2">
       <c r="B200" s="1">
         <v>196</v>
       </c>
-      <c r="D200" s="5"/>
-    </row>
-    <row r="201" spans="2:4">
+    </row>
+    <row r="201" spans="2:2">
       <c r="B201" s="1">
         <v>197</v>
       </c>
-      <c r="D201" s="5"/>
-    </row>
-    <row r="202" spans="2:4">
+    </row>
+    <row r="202" spans="2:2">
       <c r="B202" s="1">
         <v>198</v>
       </c>
-      <c r="D202" s="5"/>
-    </row>
-    <row r="203" spans="2:4">
+    </row>
+    <row r="203" spans="2:2">
       <c r="B203" s="1">
         <v>199</v>
       </c>
-      <c r="D203" s="5"/>
-    </row>
-    <row r="204" spans="2:4">
+    </row>
+    <row r="204" spans="2:2">
       <c r="B204" s="1">
         <v>200</v>
       </c>
-      <c r="D204" s="5"/>
-    </row>
-    <row r="205" spans="2:4">
+    </row>
+    <row r="205" spans="2:2">
       <c r="B205" s="1">
         <v>201</v>
       </c>
-      <c r="D205" s="5"/>
-    </row>
-    <row r="206" spans="2:4">
+    </row>
+    <row r="206" spans="2:2">
       <c r="B206" s="1">
         <v>202</v>
       </c>
-      <c r="D206" s="5"/>
-    </row>
-    <row r="207" spans="2:4">
+    </row>
+    <row r="207" spans="2:2">
       <c r="B207" s="1">
         <v>203</v>
       </c>
-      <c r="D207" s="5"/>
-    </row>
-    <row r="208" spans="2:4">
+    </row>
+    <row r="208" spans="2:2">
       <c r="B208" s="1">
         <v>204</v>
       </c>
-      <c r="D208" s="5"/>
-    </row>
-    <row r="209" spans="2:4">
+    </row>
+    <row r="209" spans="2:2">
       <c r="B209" s="1">
         <v>205</v>
       </c>
-      <c r="D209" s="5"/>
-    </row>
-    <row r="210" spans="2:4">
+    </row>
+    <row r="210" spans="2:2">
       <c r="B210" s="1">
         <v>206</v>
       </c>
-      <c r="D210" s="5"/>
-    </row>
-    <row r="211" spans="2:4">
+    </row>
+    <row r="211" spans="2:2">
       <c r="B211" s="1">
         <v>207</v>
       </c>
-      <c r="D211" s="5"/>
-    </row>
-    <row r="212" spans="2:4">
+    </row>
+    <row r="212" spans="2:2">
       <c r="B212" s="1">
         <v>208</v>
       </c>
-      <c r="D212" s="5"/>
-    </row>
-    <row r="213" spans="2:4">
+    </row>
+    <row r="213" spans="2:2">
       <c r="B213" s="1">
         <v>209</v>
       </c>
-      <c r="D213" s="5"/>
-    </row>
-    <row r="214" spans="2:4">
+    </row>
+    <row r="214" spans="2:2">
       <c r="B214" s="1">
         <v>210</v>
       </c>
-      <c r="D214" s="5"/>
-    </row>
-    <row r="215" spans="2:4">
+    </row>
+    <row r="215" spans="2:2">
       <c r="B215" s="1">
         <v>211</v>
       </c>
-      <c r="D215" s="5"/>
-    </row>
-    <row r="216" spans="2:4">
+    </row>
+    <row r="216" spans="2:2">
       <c r="B216" s="1">
         <v>212</v>
       </c>
-      <c r="D216" s="5"/>
-    </row>
-    <row r="217" spans="2:4">
+    </row>
+    <row r="217" spans="2:2">
       <c r="B217" s="1">
         <v>213</v>
       </c>
-      <c r="D217" s="5"/>
-    </row>
-    <row r="218" spans="2:4">
+    </row>
+    <row r="218" spans="2:2">
       <c r="B218" s="1">
         <v>214</v>
       </c>
-      <c r="D218" s="5"/>
-    </row>
-    <row r="219" spans="2:4">
+    </row>
+    <row r="219" spans="2:2">
       <c r="B219" s="1">
         <v>215</v>
       </c>
-      <c r="D219" s="5"/>
-    </row>
-    <row r="220" spans="2:4">
+    </row>
+    <row r="220" spans="2:2">
       <c r="B220" s="1">
         <v>216</v>
       </c>
-      <c r="D220" s="5"/>
-    </row>
-    <row r="221" spans="2:4">
+    </row>
+    <row r="221" spans="2:2">
       <c r="B221" s="1">
         <v>217</v>
       </c>
-      <c r="D221" s="5"/>
-    </row>
-    <row r="222" spans="2:4">
+    </row>
+    <row r="222" spans="2:2">
       <c r="B222" s="1">
         <v>218</v>
       </c>
-      <c r="D222" s="5"/>
-    </row>
-    <row r="223" spans="2:4">
+    </row>
+    <row r="223" spans="2:2">
       <c r="B223" s="1">
         <v>219</v>
       </c>
-      <c r="D223" s="5"/>
-    </row>
-    <row r="224" spans="2:4">
+    </row>
+    <row r="224" spans="2:2">
       <c r="B224" s="1">
         <v>220</v>
       </c>
-      <c r="D224" s="5"/>
-    </row>
-    <row r="225" spans="2:4">
+    </row>
+    <row r="225" spans="2:2">
       <c r="B225" s="1">
         <v>221</v>
       </c>
-      <c r="D225" s="5"/>
-    </row>
-    <row r="226" spans="2:4">
+    </row>
+    <row r="226" spans="2:2">
       <c r="B226" s="1">
         <v>222</v>
       </c>
-      <c r="D226" s="5"/>
-    </row>
-    <row r="227" spans="2:4">
+    </row>
+    <row r="227" spans="2:2">
       <c r="B227" s="1">
         <v>223</v>
       </c>
-      <c r="D227" s="5"/>
-    </row>
-    <row r="228" spans="2:4">
+    </row>
+    <row r="228" spans="2:2">
       <c r="B228" s="1">
         <v>224</v>
       </c>
-      <c r="D228" s="5"/>
-    </row>
-    <row r="229" spans="2:4">
+    </row>
+    <row r="229" spans="2:2">
       <c r="B229" s="1">
         <v>225</v>
       </c>
-      <c r="D229" s="5"/>
-    </row>
-    <row r="230" spans="2:4">
+    </row>
+    <row r="230" spans="2:2">
       <c r="B230" s="1">
         <v>226</v>
       </c>
-      <c r="D230" s="5"/>
-    </row>
-    <row r="231" spans="2:4">
+    </row>
+    <row r="231" spans="2:2">
       <c r="B231" s="1">
         <v>227</v>
       </c>
-      <c r="D231" s="5"/>
-    </row>
-    <row r="232" spans="2:4">
+    </row>
+    <row r="232" spans="2:2">
       <c r="B232" s="1">
         <v>228</v>
       </c>
-      <c r="D232" s="5"/>
-    </row>
-    <row r="233" spans="2:4">
+    </row>
+    <row r="233" spans="2:2">
       <c r="B233" s="1">
         <v>229</v>
       </c>
-      <c r="D233" s="5"/>
-    </row>
-    <row r="234" spans="2:4">
+    </row>
+    <row r="234" spans="2:2">
       <c r="B234" s="1">
         <v>230</v>
       </c>
-      <c r="D234" s="5"/>
-    </row>
-    <row r="235" spans="2:4">
+    </row>
+    <row r="235" spans="2:2">
       <c r="B235" s="1">
         <v>231</v>
       </c>
-      <c r="D235" s="5"/>
-    </row>
-    <row r="236" spans="2:4">
+    </row>
+    <row r="236" spans="2:2">
       <c r="B236" s="1">
         <v>232</v>
       </c>
-      <c r="D236" s="5"/>
-    </row>
-    <row r="237" spans="2:4">
+    </row>
+    <row r="237" spans="2:2">
       <c r="B237" s="1">
         <v>233</v>
       </c>
-      <c r="D237" s="5"/>
-    </row>
-    <row r="238" spans="2:4">
+    </row>
+    <row r="238" spans="2:2">
       <c r="B238" s="1">
         <v>234</v>
       </c>
-      <c r="D238" s="5"/>
-    </row>
-    <row r="239" spans="2:4">
+    </row>
+    <row r="239" spans="2:2">
       <c r="B239" s="1">
         <v>235</v>
       </c>
-      <c r="D239" s="5"/>
-    </row>
-    <row r="240" spans="2:4">
+    </row>
+    <row r="240" spans="2:2">
       <c r="B240" s="1">
         <v>236</v>
       </c>
-      <c r="D240" s="5"/>
-    </row>
-    <row r="241" spans="2:4">
+    </row>
+    <row r="241" spans="2:2">
       <c r="B241" s="1">
         <v>237</v>
       </c>
-      <c r="D241" s="5"/>
-    </row>
-    <row r="242" spans="2:4">
+    </row>
+    <row r="242" spans="2:2">
       <c r="B242" s="1">
         <v>238</v>
       </c>
-      <c r="D242" s="5"/>
-    </row>
-    <row r="243" spans="2:4">
+    </row>
+    <row r="243" spans="2:2">
       <c r="B243" s="1">
         <v>239</v>
       </c>
-      <c r="D243" s="5"/>
-    </row>
-    <row r="244" spans="2:4">
+    </row>
+    <row r="244" spans="2:2">
       <c r="B244" s="1">
         <v>240</v>
       </c>
-      <c r="D244" s="5"/>
-    </row>
-    <row r="245" spans="2:4">
+    </row>
+    <row r="245" spans="2:2">
       <c r="B245" s="1">
         <v>241</v>
       </c>
-      <c r="D245" s="5"/>
-    </row>
-    <row r="246" spans="2:4">
+    </row>
+    <row r="246" spans="2:2">
       <c r="B246" s="1">
         <v>242</v>
       </c>
-      <c r="D246" s="5"/>
-    </row>
-    <row r="247" spans="2:4">
+    </row>
+    <row r="247" spans="2:2">
       <c r="B247" s="1">
         <v>243</v>
       </c>
-      <c r="D247" s="5"/>
-    </row>
-    <row r="248" spans="2:4">
+    </row>
+    <row r="248" spans="2:2">
       <c r="B248" s="1">
         <v>244</v>
       </c>
-      <c r="D248" s="5"/>
-    </row>
-    <row r="249" spans="2:4">
+    </row>
+    <row r="249" spans="2:2">
       <c r="B249" s="1">
         <v>245</v>
       </c>
-      <c r="D249" s="5"/>
-    </row>
-    <row r="250" spans="2:4">
+    </row>
+    <row r="250" spans="2:2">
       <c r="B250" s="1">
         <v>246</v>
       </c>
-      <c r="D250" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="S3:T3"/>
     <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="D3:E3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="F3:F4"/>
@@ -2515,30 +2187,22 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
-    <mergeCell ref="D3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:T250">
+  <conditionalFormatting sqref="B5:S250">
     <cfRule type="expression" priority="6" stopIfTrue="1">
-      <formula>$P5=""</formula>
+      <formula>$Q5=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="7">
-      <formula>$P5&lt;TODAY()</formula>
+    <cfRule type="expression" dxfId="3" priority="7">
+      <formula>$Q5&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>OR($P5-TODAY()=0, $P5-TODAY()=1)</formula>
+    <cfRule type="expression" dxfId="2" priority="8">
+      <formula>OR($Q5-TODAY()=0, $Q5-TODAY()=1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="9">
-      <formula>AND($P5-TODAY()&gt;=0, $P5-TODAY()&lt;=3)</formula>
+    <cfRule type="expression" dxfId="1" priority="9">
+      <formula>AND($Q5-TODAY()&gt;=0, $Q5-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="10">
-      <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>AND($Q5-TODAY()&gt;=4, $Q5-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2560,131 +2224,131 @@
   <sheetData>
     <row r="3" spans="2:10" ht="15" customHeight="1"/>
     <row r="4" spans="2:10" ht="15" customHeight="1">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="J4" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
         <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:10">
       <c r="B6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:10">
       <c r="B7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
         <v>33</v>
       </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" t="s">
-        <v>34</v>
-      </c>
       <c r="J7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="B8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="2:10">
       <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
         <v>48</v>
       </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
       <c r="J9" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:10">
       <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" t="s">
         <v>51</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="11" spans="2:10">
       <c r="F11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="2:10">
       <c r="J12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="2:10">
       <c r="J13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB091A07-861C-4969-94C1-E395357F18B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4877E3-5C07-423A-949F-B4F118F8D4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -389,6 +389,21 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -410,26 +425,67 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -773,7 +829,7 @@
   <cols>
     <col min="1" max="2" width="9.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="25" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="17" customWidth="1"/>
     <col min="5" max="5" width="7.109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" style="1" customWidth="1"/>
     <col min="7" max="8" width="20.33203125" style="1" customWidth="1"/>
@@ -794,113 +850,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22" t="s">
+      <c r="J1" s="26"/>
+      <c r="K1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="22"/>
+      <c r="L1" s="27"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
     </row>
     <row r="3" spans="1:20" ht="19.8" customHeight="1">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="21"/>
+      <c r="F3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="23" t="s">
+      <c r="L3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="23" t="s">
+      <c r="N3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="23" t="s">
+      <c r="O3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="18"/>
+      <c r="Q3" s="23"/>
       <c r="R3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="S3" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="16"/>
+      <c r="T3" s="21"/>
     </row>
     <row r="4" spans="1:20" ht="32.4" customHeight="1">
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="24" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
       <c r="P4" s="5" t="s">
         <v>18</v>
       </c>
@@ -1004,8 +1060,8 @@
         <v>17</v>
       </c>
       <c r="C21" s="10"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="27"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
@@ -1017,7 +1073,7 @@
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
-      <c r="Q21" s="27"/>
+      <c r="Q21" s="19"/>
       <c r="R21" s="12"/>
       <c r="S21" s="11"/>
     </row>
@@ -2168,11 +2224,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="P3:Q3"/>
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="E1:G2"/>
     <mergeCell ref="I1:J2"/>
@@ -2187,22 +2238,27 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="P3:Q3"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:S250">
+  <conditionalFormatting sqref="B5:T250">
     <cfRule type="expression" priority="6" stopIfTrue="1">
-      <formula>$Q5=""</formula>
+      <formula>$P5=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="7">
-      <formula>$Q5&lt;TODAY()</formula>
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>$P5&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="8">
-      <formula>OR($Q5-TODAY()=0, $Q5-TODAY()=1)</formula>
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>OR($P5-TODAY()=0, $P5-TODAY()=1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="9">
-      <formula>AND($Q5-TODAY()&gt;=0, $Q5-TODAY()&lt;=3)</formula>
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND($P5-TODAY()&gt;=0, $P5-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="10">
-      <formula>AND($Q5-TODAY()&gt;=4, $Q5-TODAY()&lt;=7)</formula>
+    <cfRule type="expression" dxfId="4" priority="10">
+      <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4877E3-5C07-423A-949F-B4F118F8D4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5E1F5F-9D3E-4D3C-843A-43A7800C908A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,7 +205,7 @@
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,7 +278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -342,6 +342,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -349,6 +375,9 @@
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -360,18 +389,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -386,31 +411,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -425,39 +426,32 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -825,11 +819,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T250"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="17" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="7.109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" style="1" customWidth="1"/>
     <col min="7" max="8" width="20.33203125" style="1" customWidth="1"/>
@@ -839,1396 +833,1441 @@
     <col min="12" max="12" width="46" style="1" customWidth="1"/>
     <col min="13" max="14" width="45.33203125" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20.77734375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.21875" style="7" customWidth="1"/>
-    <col min="20" max="20" width="16.88671875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="15" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.109375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="8.109375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="12" style="4" customWidth="1"/>
+    <col min="20" max="20" width="9.88671875" style="4" customWidth="1"/>
     <col min="21" max="21" width="100" style="1" customWidth="1"/>
     <col min="22" max="22" width="9.109375" style="1" customWidth="1"/>
     <col min="23" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="25" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="26" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="27" t="s">
+      <c r="J1" s="19"/>
+      <c r="K1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="27"/>
-    </row>
-    <row r="2" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-    </row>
-    <row r="3" spans="1:20" ht="19.8" customHeight="1">
-      <c r="B3" s="20" t="s">
+      <c r="L1" s="20"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="L3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="M3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="N3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="20" t="s">
+      <c r="O3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="6" t="s">
+      <c r="Q3" s="24"/>
+      <c r="R3" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="21" t="s">
+      <c r="S3" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="21"/>
-    </row>
-    <row r="4" spans="1:20" ht="32.4" customHeight="1">
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="16" t="s">
+      <c r="T3" s="25"/>
+    </row>
+    <row r="4" spans="1:20" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="5" t="s">
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="Q4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="R4" s="6"/>
-      <c r="S4" s="5" t="s">
+      <c r="R4" s="27"/>
+      <c r="S4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="R5" s="8"/>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="D5" s="6"/>
+      <c r="E5" s="7"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="7"/>
+      <c r="T5" s="1"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="D6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="T6" s="1"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="R7" s="8"/>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="D7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="9"/>
+      <c r="T7" s="1"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="D8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="T8" s="1"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:20">
+      <c r="D9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="T9" s="1"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="D10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="T10" s="1"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="D11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="D12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="T12" s="1"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="D13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="T13" s="1"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1">
+      <c r="D14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="T14" s="1"/>
+    </row>
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="9"/>
-    </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1">
+      <c r="C15" s="10"/>
+      <c r="D15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="T15" s="1"/>
+    </row>
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="9"/>
-    </row>
-    <row r="17" spans="2:19">
+      <c r="C16" s="10"/>
+      <c r="D16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="T16" s="1"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="2:19">
+      <c r="D17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="T17" s="1"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="2:19">
+      <c r="T18" s="1"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="2:19">
+      <c r="T19" s="1"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="2:19">
+      <c r="T20" s="1"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="12"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="13"/>
       <c r="S21" s="11"/>
-    </row>
-    <row r="22" spans="2:19">
+      <c r="T21" s="1"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="2:19">
+      <c r="T22" s="1"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="2:19">
+      <c r="T23" s="1"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="2:19">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="2:19">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="2:19">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:19">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="2:19">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="2:19">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="2:19">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B31" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="2:19">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="2:2">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B46" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="2:2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="2:2">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="2:2">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="2:2">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="2:2">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="2:2">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B54" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="2:2">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B55" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="2:2">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B56" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="2:2">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B57" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="2:2">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B58" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="2:2">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B59" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="2:2">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B60" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="2:2">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B61" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="2:2">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B62" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="2:2">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B63" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="2:2">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B64" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="2:2">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="2:2">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="2:2">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B67" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="68" spans="2:2">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B68" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="2:2">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B69" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="2:2">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B70" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="2:2">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B71" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="2:2">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B72" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="73" spans="2:2">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B73" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="2:2">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B74" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="75" spans="2:2">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B75" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="2:2">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B76" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="2:2">
+    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B77" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="2:2">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B78" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="2:2">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B79" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="2:2">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B80" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="81" spans="2:2">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B81" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="2:2">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B82" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="83" spans="2:2">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B83" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="84" spans="2:2">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B84" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="85" spans="2:2">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B85" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="86" spans="2:2">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B86" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="87" spans="2:2">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B87" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="88" spans="2:2">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B88" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="89" spans="2:2">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B89" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="90" spans="2:2">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B90" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="91" spans="2:2">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B91" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="92" spans="2:2">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B92" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="93" spans="2:2">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B93" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="94" spans="2:2">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B94" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="95" spans="2:2">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B95" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="96" spans="2:2">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B96" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="97" spans="2:2">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B97" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="98" spans="2:2">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B98" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="99" spans="2:2">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B99" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="100" spans="2:2">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B100" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="101" spans="2:2">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B101" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="102" spans="2:2">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B102" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="103" spans="2:2">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B103" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="104" spans="2:2">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B104" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="2:2">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B105" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="106" spans="2:2">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B106" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="107" spans="2:2">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B107" s="1">
         <v>103</v>
       </c>
     </row>
-    <row r="108" spans="2:2">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B108" s="1">
         <v>104</v>
       </c>
     </row>
-    <row r="109" spans="2:2">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B109" s="1">
         <v>105</v>
       </c>
     </row>
-    <row r="110" spans="2:2">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B110" s="1">
         <v>106</v>
       </c>
     </row>
-    <row r="111" spans="2:2">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B111" s="1">
         <v>107</v>
       </c>
     </row>
-    <row r="112" spans="2:2">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B112" s="1">
         <v>108</v>
       </c>
     </row>
-    <row r="113" spans="2:2">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B113" s="1">
         <v>109</v>
       </c>
     </row>
-    <row r="114" spans="2:2">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B114" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="115" spans="2:2">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B115" s="1">
         <v>111</v>
       </c>
     </row>
-    <row r="116" spans="2:2">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B116" s="1">
         <v>112</v>
       </c>
     </row>
-    <row r="117" spans="2:2">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B117" s="1">
         <v>113</v>
       </c>
     </row>
-    <row r="118" spans="2:2">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B118" s="1">
         <v>114</v>
       </c>
     </row>
-    <row r="119" spans="2:2">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B119" s="1">
         <v>115</v>
       </c>
     </row>
-    <row r="120" spans="2:2">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B120" s="1">
         <v>116</v>
       </c>
     </row>
-    <row r="121" spans="2:2">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B121" s="1">
         <v>117</v>
       </c>
     </row>
-    <row r="122" spans="2:2">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B122" s="1">
         <v>118</v>
       </c>
     </row>
-    <row r="123" spans="2:2">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B123" s="1">
         <v>119</v>
       </c>
     </row>
-    <row r="124" spans="2:2">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B124" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="125" spans="2:2">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B125" s="1">
         <v>121</v>
       </c>
     </row>
-    <row r="126" spans="2:2">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B126" s="1">
         <v>122</v>
       </c>
     </row>
-    <row r="127" spans="2:2">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B127" s="1">
         <v>123</v>
       </c>
     </row>
-    <row r="128" spans="2:2">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B128" s="1">
         <v>124</v>
       </c>
     </row>
-    <row r="129" spans="2:2">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B129" s="1">
         <v>125</v>
       </c>
     </row>
-    <row r="130" spans="2:2">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B130" s="1">
         <v>126</v>
       </c>
     </row>
-    <row r="131" spans="2:2">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B131" s="1">
         <v>127</v>
       </c>
     </row>
-    <row r="132" spans="2:2">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B132" s="1">
         <v>128</v>
       </c>
     </row>
-    <row r="133" spans="2:2">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B133" s="1">
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="2:2">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B134" s="1">
         <v>130</v>
       </c>
     </row>
-    <row r="135" spans="2:2">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B135" s="1">
         <v>131</v>
       </c>
     </row>
-    <row r="136" spans="2:2">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B136" s="1">
         <v>132</v>
       </c>
     </row>
-    <row r="137" spans="2:2">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B137" s="1">
         <v>133</v>
       </c>
     </row>
-    <row r="138" spans="2:2">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B138" s="1">
         <v>134</v>
       </c>
     </row>
-    <row r="139" spans="2:2">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B139" s="1">
         <v>135</v>
       </c>
     </row>
-    <row r="140" spans="2:2">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B140" s="1">
         <v>136</v>
       </c>
     </row>
-    <row r="141" spans="2:2">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B141" s="1">
         <v>137</v>
       </c>
     </row>
-    <row r="142" spans="2:2">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B142" s="1">
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="2:2">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B143" s="1">
         <v>139</v>
       </c>
     </row>
-    <row r="144" spans="2:2">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B144" s="1">
         <v>140</v>
       </c>
     </row>
-    <row r="145" spans="2:2">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B145" s="1">
         <v>141</v>
       </c>
     </row>
-    <row r="146" spans="2:2">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B146" s="1">
         <v>142</v>
       </c>
     </row>
-    <row r="147" spans="2:2">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B147" s="1">
         <v>143</v>
       </c>
     </row>
-    <row r="148" spans="2:2">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B148" s="1">
         <v>144</v>
       </c>
     </row>
-    <row r="149" spans="2:2">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B149" s="1">
         <v>145</v>
       </c>
     </row>
-    <row r="150" spans="2:2">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B150" s="1">
         <v>146</v>
       </c>
     </row>
-    <row r="151" spans="2:2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B151" s="1">
         <v>147</v>
       </c>
     </row>
-    <row r="152" spans="2:2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B152" s="1">
         <v>148</v>
       </c>
     </row>
-    <row r="153" spans="2:2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B153" s="1">
         <v>149</v>
       </c>
     </row>
-    <row r="154" spans="2:2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B154" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="155" spans="2:2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B155" s="1">
         <v>151</v>
       </c>
     </row>
-    <row r="156" spans="2:2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B156" s="1">
         <v>152</v>
       </c>
     </row>
-    <row r="157" spans="2:2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B157" s="1">
         <v>153</v>
       </c>
     </row>
-    <row r="158" spans="2:2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B158" s="1">
         <v>154</v>
       </c>
     </row>
-    <row r="159" spans="2:2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B159" s="1">
         <v>155</v>
       </c>
     </row>
-    <row r="160" spans="2:2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="1">
         <v>156</v>
       </c>
     </row>
-    <row r="161" spans="2:2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="1">
         <v>157</v>
       </c>
     </row>
-    <row r="162" spans="2:2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="1">
         <v>158</v>
       </c>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="1">
         <v>159</v>
       </c>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="1">
         <v>160</v>
       </c>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="1">
         <v>161</v>
       </c>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="1">
         <v>162</v>
       </c>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="1">
         <v>163</v>
       </c>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="1">
         <v>164</v>
       </c>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="1">
         <v>165</v>
       </c>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="1">
         <v>166</v>
       </c>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="1">
         <v>167</v>
       </c>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="1">
         <v>168</v>
       </c>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="1">
         <v>169</v>
       </c>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="1">
         <v>170</v>
       </c>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="1">
         <v>171</v>
       </c>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="1">
         <v>172</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="1">
         <v>173</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="1">
         <v>174</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="1">
         <v>175</v>
       </c>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="1">
         <v>176</v>
       </c>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="1">
         <v>177</v>
       </c>
     </row>
-    <row r="182" spans="2:2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="1">
         <v>178</v>
       </c>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="1">
         <v>179</v>
       </c>
     </row>
-    <row r="184" spans="2:2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="1">
         <v>180</v>
       </c>
     </row>
-    <row r="185" spans="2:2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="1">
         <v>181</v>
       </c>
     </row>
-    <row r="186" spans="2:2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="1">
         <v>182</v>
       </c>
     </row>
-    <row r="187" spans="2:2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="1">
         <v>183</v>
       </c>
     </row>
-    <row r="188" spans="2:2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="1">
         <v>184</v>
       </c>
     </row>
-    <row r="189" spans="2:2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="1">
         <v>185</v>
       </c>
     </row>
-    <row r="190" spans="2:2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="1">
         <v>186</v>
       </c>
     </row>
-    <row r="191" spans="2:2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="1">
         <v>187</v>
       </c>
     </row>
-    <row r="192" spans="2:2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="1">
         <v>188</v>
       </c>
     </row>
-    <row r="193" spans="2:2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="1">
         <v>189</v>
       </c>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="1">
         <v>190</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="1">
         <v>191</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="1">
         <v>192</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="1">
         <v>193</v>
       </c>
     </row>
-    <row r="198" spans="2:2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="1">
         <v>194</v>
       </c>
     </row>
-    <row r="199" spans="2:2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="1">
         <v>195</v>
       </c>
     </row>
-    <row r="200" spans="2:2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="1">
         <v>196</v>
       </c>
     </row>
-    <row r="201" spans="2:2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="1">
         <v>197</v>
       </c>
     </row>
-    <row r="202" spans="2:2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="1">
         <v>198</v>
       </c>
     </row>
-    <row r="203" spans="2:2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B203" s="1">
         <v>199</v>
       </c>
     </row>
-    <row r="204" spans="2:2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="205" spans="2:2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B205" s="1">
         <v>201</v>
       </c>
     </row>
-    <row r="206" spans="2:2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B206" s="1">
         <v>202</v>
       </c>
     </row>
-    <row r="207" spans="2:2">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B207" s="1">
         <v>203</v>
       </c>
     </row>
-    <row r="208" spans="2:2">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B208" s="1">
         <v>204</v>
       </c>
     </row>
-    <row r="209" spans="2:2">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B209" s="1">
         <v>205</v>
       </c>
     </row>
-    <row r="210" spans="2:2">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="1">
         <v>206</v>
       </c>
     </row>
-    <row r="211" spans="2:2">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B211" s="1">
         <v>207</v>
       </c>
     </row>
-    <row r="212" spans="2:2">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B212" s="1">
         <v>208</v>
       </c>
     </row>
-    <row r="213" spans="2:2">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B213" s="1">
         <v>209</v>
       </c>
     </row>
-    <row r="214" spans="2:2">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B214" s="1">
         <v>210</v>
       </c>
     </row>
-    <row r="215" spans="2:2">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B215" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="216" spans="2:2">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B216" s="1">
         <v>212</v>
       </c>
     </row>
-    <row r="217" spans="2:2">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B217" s="1">
         <v>213</v>
       </c>
     </row>
-    <row r="218" spans="2:2">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B218" s="1">
         <v>214</v>
       </c>
     </row>
-    <row r="219" spans="2:2">
+    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B219" s="1">
         <v>215</v>
       </c>
     </row>
-    <row r="220" spans="2:2">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B220" s="1">
         <v>216</v>
       </c>
     </row>
-    <row r="221" spans="2:2">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B221" s="1">
         <v>217</v>
       </c>
     </row>
-    <row r="222" spans="2:2">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B222" s="1">
         <v>218</v>
       </c>
     </row>
-    <row r="223" spans="2:2">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B223" s="1">
         <v>219</v>
       </c>
     </row>
-    <row r="224" spans="2:2">
+    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B224" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="225" spans="2:2">
+    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B225" s="1">
         <v>221</v>
       </c>
     </row>
-    <row r="226" spans="2:2">
+    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B226" s="1">
         <v>222</v>
       </c>
     </row>
-    <row r="227" spans="2:2">
+    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B227" s="1">
         <v>223</v>
       </c>
     </row>
-    <row r="228" spans="2:2">
+    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B228" s="1">
         <v>224</v>
       </c>
     </row>
-    <row r="229" spans="2:2">
+    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B229" s="1">
         <v>225</v>
       </c>
     </row>
-    <row r="230" spans="2:2">
+    <row r="230" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B230" s="1">
         <v>226</v>
       </c>
     </row>
-    <row r="231" spans="2:2">
+    <row r="231" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B231" s="1">
         <v>227</v>
       </c>
     </row>
-    <row r="232" spans="2:2">
+    <row r="232" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B232" s="1">
         <v>228</v>
       </c>
     </row>
-    <row r="233" spans="2:2">
+    <row r="233" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B233" s="1">
         <v>229</v>
       </c>
     </row>
-    <row r="234" spans="2:2">
+    <row r="234" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B234" s="1">
         <v>230</v>
       </c>
     </row>
-    <row r="235" spans="2:2">
+    <row r="235" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B235" s="1">
         <v>231</v>
       </c>
     </row>
-    <row r="236" spans="2:2">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B236" s="1">
         <v>232</v>
       </c>
     </row>
-    <row r="237" spans="2:2">
+    <row r="237" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B237" s="1">
         <v>233</v>
       </c>
     </row>
-    <row r="238" spans="2:2">
+    <row r="238" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B238" s="1">
         <v>234</v>
       </c>
     </row>
-    <row r="239" spans="2:2">
+    <row r="239" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B239" s="1">
         <v>235</v>
       </c>
     </row>
-    <row r="240" spans="2:2">
+    <row r="240" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B240" s="1">
         <v>236</v>
       </c>
     </row>
-    <row r="241" spans="2:2">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B241" s="1">
         <v>237</v>
       </c>
     </row>
-    <row r="242" spans="2:2">
+    <row r="242" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B242" s="1">
         <v>238</v>
       </c>
     </row>
-    <row r="243" spans="2:2">
+    <row r="243" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B243" s="1">
         <v>239</v>
       </c>
     </row>
-    <row r="244" spans="2:2">
+    <row r="244" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B244" s="1">
         <v>240</v>
       </c>
     </row>
-    <row r="245" spans="2:2">
+    <row r="245" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B245" s="1">
         <v>241</v>
       </c>
     </row>
-    <row r="246" spans="2:2">
+    <row r="246" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B246" s="1">
         <v>242</v>
       </c>
     </row>
-    <row r="247" spans="2:2">
+    <row r="247" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B247" s="1">
         <v>243</v>
       </c>
     </row>
-    <row r="248" spans="2:2">
+    <row r="248" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B248" s="1">
         <v>244</v>
       </c>
     </row>
-    <row r="249" spans="2:2">
+    <row r="249" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B249" s="1">
         <v>245</v>
       </c>
     </row>
-    <row r="250" spans="2:2">
+    <row r="250" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B250" s="1">
         <v>246</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
-    <mergeCell ref="D3:E3"/>
+  <mergeCells count="20">
+    <mergeCell ref="S3:T3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="F3:F4"/>
@@ -2241,24 +2280,46 @@
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
-    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
     <mergeCell ref="P3:Q3"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:T250">
+  <conditionalFormatting sqref="B5:S250">
     <cfRule type="expression" priority="6" stopIfTrue="1">
-      <formula>$P5=""</formula>
+      <formula>$Q5=""</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="7">
-      <formula>$P5&lt;TODAY()</formula>
+      <formula>$Q5&lt;TODAY()</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="8">
-      <formula>OR($P5-TODAY()=0, $P5-TODAY()=1)</formula>
+      <formula>OR($Q5-TODAY()=0, $Q5-TODAY()=1)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="9">
-      <formula>AND($P5-TODAY()&gt;=0, $P5-TODAY()&lt;=3)</formula>
+      <formula>AND($Q5-TODAY()&gt;=0, $Q5-TODAY()&lt;=3)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="10">
-      <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
+      <formula>AND($Q5-TODAY()&gt;=4, $Q5-TODAY()&lt;=7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G43:H43">
+    <cfRule type="expression" priority="16">
+      <formula>$Q44=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="17">
+      <formula>$Q44&lt;TODAY()</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="18">
+      <formula>$Q44-TODAY()=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="19">
+      <formula>AND($Q44-TODAY()&gt;=0, $Q44-TODAY()&lt;=3)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="20">
+      <formula>AND($Q44-TODAY()&gt;=4, $Q44-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2269,7 +2330,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:J13"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.109375" customWidth="1"/>
     <col min="4" max="4" width="15.88671875" customWidth="1"/>
@@ -2278,25 +2339,25 @@
     <col min="10" max="12" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="15" customHeight="1"/>
-    <row r="4" spans="2:10" ht="15" customHeight="1">
-      <c r="B4" s="13" t="s">
+    <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>21</v>
       </c>
@@ -2313,7 +2374,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>40</v>
       </c>
@@ -2330,7 +2391,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>43</v>
       </c>
@@ -2347,7 +2408,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>30</v>
       </c>
@@ -2364,7 +2425,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>47</v>
       </c>
@@ -2378,7 +2439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>49</v>
       </c>
@@ -2389,7 +2450,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
         <v>52</v>
       </c>
@@ -2397,12 +2458,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J13" t="s">
         <v>55</v>
       </c>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5E1F5F-9D3E-4D3C-843A-43A7800C908A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1274C825-DBAD-48F9-91B9-17FA606C9B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,8 +11,19 @@
     <sheet name="Requisições 2026" sheetId="1" r:id="rId1"/>
     <sheet name="DADOS" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -205,7 +216,7 @@
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,12 +383,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -411,7 +419,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -429,29 +452,74 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="16">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -819,12 +887,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T250"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" style="1" customWidth="1"/>
     <col min="7" max="8" width="20.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.33203125" style="1" customWidth="1"/>
@@ -833,1440 +901,1643 @@
     <col min="12" max="12" width="46" style="1" customWidth="1"/>
     <col min="13" max="14" width="45.33203125" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="15" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.109375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="12" style="4" customWidth="1"/>
-    <col min="20" max="20" width="9.88671875" style="4" customWidth="1"/>
+    <col min="16" max="16" width="15" style="5" customWidth="1"/>
+    <col min="17" max="17" width="12.109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="10.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="12" style="5" customWidth="1"/>
+    <col min="20" max="20" width="9.88671875" style="3" customWidth="1"/>
     <col min="21" max="21" width="100" style="1" customWidth="1"/>
     <col min="22" max="22" width="9.109375" style="1" customWidth="1"/>
     <col min="23" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:20" ht="14.4" customHeight="1">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="18" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="19" t="s">
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20" t="s">
+      <c r="J1" s="23"/>
+      <c r="K1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16" t="s">
+      <c r="L1" s="24"/>
+    </row>
+    <row r="2" spans="1:20" ht="14.4" customHeight="1">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+    </row>
+    <row r="3" spans="1:20" ht="19.8" customHeight="1">
+      <c r="B3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="16" t="s">
+      <c r="E3" s="17"/>
+      <c r="F3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="P3" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="26" t="s">
+      <c r="Q3" s="26"/>
+      <c r="R3" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="25" t="s">
+      <c r="S3" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="25"/>
-    </row>
-    <row r="4" spans="1:20" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="23" t="s">
+      <c r="T3" s="17"/>
+    </row>
+    <row r="4" spans="1:20" ht="32.4" customHeight="1">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="23" t="s">
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="22" t="s">
+      <c r="Q4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="R4" s="27"/>
-      <c r="S4" s="23" t="s">
+      <c r="R4" s="20"/>
+      <c r="S4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="T4" s="22" t="s">
+      <c r="T4" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20">
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="7"/>
-      <c r="T5" s="1"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E5" s="3"/>
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" spans="1:20">
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="T6" s="1"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:20">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="9"/>
-      <c r="T7" s="1"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="D7" s="7"/>
+      <c r="E7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="8"/>
+    </row>
+    <row r="8" spans="1:20">
       <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="T8" s="1"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:20">
       <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="T9" s="1"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:20">
       <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="T10" s="1"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:20">
       <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:20">
       <c r="B12" s="1">
         <v>8</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="T12" s="1"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:20">
       <c r="B13" s="1">
         <v>9</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="T13" s="1"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:20">
       <c r="B14" s="1">
         <v>10</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="T14" s="1"/>
-    </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" ht="15" customHeight="1">
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="T15" s="1"/>
-    </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="9"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" ht="15" customHeight="1">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="T16" s="1"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C16" s="9"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="2:19">
       <c r="B17" s="1">
         <v>13</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="T17" s="1"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="2:19">
       <c r="B18" s="1">
         <v>14</v>
       </c>
-      <c r="T18" s="1"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="2:19">
       <c r="B19" s="1">
         <v>15</v>
       </c>
-      <c r="T19" s="1"/>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="2:19">
       <c r="B20" s="1">
         <v>16</v>
       </c>
-      <c r="T20" s="1"/>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="2:19">
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
       <c r="P21" s="11"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="13"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="12"/>
       <c r="S21" s="11"/>
-      <c r="T21" s="1"/>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="2:19">
       <c r="B22" s="1">
         <v>18</v>
       </c>
-      <c r="T22" s="1"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="2:19">
       <c r="B23" s="1">
         <v>19</v>
       </c>
-      <c r="T23" s="1"/>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="2:19">
       <c r="B24" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="2:19">
       <c r="B25" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="2:19">
       <c r="B26" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="2:19">
       <c r="B27" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="2:19">
       <c r="B28" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="2:19">
       <c r="B29" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="2:19">
       <c r="B30" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="2:19">
       <c r="B31" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="2:19">
       <c r="B32" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="2:5">
       <c r="B33" s="1">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="2:5">
       <c r="B34" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="2:5">
       <c r="B35" s="1">
         <v>31</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="2:5">
       <c r="B36" s="1">
         <v>32</v>
       </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="2:5">
       <c r="B37" s="1">
         <v>33</v>
       </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" spans="2:5">
       <c r="B38" s="1">
         <v>34</v>
       </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" spans="2:5">
       <c r="B39" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="2:5">
       <c r="B40" s="1">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="2:5">
       <c r="B41" s="1">
         <v>37</v>
       </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="2:5">
       <c r="B42" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="2:5">
       <c r="B43" s="1">
         <v>39</v>
       </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="2:5">
       <c r="B44" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="2:5">
       <c r="B45" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="2:5">
       <c r="B46" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="2:5">
       <c r="B47" s="1">
         <v>43</v>
       </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="2:5">
       <c r="B48" s="1">
         <v>44</v>
       </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="2:5">
       <c r="B49" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="2:5">
       <c r="B50" s="1">
         <v>46</v>
       </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="2:5">
       <c r="B51" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="2:5">
       <c r="B52" s="1">
         <v>48</v>
       </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="2:5">
       <c r="B53" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="2:5">
       <c r="B54" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="2:5">
       <c r="B55" s="1">
         <v>51</v>
       </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="2:5">
       <c r="B56" s="1">
         <v>52</v>
       </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="2:5">
       <c r="B57" s="1">
         <v>53</v>
       </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="2:5">
       <c r="B58" s="1">
         <v>54</v>
       </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="2:5">
       <c r="B59" s="1">
         <v>55</v>
       </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="2:5">
       <c r="B60" s="1">
         <v>56</v>
       </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="2:5">
       <c r="B61" s="1">
         <v>57</v>
       </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" spans="2:5">
       <c r="B62" s="1">
         <v>58</v>
       </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" spans="2:5">
       <c r="B63" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E63" s="3"/>
+    </row>
+    <row r="64" spans="2:5">
       <c r="B64" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E64" s="3"/>
+    </row>
+    <row r="65" spans="2:5">
       <c r="B65" s="1">
         <v>61</v>
       </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" spans="2:5">
       <c r="B66" s="1">
         <v>62</v>
       </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="2:5">
       <c r="B67" s="1">
         <v>63</v>
       </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="2:5">
       <c r="B68" s="1">
         <v>64</v>
       </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" spans="2:5">
       <c r="B69" s="1">
         <v>65</v>
       </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E69" s="3"/>
+    </row>
+    <row r="70" spans="2:5">
       <c r="B70" s="1">
         <v>66</v>
       </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E70" s="3"/>
+    </row>
+    <row r="71" spans="2:5">
       <c r="B71" s="1">
         <v>67</v>
       </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E71" s="3"/>
+    </row>
+    <row r="72" spans="2:5">
       <c r="B72" s="1">
         <v>68</v>
       </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E72" s="3"/>
+    </row>
+    <row r="73" spans="2:5">
       <c r="B73" s="1">
         <v>69</v>
       </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E73" s="3"/>
+    </row>
+    <row r="74" spans="2:5">
       <c r="B74" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E74" s="3"/>
+    </row>
+    <row r="75" spans="2:5">
       <c r="B75" s="1">
         <v>71</v>
       </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E75" s="3"/>
+    </row>
+    <row r="76" spans="2:5">
       <c r="B76" s="1">
         <v>72</v>
       </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E76" s="3"/>
+    </row>
+    <row r="77" spans="2:5">
       <c r="B77" s="1">
         <v>73</v>
       </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" spans="2:5">
       <c r="B78" s="1">
         <v>74</v>
       </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" spans="2:5">
       <c r="B79" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" spans="2:5">
       <c r="B80" s="1">
         <v>76</v>
       </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" spans="2:5">
       <c r="B81" s="1">
         <v>77</v>
       </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" spans="2:5">
       <c r="B82" s="1">
         <v>78</v>
       </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" spans="2:5">
       <c r="B83" s="1">
         <v>79</v>
       </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="2:5">
       <c r="B84" s="1">
         <v>80</v>
       </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="2:5">
       <c r="B85" s="1">
         <v>81</v>
       </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" spans="2:5">
       <c r="B86" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" spans="2:5">
       <c r="B87" s="1">
         <v>83</v>
       </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E87" s="3"/>
+    </row>
+    <row r="88" spans="2:5">
       <c r="B88" s="1">
         <v>84</v>
       </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="2:5">
       <c r="B89" s="1">
         <v>85</v>
       </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" spans="2:5">
       <c r="B90" s="1">
         <v>86</v>
       </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" spans="2:5">
       <c r="B91" s="1">
         <v>87</v>
       </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E91" s="3"/>
+    </row>
+    <row r="92" spans="2:5">
       <c r="B92" s="1">
         <v>88</v>
       </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E92" s="3"/>
+    </row>
+    <row r="93" spans="2:5">
       <c r="B93" s="1">
         <v>89</v>
       </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" spans="2:5">
       <c r="B94" s="1">
         <v>90</v>
       </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E94" s="3"/>
+    </row>
+    <row r="95" spans="2:5">
       <c r="B95" s="1">
         <v>91</v>
       </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" spans="2:5">
       <c r="B96" s="1">
         <v>92</v>
       </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E96" s="3"/>
+    </row>
+    <row r="97" spans="2:5">
       <c r="B97" s="1">
         <v>93</v>
       </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E97" s="3"/>
+    </row>
+    <row r="98" spans="2:5">
       <c r="B98" s="1">
         <v>94</v>
       </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" spans="2:5">
       <c r="B99" s="1">
         <v>95</v>
       </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E99" s="3"/>
+    </row>
+    <row r="100" spans="2:5">
       <c r="B100" s="1">
         <v>96</v>
       </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E100" s="3"/>
+    </row>
+    <row r="101" spans="2:5">
       <c r="B101" s="1">
         <v>97</v>
       </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E101" s="3"/>
+    </row>
+    <row r="102" spans="2:5">
       <c r="B102" s="1">
         <v>98</v>
       </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E102" s="3"/>
+    </row>
+    <row r="103" spans="2:5">
       <c r="B103" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E103" s="3"/>
+    </row>
+    <row r="104" spans="2:5">
       <c r="B104" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E104" s="3"/>
+    </row>
+    <row r="105" spans="2:5">
       <c r="B105" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E105" s="3"/>
+    </row>
+    <row r="106" spans="2:5">
       <c r="B106" s="1">
         <v>102</v>
       </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E106" s="3"/>
+    </row>
+    <row r="107" spans="2:5">
       <c r="B107" s="1">
         <v>103</v>
       </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E107" s="3"/>
+    </row>
+    <row r="108" spans="2:5">
       <c r="B108" s="1">
         <v>104</v>
       </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E108" s="3"/>
+    </row>
+    <row r="109" spans="2:5">
       <c r="B109" s="1">
         <v>105</v>
       </c>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E109" s="3"/>
+    </row>
+    <row r="110" spans="2:5">
       <c r="B110" s="1">
         <v>106</v>
       </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E110" s="3"/>
+    </row>
+    <row r="111" spans="2:5">
       <c r="B111" s="1">
         <v>107</v>
       </c>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E111" s="3"/>
+    </row>
+    <row r="112" spans="2:5">
       <c r="B112" s="1">
         <v>108</v>
       </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E112" s="3"/>
+    </row>
+    <row r="113" spans="2:5">
       <c r="B113" s="1">
         <v>109</v>
       </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114" spans="2:5">
       <c r="B114" s="1">
         <v>110</v>
       </c>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115" spans="2:5">
       <c r="B115" s="1">
         <v>111</v>
       </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="2:5">
       <c r="B116" s="1">
         <v>112</v>
       </c>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="2:5">
       <c r="B117" s="1">
         <v>113</v>
       </c>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118" spans="2:5">
       <c r="B118" s="1">
         <v>114</v>
       </c>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="2:5">
       <c r="B119" s="1">
         <v>115</v>
       </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120" spans="2:5">
       <c r="B120" s="1">
         <v>116</v>
       </c>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121" spans="2:5">
       <c r="B121" s="1">
         <v>117</v>
       </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E121" s="3"/>
+    </row>
+    <row r="122" spans="2:5">
       <c r="B122" s="1">
         <v>118</v>
       </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E122" s="3"/>
+    </row>
+    <row r="123" spans="2:5">
       <c r="B123" s="1">
         <v>119</v>
       </c>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124" spans="2:5">
       <c r="B124" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E124" s="3"/>
+    </row>
+    <row r="125" spans="2:5">
       <c r="B125" s="1">
         <v>121</v>
       </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E125" s="3"/>
+    </row>
+    <row r="126" spans="2:5">
       <c r="B126" s="1">
         <v>122</v>
       </c>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127" spans="2:5">
       <c r="B127" s="1">
         <v>123</v>
       </c>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E127" s="3"/>
+    </row>
+    <row r="128" spans="2:5">
       <c r="B128" s="1">
         <v>124</v>
       </c>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="2:5">
       <c r="B129" s="1">
         <v>125</v>
       </c>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="2:5">
       <c r="B130" s="1">
         <v>126</v>
       </c>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="2:5">
       <c r="B131" s="1">
         <v>127</v>
       </c>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="2:5">
       <c r="B132" s="1">
         <v>128</v>
       </c>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="2:5">
       <c r="B133" s="1">
         <v>129</v>
       </c>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="2:5">
       <c r="B134" s="1">
         <v>130</v>
       </c>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="2:5">
       <c r="B135" s="1">
         <v>131</v>
       </c>
-    </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="2:5">
       <c r="B136" s="1">
         <v>132</v>
       </c>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="2:5">
       <c r="B137" s="1">
         <v>133</v>
       </c>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="2:5">
       <c r="B138" s="1">
         <v>134</v>
       </c>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="2:5">
       <c r="B139" s="1">
         <v>135</v>
       </c>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="2:5">
       <c r="B140" s="1">
         <v>136</v>
       </c>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="2:5">
       <c r="B141" s="1">
         <v>137</v>
       </c>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="2:5">
       <c r="B142" s="1">
         <v>138</v>
       </c>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="2:5">
       <c r="B143" s="1">
         <v>139</v>
       </c>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="2:5">
       <c r="B144" s="1">
         <v>140</v>
       </c>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="2:5">
       <c r="B145" s="1">
         <v>141</v>
       </c>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="2:5">
       <c r="B146" s="1">
         <v>142</v>
       </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="2:5">
       <c r="B147" s="1">
         <v>143</v>
       </c>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="2:5">
       <c r="B148" s="1">
         <v>144</v>
       </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="2:5">
       <c r="B149" s="1">
         <v>145</v>
       </c>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="2:5">
       <c r="B150" s="1">
         <v>146</v>
       </c>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="2:5">
       <c r="B151" s="1">
         <v>147</v>
       </c>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="2:5">
       <c r="B152" s="1">
         <v>148</v>
       </c>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="2:5">
       <c r="B153" s="1">
         <v>149</v>
       </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="2:5">
       <c r="B154" s="1">
         <v>150</v>
       </c>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="2:5">
       <c r="B155" s="1">
         <v>151</v>
       </c>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="2:5">
       <c r="B156" s="1">
         <v>152</v>
       </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="2:5">
       <c r="B157" s="1">
         <v>153</v>
       </c>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="2:5">
       <c r="B158" s="1">
         <v>154</v>
       </c>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="2:5">
       <c r="B159" s="1">
         <v>155</v>
       </c>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="2:5">
       <c r="B160" s="1">
         <v>156</v>
       </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="2:5">
       <c r="B161" s="1">
         <v>157</v>
       </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="2:5">
       <c r="B162" s="1">
         <v>158</v>
       </c>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="2:5">
       <c r="B163" s="1">
         <v>159</v>
       </c>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="2:5">
       <c r="B164" s="1">
         <v>160</v>
       </c>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="2:5">
       <c r="B165" s="1">
         <v>161</v>
       </c>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="2:5">
       <c r="B166" s="1">
         <v>162</v>
       </c>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="2:5">
       <c r="B167" s="1">
         <v>163</v>
       </c>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="2:5">
       <c r="B168" s="1">
         <v>164</v>
       </c>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="2:5">
       <c r="B169" s="1">
         <v>165</v>
       </c>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="2:5">
       <c r="B170" s="1">
         <v>166</v>
       </c>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="2:5">
       <c r="B171" s="1">
         <v>167</v>
       </c>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="2:5">
       <c r="B172" s="1">
         <v>168</v>
       </c>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="2:5">
       <c r="B173" s="1">
         <v>169</v>
       </c>
-    </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E173" s="3"/>
+    </row>
+    <row r="174" spans="2:5">
       <c r="B174" s="1">
         <v>170</v>
       </c>
-    </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E174" s="3"/>
+    </row>
+    <row r="175" spans="2:5">
       <c r="B175" s="1">
         <v>171</v>
       </c>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E175" s="3"/>
+    </row>
+    <row r="176" spans="2:5">
       <c r="B176" s="1">
         <v>172</v>
       </c>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E176" s="3"/>
+    </row>
+    <row r="177" spans="2:5">
       <c r="B177" s="1">
         <v>173</v>
       </c>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E177" s="3"/>
+    </row>
+    <row r="178" spans="2:5">
       <c r="B178" s="1">
         <v>174</v>
       </c>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E178" s="3"/>
+    </row>
+    <row r="179" spans="2:5">
       <c r="B179" s="1">
         <v>175</v>
       </c>
-    </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="2:5">
       <c r="B180" s="1">
         <v>176</v>
       </c>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E180" s="3"/>
+    </row>
+    <row r="181" spans="2:5">
       <c r="B181" s="1">
         <v>177</v>
       </c>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E181" s="3"/>
+    </row>
+    <row r="182" spans="2:5">
       <c r="B182" s="1">
         <v>178</v>
       </c>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E182" s="3"/>
+    </row>
+    <row r="183" spans="2:5">
       <c r="B183" s="1">
         <v>179</v>
       </c>
-    </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E183" s="3"/>
+    </row>
+    <row r="184" spans="2:5">
       <c r="B184" s="1">
         <v>180</v>
       </c>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E184" s="3"/>
+    </row>
+    <row r="185" spans="2:5">
       <c r="B185" s="1">
         <v>181</v>
       </c>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E185" s="3"/>
+    </row>
+    <row r="186" spans="2:5">
       <c r="B186" s="1">
         <v>182</v>
       </c>
-    </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E186" s="3"/>
+    </row>
+    <row r="187" spans="2:5">
       <c r="B187" s="1">
         <v>183</v>
       </c>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E187" s="3"/>
+    </row>
+    <row r="188" spans="2:5">
       <c r="B188" s="1">
         <v>184</v>
       </c>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E188" s="3"/>
+    </row>
+    <row r="189" spans="2:5">
       <c r="B189" s="1">
         <v>185</v>
       </c>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E189" s="3"/>
+    </row>
+    <row r="190" spans="2:5">
       <c r="B190" s="1">
         <v>186</v>
       </c>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E190" s="3"/>
+    </row>
+    <row r="191" spans="2:5">
       <c r="B191" s="1">
         <v>187</v>
       </c>
-    </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E191" s="3"/>
+    </row>
+    <row r="192" spans="2:5">
       <c r="B192" s="1">
         <v>188</v>
       </c>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E192" s="3"/>
+    </row>
+    <row r="193" spans="2:5">
       <c r="B193" s="1">
         <v>189</v>
       </c>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E193" s="3"/>
+    </row>
+    <row r="194" spans="2:5">
       <c r="B194" s="1">
         <v>190</v>
       </c>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E194" s="3"/>
+    </row>
+    <row r="195" spans="2:5">
       <c r="B195" s="1">
         <v>191</v>
       </c>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E195" s="3"/>
+    </row>
+    <row r="196" spans="2:5">
       <c r="B196" s="1">
         <v>192</v>
       </c>
-    </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E196" s="3"/>
+    </row>
+    <row r="197" spans="2:5">
       <c r="B197" s="1">
         <v>193</v>
       </c>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E197" s="3"/>
+    </row>
+    <row r="198" spans="2:5">
       <c r="B198" s="1">
         <v>194</v>
       </c>
-    </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E198" s="3"/>
+    </row>
+    <row r="199" spans="2:5">
       <c r="B199" s="1">
         <v>195</v>
       </c>
-    </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E199" s="3"/>
+    </row>
+    <row r="200" spans="2:5">
       <c r="B200" s="1">
         <v>196</v>
       </c>
-    </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E200" s="3"/>
+    </row>
+    <row r="201" spans="2:5">
       <c r="B201" s="1">
         <v>197</v>
       </c>
-    </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E201" s="3"/>
+    </row>
+    <row r="202" spans="2:5">
       <c r="B202" s="1">
         <v>198</v>
       </c>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E202" s="3"/>
+    </row>
+    <row r="203" spans="2:5">
       <c r="B203" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E203" s="3"/>
+    </row>
+    <row r="204" spans="2:5">
       <c r="B204" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E204" s="3"/>
+    </row>
+    <row r="205" spans="2:5">
       <c r="B205" s="1">
         <v>201</v>
       </c>
-    </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E205" s="3"/>
+    </row>
+    <row r="206" spans="2:5">
       <c r="B206" s="1">
         <v>202</v>
       </c>
-    </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E206" s="3"/>
+    </row>
+    <row r="207" spans="2:5">
       <c r="B207" s="1">
         <v>203</v>
       </c>
-    </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E207" s="3"/>
+    </row>
+    <row r="208" spans="2:5">
       <c r="B208" s="1">
         <v>204</v>
       </c>
-    </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E208" s="3"/>
+    </row>
+    <row r="209" spans="2:5">
       <c r="B209" s="1">
         <v>205</v>
       </c>
-    </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E209" s="3"/>
+    </row>
+    <row r="210" spans="2:5">
       <c r="B210" s="1">
         <v>206</v>
       </c>
-    </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E210" s="3"/>
+    </row>
+    <row r="211" spans="2:5">
       <c r="B211" s="1">
         <v>207</v>
       </c>
-    </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E211" s="3"/>
+    </row>
+    <row r="212" spans="2:5">
       <c r="B212" s="1">
         <v>208</v>
       </c>
-    </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E212" s="3"/>
+    </row>
+    <row r="213" spans="2:5">
       <c r="B213" s="1">
         <v>209</v>
       </c>
-    </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E213" s="3"/>
+    </row>
+    <row r="214" spans="2:5">
       <c r="B214" s="1">
         <v>210</v>
       </c>
-    </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E214" s="3"/>
+    </row>
+    <row r="215" spans="2:5">
       <c r="B215" s="1">
         <v>211</v>
       </c>
-    </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E215" s="3"/>
+    </row>
+    <row r="216" spans="2:5">
       <c r="B216" s="1">
         <v>212</v>
       </c>
-    </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E216" s="3"/>
+    </row>
+    <row r="217" spans="2:5">
       <c r="B217" s="1">
         <v>213</v>
       </c>
-    </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E217" s="3"/>
+    </row>
+    <row r="218" spans="2:5">
       <c r="B218" s="1">
         <v>214</v>
       </c>
-    </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E218" s="3"/>
+    </row>
+    <row r="219" spans="2:5">
       <c r="B219" s="1">
         <v>215</v>
       </c>
-    </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E219" s="3"/>
+    </row>
+    <row r="220" spans="2:5">
       <c r="B220" s="1">
         <v>216</v>
       </c>
-    </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E220" s="3"/>
+    </row>
+    <row r="221" spans="2:5">
       <c r="B221" s="1">
         <v>217</v>
       </c>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E221" s="3"/>
+    </row>
+    <row r="222" spans="2:5">
       <c r="B222" s="1">
         <v>218</v>
       </c>
-    </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E222" s="3"/>
+    </row>
+    <row r="223" spans="2:5">
       <c r="B223" s="1">
         <v>219</v>
       </c>
-    </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E223" s="3"/>
+    </row>
+    <row r="224" spans="2:5">
       <c r="B224" s="1">
         <v>220</v>
       </c>
-    </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E224" s="3"/>
+    </row>
+    <row r="225" spans="2:5">
       <c r="B225" s="1">
         <v>221</v>
       </c>
-    </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E225" s="3"/>
+    </row>
+    <row r="226" spans="2:5">
       <c r="B226" s="1">
         <v>222</v>
       </c>
-    </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E226" s="3"/>
+    </row>
+    <row r="227" spans="2:5">
       <c r="B227" s="1">
         <v>223</v>
       </c>
-    </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E227" s="3"/>
+    </row>
+    <row r="228" spans="2:5">
       <c r="B228" s="1">
         <v>224</v>
       </c>
-    </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E228" s="3"/>
+    </row>
+    <row r="229" spans="2:5">
       <c r="B229" s="1">
         <v>225</v>
       </c>
-    </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E229" s="3"/>
+    </row>
+    <row r="230" spans="2:5">
       <c r="B230" s="1">
         <v>226</v>
       </c>
-    </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E230" s="3"/>
+    </row>
+    <row r="231" spans="2:5">
       <c r="B231" s="1">
         <v>227</v>
       </c>
-    </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E231" s="3"/>
+    </row>
+    <row r="232" spans="2:5">
       <c r="B232" s="1">
         <v>228</v>
       </c>
-    </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E232" s="3"/>
+    </row>
+    <row r="233" spans="2:5">
       <c r="B233" s="1">
         <v>229</v>
       </c>
-    </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E233" s="3"/>
+    </row>
+    <row r="234" spans="2:5">
       <c r="B234" s="1">
         <v>230</v>
       </c>
-    </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E234" s="3"/>
+    </row>
+    <row r="235" spans="2:5">
       <c r="B235" s="1">
         <v>231</v>
       </c>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E235" s="3"/>
+    </row>
+    <row r="236" spans="2:5">
       <c r="B236" s="1">
         <v>232</v>
       </c>
-    </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E236" s="3"/>
+    </row>
+    <row r="237" spans="2:5">
       <c r="B237" s="1">
         <v>233</v>
       </c>
-    </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E237" s="3"/>
+    </row>
+    <row r="238" spans="2:5">
       <c r="B238" s="1">
         <v>234</v>
       </c>
-    </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E238" s="3"/>
+    </row>
+    <row r="239" spans="2:5">
       <c r="B239" s="1">
         <v>235</v>
       </c>
-    </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E239" s="3"/>
+    </row>
+    <row r="240" spans="2:5">
       <c r="B240" s="1">
         <v>236</v>
       </c>
-    </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E240" s="3"/>
+    </row>
+    <row r="241" spans="2:5">
       <c r="B241" s="1">
         <v>237</v>
       </c>
-    </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E241" s="3"/>
+    </row>
+    <row r="242" spans="2:5">
       <c r="B242" s="1">
         <v>238</v>
       </c>
-    </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E242" s="3"/>
+    </row>
+    <row r="243" spans="2:5">
       <c r="B243" s="1">
         <v>239</v>
       </c>
-    </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E243" s="3"/>
+    </row>
+    <row r="244" spans="2:5">
       <c r="B244" s="1">
         <v>240</v>
       </c>
-    </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E244" s="3"/>
+    </row>
+    <row r="245" spans="2:5">
       <c r="B245" s="1">
         <v>241</v>
       </c>
-    </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E245" s="3"/>
+    </row>
+    <row r="246" spans="2:5">
       <c r="B246" s="1">
         <v>242</v>
       </c>
-    </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E246" s="3"/>
+    </row>
+    <row r="247" spans="2:5">
       <c r="B247" s="1">
         <v>243</v>
       </c>
-    </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E247" s="3"/>
+    </row>
+    <row r="248" spans="2:5">
       <c r="B248" s="1">
         <v>244</v>
       </c>
-    </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E248" s="3"/>
+    </row>
+    <row r="249" spans="2:5">
       <c r="B249" s="1">
         <v>245</v>
       </c>
-    </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="E249" s="3"/>
+    </row>
+    <row r="250" spans="2:5">
       <c r="B250" s="1">
         <v>246</v>
       </c>
+      <c r="E250" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="P3:Q3"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -2282,43 +2553,38 @@
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="R3:R4"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
-    <mergeCell ref="P3:Q3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:S250">
     <cfRule type="expression" priority="6" stopIfTrue="1">
-      <formula>$Q5=""</formula>
+      <formula>$P5=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="7">
-      <formula>$Q5&lt;TODAY()</formula>
+    <cfRule type="expression" dxfId="11" priority="7">
+      <formula>$P5&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>OR($Q5-TODAY()=0, $Q5-TODAY()=1)</formula>
+    <cfRule type="expression" dxfId="10" priority="8">
+      <formula>OR($P5-TODAY()=0, $P5-TODAY()=1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="9">
-      <formula>AND($Q5-TODAY()&gt;=0, $Q5-TODAY()&lt;=3)</formula>
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>AND($P5-TODAY()&gt;=0, $P5-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="10">
-      <formula>AND($Q5-TODAY()&gt;=4, $Q5-TODAY()&lt;=7)</formula>
+    <cfRule type="expression" dxfId="8" priority="10">
+      <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:H43">
     <cfRule type="expression" priority="16">
       <formula>$Q44=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="17">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>$Q44&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18">
+    <cfRule type="expression" dxfId="14" priority="18">
       <formula>$Q44-TODAY()=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="19">
+    <cfRule type="expression" dxfId="13" priority="19">
       <formula>AND($Q44-TODAY()&gt;=0, $Q44-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="12" priority="20">
       <formula>AND($Q44-TODAY()&gt;=4, $Q44-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2330,7 +2596,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:J13"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.109375" customWidth="1"/>
     <col min="4" max="4" width="15.88671875" customWidth="1"/>
@@ -2339,25 +2605,25 @@
     <col min="10" max="12" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="14" t="s">
+    <row r="3" spans="2:10" ht="15" customHeight="1"/>
+    <row r="4" spans="2:10" ht="15" customHeight="1">
+      <c r="B4" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>21</v>
       </c>
@@ -2374,7 +2640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>40</v>
       </c>
@@ -2391,7 +2657,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
         <v>43</v>
       </c>
@@ -2408,7 +2674,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10">
       <c r="B8" t="s">
         <v>30</v>
       </c>
@@ -2425,7 +2691,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10">
       <c r="B9" t="s">
         <v>47</v>
       </c>
@@ -2439,7 +2705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10">
       <c r="D10" t="s">
         <v>49</v>
       </c>
@@ -2450,7 +2716,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10">
       <c r="F11" t="s">
         <v>52</v>
       </c>
@@ -2458,12 +2724,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10">
       <c r="J12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10">
       <c r="J13" t="s">
         <v>55</v>
       </c>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1274C825-DBAD-48F9-91B9-17FA606C9B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3037DBCB-7B68-43C9-9604-11134DA61C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -425,16 +425,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -455,8 +447,16 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -912,120 +912,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="23"/>
-      <c r="K1" s="24" t="s">
+      <c r="J1" s="21"/>
+      <c r="K1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="24"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3" spans="1:20" ht="19.8" customHeight="1">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="M3" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="P3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="19" t="s">
+      <c r="Q3" s="24"/>
+      <c r="R3" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="17"/>
+      <c r="T3" s="25"/>
     </row>
     <row r="4" spans="1:20" ht="32.4" customHeight="1">
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="15" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
       <c r="P4" s="15" t="s">
         <v>18</v>
       </c>
       <c r="Q4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="R4" s="20"/>
+      <c r="R4" s="28"/>
       <c r="S4" s="15" t="s">
         <v>18</v>
       </c>
@@ -1051,8 +1051,8 @@
         <v>3</v>
       </c>
       <c r="D7" s="7"/>
-      <c r="E7" s="27"/>
-      <c r="Q7" s="27"/>
+      <c r="E7" s="17"/>
+      <c r="Q7" s="17"/>
       <c r="R7" s="8"/>
     </row>
     <row r="8" spans="1:20">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="11"/>
-      <c r="E21" s="28"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
@@ -1153,7 +1153,7 @@
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
       <c r="P21" s="11"/>
-      <c r="Q21" s="28"/>
+      <c r="Q21" s="18"/>
       <c r="R21" s="12"/>
       <c r="S21" s="11"/>
     </row>
@@ -2533,11 +2533,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
-    <mergeCell ref="P3:Q3"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -2553,24 +2548,12 @@
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="R3:R4"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="P3:Q3"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:S250">
-    <cfRule type="expression" priority="6" stopIfTrue="1">
-      <formula>$P5=""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="7">
-      <formula>$P5&lt;TODAY()</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8">
-      <formula>OR($P5-TODAY()=0, $P5-TODAY()=1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="9">
-      <formula>AND($P5-TODAY()&gt;=0, $P5-TODAY()&lt;=3)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
-      <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G43:H43">
     <cfRule type="expression" priority="16">
       <formula>$Q44=""</formula>
@@ -2586,6 +2569,23 @@
     </cfRule>
     <cfRule type="expression" dxfId="12" priority="20">
       <formula>AND($Q44-TODAY()&gt;=4, $Q44-TODAY()&lt;=7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:T250">
+    <cfRule type="expression" priority="6" stopIfTrue="1">
+      <formula>$P5=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="7">
+      <formula>$P5&lt;TODAY()</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="8">
+      <formula>OR($P5-TODAY()=0, $P5-TODAY()=1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>AND($P5-TODAY()&gt;=0, $P5-TODAY()&lt;=3)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="10">
+      <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3037DBCB-7B68-43C9-9604-11134DA61C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781E55B5-77FF-4174-98AC-4B18FC1681C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -383,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -403,8 +403,6 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -425,8 +423,19 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -447,79 +456,11 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -912,124 +853,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22" t="s">
+      <c r="J1" s="22"/>
+      <c r="K1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="22"/>
+      <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
     </row>
     <row r="3" spans="1:20" ht="19.8" customHeight="1">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="26" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="I3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="M3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="N3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="O3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="23" t="s">
+      <c r="P3" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="27" t="s">
+      <c r="Q3" s="25"/>
+      <c r="R3" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="25" t="s">
+      <c r="S3" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="25"/>
+      <c r="T3" s="16"/>
     </row>
     <row r="4" spans="1:20" ht="32.4" customHeight="1">
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="15" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="15" t="s">
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="16" t="s">
+      <c r="Q4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="R4" s="28"/>
-      <c r="S4" s="15" t="s">
+      <c r="R4" s="19"/>
+      <c r="S4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="T4" s="16" t="s">
+      <c r="T4" s="14" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1050,10 +991,8 @@
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="8"/>
+      <c r="E7" s="3"/>
+      <c r="R7" s="6"/>
     </row>
     <row r="8" spans="1:20">
       <c r="B8" s="1">
@@ -1101,14 +1040,14 @@
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="9"/>
+      <c r="C15" s="7"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="9"/>
+      <c r="C16" s="7"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="2:19">
@@ -1139,23 +1078,23 @@
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="11"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="9"/>
     </row>
     <row r="22" spans="2:19">
       <c r="B22" s="1">
@@ -2533,6 +2472,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="P3:Q3"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -2548,44 +2492,39 @@
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="R3:R4"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
-    <mergeCell ref="P3:Q3"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:T250">
+    <cfRule type="expression" priority="6" stopIfTrue="1">
+      <formula>$P5=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>$P5&lt;TODAY()</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>OR($P5-TODAY()=0, $P5-TODAY()=1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND($P5-TODAY()&gt;=0, $P5-TODAY()&lt;=3)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="10">
+      <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G43:H43">
     <cfRule type="expression" priority="16">
       <formula>$Q44=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="17">
+    <cfRule type="expression" dxfId="3" priority="17">
       <formula>$Q44&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="18">
+    <cfRule type="expression" dxfId="2" priority="18">
       <formula>$Q44-TODAY()=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="19">
+    <cfRule type="expression" dxfId="1" priority="19">
       <formula>AND($Q44-TODAY()&gt;=0, $Q44-TODAY()&lt;=3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="20">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>AND($Q44-TODAY()&gt;=4, $Q44-TODAY()&lt;=7)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:T250">
-    <cfRule type="expression" priority="6" stopIfTrue="1">
-      <formula>$P5=""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="7">
-      <formula>$P5&lt;TODAY()</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8">
-      <formula>OR($P5-TODAY()=0, $P5-TODAY()=1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="9">
-      <formula>AND($P5-TODAY()&gt;=0, $P5-TODAY()&lt;=3)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
-      <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2607,19 +2546,19 @@
   <sheetData>
     <row r="3" spans="2:10" ht="15" customHeight="1"/>
     <row r="4" spans="2:10" ht="15" customHeight="1">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="12" t="s">
         <v>39</v>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781E55B5-77FF-4174-98AC-4B18FC1681C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A965254A-DC1A-4B9C-A193-46E2037ECC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,8 @@
     <sheet name="Requisições 2026" sheetId="1" r:id="rId1"/>
     <sheet name="DADOS" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="171027"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -88,6 +77,12 @@
     <t>LIMITE*</t>
   </si>
   <si>
+    <t>ESTADO</t>
+  </si>
+  <si>
+    <t>CONCLUSÃO</t>
+  </si>
+  <si>
     <t>DATA</t>
   </si>
   <si>
@@ -109,78 +104,78 @@
     <t>Diária</t>
   </si>
   <si>
+    <t>CCR-INVEST</t>
+  </si>
+  <si>
+    <t>Monitorização</t>
+  </si>
+  <si>
+    <t>Póvoa de Varzim</t>
+  </si>
+  <si>
+    <t>Lev. Topográfico</t>
+  </si>
+  <si>
+    <t>GROWNOR</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Maia</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>Guimarães</t>
+  </si>
+  <si>
+    <t>WEST-VIEW</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>VIA</t>
+  </si>
+  <si>
+    <t>CONCELHO</t>
+  </si>
+  <si>
+    <t>FREQUÊNCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE TRABALHO</t>
+  </si>
+  <si>
+    <t>EMPRESA</t>
+  </si>
+  <si>
+    <t>SMS</t>
+  </si>
+  <si>
+    <t>Semanal</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Mensal</t>
+  </si>
+  <si>
+    <t>Trimestral</t>
+  </si>
+  <si>
+    <t>Whatsapp</t>
+  </si>
+  <si>
+    <t>Semestral</t>
+  </si>
+  <si>
     <t>GRAU-ON</t>
   </si>
   <si>
-    <t>Lev. Topográfico</t>
-  </si>
-  <si>
-    <t>CCR-INVEST</t>
-  </si>
-  <si>
-    <t>Póvoa de Varzim</t>
-  </si>
-  <si>
-    <t>GROWNOR</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Maia</t>
-  </si>
-  <si>
-    <t>Guimarães</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>VIA</t>
-  </si>
-  <si>
-    <t>CONCELHO</t>
-  </si>
-  <si>
-    <t>FREQUÊNCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE TRABALHO</t>
-  </si>
-  <si>
-    <t>EMPRESA</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>Semanal</t>
-  </si>
-  <si>
-    <t>Monitorização</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Mensal</t>
-  </si>
-  <si>
-    <t>Trimestral</t>
-  </si>
-  <si>
-    <t>WEST-VIEW</t>
-  </si>
-  <si>
-    <t>Whatsapp</t>
-  </si>
-  <si>
-    <t>Semestral</t>
-  </si>
-  <si>
     <t>Porto</t>
   </si>
   <si>
@@ -200,12 +195,6 @@
   </si>
   <si>
     <t>EXTERNO</t>
-  </si>
-  <si>
-    <t>ESTADO</t>
-  </si>
-  <si>
-    <t>CONCLUSÃO</t>
   </si>
 </sst>
 </file>
@@ -213,8 +202,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="h:mm;@"/>
-    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -313,21 +302,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -379,13 +353,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -395,6 +387,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -412,32 +410,14 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -450,17 +430,113 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="20">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -832,8 +908,8 @@
   <cols>
     <col min="1" max="2" width="9.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" style="1" customWidth="1"/>
     <col min="7" max="8" width="20.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.33203125" style="1" customWidth="1"/>
@@ -842,10 +918,10 @@
     <col min="12" max="12" width="46" style="1" customWidth="1"/>
     <col min="13" max="14" width="45.33203125" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="15" style="5" customWidth="1"/>
+    <col min="16" max="16" width="15" style="2" customWidth="1"/>
     <col min="17" max="17" width="12.109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="10.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="12" style="5" customWidth="1"/>
+    <col min="18" max="18" width="10.77734375" style="4" customWidth="1"/>
+    <col min="19" max="19" width="12" style="2" customWidth="1"/>
     <col min="20" max="20" width="9.88671875" style="3" customWidth="1"/>
     <col min="21" max="21" width="100" style="1" customWidth="1"/>
     <col min="22" max="22" width="9.109375" style="1" customWidth="1"/>
@@ -853,1629 +929,2360 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="21" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="22" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="22"/>
-      <c r="K1" s="23" t="s">
+      <c r="J1" s="19"/>
+      <c r="K1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="23"/>
+      <c r="L1" s="20"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
     </row>
     <row r="3" spans="1:20" ht="19.8" customHeight="1">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="21"/>
+      <c r="F3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="24" t="s">
+      <c r="P3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="S3" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="T3" s="16"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" s="21"/>
     </row>
     <row r="4" spans="1:20" ht="32.4" customHeight="1">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q4" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" s="19"/>
-      <c r="S4" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="T4" s="14" t="s">
-        <v>19</v>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" s="26"/>
+      <c r="S4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="B5" s="1">
         <v>1</v>
       </c>
+      <c r="D5" s="8"/>
       <c r="E5" s="3"/>
-      <c r="R5" s="6"/>
+      <c r="P5" s="8"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="8"/>
     </row>
     <row r="6" spans="1:20">
       <c r="B6" s="1">
         <v>2</v>
       </c>
+      <c r="D6" s="8"/>
       <c r="E6" s="3"/>
+      <c r="P6" s="8"/>
+      <c r="S6" s="8"/>
     </row>
     <row r="7" spans="1:20">
       <c r="B7" s="1">
         <v>3</v>
       </c>
+      <c r="D7" s="8"/>
       <c r="E7" s="3"/>
-      <c r="R7" s="6"/>
+      <c r="P7" s="8"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="8"/>
     </row>
     <row r="8" spans="1:20">
       <c r="B8" s="1">
         <v>4</v>
       </c>
+      <c r="D8" s="8"/>
       <c r="E8" s="3"/>
+      <c r="P8" s="8"/>
+      <c r="S8" s="8"/>
     </row>
     <row r="9" spans="1:20">
       <c r="B9" s="1">
         <v>5</v>
       </c>
+      <c r="D9" s="8"/>
       <c r="E9" s="3"/>
+      <c r="P9" s="8"/>
+      <c r="S9" s="8"/>
     </row>
     <row r="10" spans="1:20">
       <c r="B10" s="1">
         <v>6</v>
       </c>
+      <c r="D10" s="8"/>
       <c r="E10" s="3"/>
+      <c r="P10" s="8"/>
+      <c r="S10" s="8"/>
     </row>
     <row r="11" spans="1:20">
       <c r="B11" s="1">
         <v>7</v>
       </c>
+      <c r="D11" s="8"/>
       <c r="E11" s="3"/>
+      <c r="P11" s="8"/>
+      <c r="S11" s="8"/>
     </row>
     <row r="12" spans="1:20">
       <c r="B12" s="1">
         <v>8</v>
       </c>
+      <c r="D12" s="8"/>
       <c r="E12" s="3"/>
+      <c r="P12" s="8"/>
+      <c r="S12" s="8"/>
     </row>
     <row r="13" spans="1:20">
       <c r="B13" s="1">
         <v>9</v>
       </c>
+      <c r="D13" s="8"/>
       <c r="E13" s="3"/>
+      <c r="P13" s="8"/>
+      <c r="S13" s="8"/>
     </row>
     <row r="14" spans="1:20">
       <c r="B14" s="1">
         <v>10</v>
       </c>
+      <c r="D14" s="8"/>
       <c r="E14" s="3"/>
+      <c r="P14" s="8"/>
+      <c r="S14" s="8"/>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1">
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="7"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="8"/>
       <c r="E15" s="3"/>
+      <c r="P15" s="8"/>
+      <c r="S15" s="8"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="7"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="3"/>
+      <c r="P16" s="8"/>
+      <c r="S16" s="8"/>
     </row>
     <row r="17" spans="2:19">
       <c r="B17" s="1">
         <v>13</v>
       </c>
+      <c r="D17" s="8"/>
       <c r="E17" s="3"/>
+      <c r="P17" s="8"/>
+      <c r="S17" s="8"/>
     </row>
     <row r="18" spans="2:19">
       <c r="B18" s="1">
         <v>14</v>
       </c>
+      <c r="D18" s="8"/>
       <c r="E18" s="3"/>
+      <c r="P18" s="8"/>
+      <c r="S18" s="8"/>
     </row>
     <row r="19" spans="2:19">
       <c r="B19" s="1">
         <v>15</v>
       </c>
+      <c r="D19" s="8"/>
       <c r="E19" s="3"/>
+      <c r="P19" s="8"/>
+      <c r="S19" s="8"/>
     </row>
     <row r="20" spans="2:19">
       <c r="B20" s="1">
         <v>16</v>
       </c>
+      <c r="D20" s="8"/>
       <c r="E20" s="3"/>
+      <c r="P20" s="8"/>
+      <c r="S20" s="8"/>
     </row>
     <row r="21" spans="2:19">
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="9"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="12"/>
     </row>
     <row r="22" spans="2:19">
       <c r="B22" s="1">
         <v>18</v>
       </c>
+      <c r="D22" s="8"/>
       <c r="E22" s="3"/>
+      <c r="P22" s="8"/>
+      <c r="S22" s="8"/>
     </row>
     <row r="23" spans="2:19">
       <c r="B23" s="1">
         <v>19</v>
       </c>
+      <c r="D23" s="8"/>
       <c r="E23" s="3"/>
+      <c r="P23" s="8"/>
+      <c r="S23" s="8"/>
     </row>
     <row r="24" spans="2:19">
       <c r="B24" s="1">
         <v>20</v>
       </c>
+      <c r="D24" s="8"/>
       <c r="E24" s="3"/>
+      <c r="P24" s="8"/>
+      <c r="S24" s="8"/>
     </row>
     <row r="25" spans="2:19">
       <c r="B25" s="1">
         <v>21</v>
       </c>
+      <c r="D25" s="8"/>
       <c r="E25" s="3"/>
+      <c r="P25" s="8"/>
+      <c r="S25" s="8"/>
     </row>
     <row r="26" spans="2:19">
       <c r="B26" s="1">
         <v>22</v>
       </c>
+      <c r="D26" s="8"/>
       <c r="E26" s="3"/>
+      <c r="P26" s="8"/>
+      <c r="S26" s="8"/>
     </row>
     <row r="27" spans="2:19">
       <c r="B27" s="1">
         <v>23</v>
       </c>
+      <c r="D27" s="8"/>
       <c r="E27" s="3"/>
+      <c r="P27" s="8"/>
+      <c r="S27" s="8"/>
     </row>
     <row r="28" spans="2:19">
       <c r="B28" s="1">
         <v>24</v>
       </c>
+      <c r="D28" s="8"/>
       <c r="E28" s="3"/>
+      <c r="P28" s="8"/>
+      <c r="S28" s="8"/>
     </row>
     <row r="29" spans="2:19">
       <c r="B29" s="1">
         <v>25</v>
       </c>
+      <c r="D29" s="8"/>
       <c r="E29" s="3"/>
+      <c r="P29" s="8"/>
+      <c r="S29" s="8"/>
     </row>
     <row r="30" spans="2:19">
       <c r="B30" s="1">
         <v>26</v>
       </c>
+      <c r="D30" s="8"/>
       <c r="E30" s="3"/>
+      <c r="P30" s="8"/>
+      <c r="S30" s="8"/>
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="1">
         <v>27</v>
       </c>
+      <c r="D31" s="8"/>
       <c r="E31" s="3"/>
+      <c r="P31" s="8"/>
+      <c r="S31" s="8"/>
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="1">
         <v>28</v>
       </c>
+      <c r="D32" s="8"/>
       <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="2:5">
+      <c r="P32" s="8"/>
+      <c r="S32" s="8"/>
+    </row>
+    <row r="33" spans="2:19">
       <c r="B33" s="1">
         <v>29</v>
       </c>
+      <c r="D33" s="8"/>
       <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="2:5">
+      <c r="P33" s="8"/>
+      <c r="S33" s="8"/>
+    </row>
+    <row r="34" spans="2:19">
       <c r="B34" s="1">
         <v>30</v>
       </c>
+      <c r="D34" s="8"/>
       <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="2:5">
+      <c r="P34" s="8"/>
+      <c r="S34" s="8"/>
+    </row>
+    <row r="35" spans="2:19">
       <c r="B35" s="1">
         <v>31</v>
       </c>
+      <c r="D35" s="8"/>
       <c r="E35" s="3"/>
-    </row>
-    <row r="36" spans="2:5">
+      <c r="P35" s="8"/>
+      <c r="S35" s="8"/>
+    </row>
+    <row r="36" spans="2:19">
       <c r="B36" s="1">
         <v>32</v>
       </c>
+      <c r="D36" s="8"/>
       <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="2:5">
+      <c r="P36" s="8"/>
+      <c r="S36" s="8"/>
+    </row>
+    <row r="37" spans="2:19">
       <c r="B37" s="1">
         <v>33</v>
       </c>
+      <c r="D37" s="8"/>
       <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="2:5">
+      <c r="P37" s="8"/>
+      <c r="S37" s="8"/>
+    </row>
+    <row r="38" spans="2:19">
       <c r="B38" s="1">
         <v>34</v>
       </c>
+      <c r="D38" s="8"/>
       <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="2:5">
+      <c r="P38" s="8"/>
+      <c r="S38" s="8"/>
+    </row>
+    <row r="39" spans="2:19">
       <c r="B39" s="1">
         <v>35</v>
       </c>
+      <c r="D39" s="8"/>
       <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="2:5">
+      <c r="P39" s="8"/>
+      <c r="S39" s="8"/>
+    </row>
+    <row r="40" spans="2:19">
       <c r="B40" s="1">
         <v>36</v>
       </c>
+      <c r="D40" s="8"/>
       <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="2:5">
+      <c r="P40" s="8"/>
+      <c r="S40" s="8"/>
+    </row>
+    <row r="41" spans="2:19">
       <c r="B41" s="1">
         <v>37</v>
       </c>
+      <c r="D41" s="8"/>
       <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="2:5">
+      <c r="P41" s="8"/>
+      <c r="S41" s="8"/>
+    </row>
+    <row r="42" spans="2:19">
       <c r="B42" s="1">
         <v>38</v>
       </c>
+      <c r="D42" s="8"/>
       <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="2:5">
+      <c r="P42" s="8"/>
+      <c r="S42" s="8"/>
+    </row>
+    <row r="43" spans="2:19">
       <c r="B43" s="1">
         <v>39</v>
       </c>
+      <c r="D43" s="8"/>
       <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="2:5">
+      <c r="P43" s="8"/>
+      <c r="S43" s="8"/>
+    </row>
+    <row r="44" spans="2:19">
       <c r="B44" s="1">
         <v>40</v>
       </c>
+      <c r="D44" s="8"/>
       <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="2:5">
+      <c r="P44" s="8"/>
+      <c r="S44" s="8"/>
+    </row>
+    <row r="45" spans="2:19">
       <c r="B45" s="1">
         <v>41</v>
       </c>
+      <c r="D45" s="8"/>
       <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="2:5">
+      <c r="P45" s="8"/>
+      <c r="S45" s="8"/>
+    </row>
+    <row r="46" spans="2:19">
       <c r="B46" s="1">
         <v>42</v>
       </c>
+      <c r="D46" s="8"/>
       <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="2:5">
+      <c r="P46" s="8"/>
+      <c r="S46" s="8"/>
+    </row>
+    <row r="47" spans="2:19">
       <c r="B47" s="1">
         <v>43</v>
       </c>
+      <c r="D47" s="8"/>
       <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="2:5">
+      <c r="P47" s="8"/>
+      <c r="S47" s="8"/>
+    </row>
+    <row r="48" spans="2:19">
       <c r="B48" s="1">
         <v>44</v>
       </c>
+      <c r="D48" s="8"/>
       <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="2:5">
+      <c r="P48" s="8"/>
+      <c r="S48" s="8"/>
+    </row>
+    <row r="49" spans="2:19">
       <c r="B49" s="1">
         <v>45</v>
       </c>
+      <c r="D49" s="8"/>
       <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="2:5">
+      <c r="P49" s="8"/>
+      <c r="S49" s="8"/>
+    </row>
+    <row r="50" spans="2:19">
       <c r="B50" s="1">
         <v>46</v>
       </c>
+      <c r="D50" s="8"/>
       <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="2:5">
+      <c r="P50" s="8"/>
+      <c r="S50" s="8"/>
+    </row>
+    <row r="51" spans="2:19">
       <c r="B51" s="1">
         <v>47</v>
       </c>
+      <c r="D51" s="8"/>
       <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="2:5">
+      <c r="P51" s="8"/>
+      <c r="S51" s="8"/>
+    </row>
+    <row r="52" spans="2:19">
       <c r="B52" s="1">
         <v>48</v>
       </c>
+      <c r="D52" s="8"/>
       <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="2:5">
+      <c r="P52" s="8"/>
+      <c r="S52" s="8"/>
+    </row>
+    <row r="53" spans="2:19">
       <c r="B53" s="1">
         <v>49</v>
       </c>
+      <c r="D53" s="8"/>
       <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="2:5">
+      <c r="P53" s="8"/>
+      <c r="S53" s="8"/>
+    </row>
+    <row r="54" spans="2:19">
       <c r="B54" s="1">
         <v>50</v>
       </c>
+      <c r="D54" s="8"/>
       <c r="E54" s="3"/>
-    </row>
-    <row r="55" spans="2:5">
+      <c r="P54" s="8"/>
+      <c r="S54" s="8"/>
+    </row>
+    <row r="55" spans="2:19">
       <c r="B55" s="1">
         <v>51</v>
       </c>
+      <c r="D55" s="8"/>
       <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="2:5">
+      <c r="P55" s="8"/>
+      <c r="S55" s="8"/>
+    </row>
+    <row r="56" spans="2:19">
       <c r="B56" s="1">
         <v>52</v>
       </c>
+      <c r="D56" s="8"/>
       <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="2:5">
+      <c r="P56" s="8"/>
+      <c r="S56" s="8"/>
+    </row>
+    <row r="57" spans="2:19">
       <c r="B57" s="1">
         <v>53</v>
       </c>
+      <c r="D57" s="8"/>
       <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="2:5">
+      <c r="P57" s="8"/>
+      <c r="S57" s="8"/>
+    </row>
+    <row r="58" spans="2:19">
       <c r="B58" s="1">
         <v>54</v>
       </c>
+      <c r="D58" s="8"/>
       <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="2:5">
+      <c r="P58" s="8"/>
+      <c r="S58" s="8"/>
+    </row>
+    <row r="59" spans="2:19">
       <c r="B59" s="1">
         <v>55</v>
       </c>
+      <c r="D59" s="8"/>
       <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="2:5">
+      <c r="P59" s="8"/>
+      <c r="S59" s="8"/>
+    </row>
+    <row r="60" spans="2:19">
       <c r="B60" s="1">
         <v>56</v>
       </c>
+      <c r="D60" s="8"/>
       <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="2:5">
+      <c r="P60" s="8"/>
+      <c r="S60" s="8"/>
+    </row>
+    <row r="61" spans="2:19">
       <c r="B61" s="1">
         <v>57</v>
       </c>
+      <c r="D61" s="8"/>
       <c r="E61" s="3"/>
-    </row>
-    <row r="62" spans="2:5">
+      <c r="P61" s="8"/>
+      <c r="S61" s="8"/>
+    </row>
+    <row r="62" spans="2:19">
       <c r="B62" s="1">
         <v>58</v>
       </c>
+      <c r="D62" s="8"/>
       <c r="E62" s="3"/>
-    </row>
-    <row r="63" spans="2:5">
+      <c r="P62" s="8"/>
+      <c r="S62" s="8"/>
+    </row>
+    <row r="63" spans="2:19">
       <c r="B63" s="1">
         <v>59</v>
       </c>
+      <c r="D63" s="8"/>
       <c r="E63" s="3"/>
-    </row>
-    <row r="64" spans="2:5">
+      <c r="P63" s="8"/>
+      <c r="S63" s="8"/>
+    </row>
+    <row r="64" spans="2:19">
       <c r="B64" s="1">
         <v>60</v>
       </c>
+      <c r="D64" s="8"/>
       <c r="E64" s="3"/>
-    </row>
-    <row r="65" spans="2:5">
+      <c r="P64" s="8"/>
+      <c r="S64" s="8"/>
+    </row>
+    <row r="65" spans="2:19">
       <c r="B65" s="1">
         <v>61</v>
       </c>
+      <c r="D65" s="8"/>
       <c r="E65" s="3"/>
-    </row>
-    <row r="66" spans="2:5">
+      <c r="P65" s="8"/>
+      <c r="S65" s="8"/>
+    </row>
+    <row r="66" spans="2:19">
       <c r="B66" s="1">
         <v>62</v>
       </c>
+      <c r="D66" s="8"/>
       <c r="E66" s="3"/>
-    </row>
-    <row r="67" spans="2:5">
+      <c r="P66" s="8"/>
+      <c r="S66" s="8"/>
+    </row>
+    <row r="67" spans="2:19">
       <c r="B67" s="1">
         <v>63</v>
       </c>
+      <c r="D67" s="8"/>
       <c r="E67" s="3"/>
-    </row>
-    <row r="68" spans="2:5">
+      <c r="P67" s="8"/>
+      <c r="S67" s="8"/>
+    </row>
+    <row r="68" spans="2:19">
       <c r="B68" s="1">
         <v>64</v>
       </c>
+      <c r="D68" s="8"/>
       <c r="E68" s="3"/>
-    </row>
-    <row r="69" spans="2:5">
+      <c r="P68" s="8"/>
+      <c r="S68" s="8"/>
+    </row>
+    <row r="69" spans="2:19">
       <c r="B69" s="1">
         <v>65</v>
       </c>
+      <c r="D69" s="8"/>
       <c r="E69" s="3"/>
-    </row>
-    <row r="70" spans="2:5">
+      <c r="P69" s="8"/>
+      <c r="S69" s="8"/>
+    </row>
+    <row r="70" spans="2:19">
       <c r="B70" s="1">
         <v>66</v>
       </c>
+      <c r="D70" s="8"/>
       <c r="E70" s="3"/>
-    </row>
-    <row r="71" spans="2:5">
+      <c r="P70" s="8"/>
+      <c r="S70" s="8"/>
+    </row>
+    <row r="71" spans="2:19">
       <c r="B71" s="1">
         <v>67</v>
       </c>
+      <c r="D71" s="8"/>
       <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="2:5">
+      <c r="P71" s="8"/>
+      <c r="S71" s="8"/>
+    </row>
+    <row r="72" spans="2:19">
       <c r="B72" s="1">
         <v>68</v>
       </c>
+      <c r="D72" s="8"/>
       <c r="E72" s="3"/>
-    </row>
-    <row r="73" spans="2:5">
+      <c r="P72" s="8"/>
+      <c r="S72" s="8"/>
+    </row>
+    <row r="73" spans="2:19">
       <c r="B73" s="1">
         <v>69</v>
       </c>
+      <c r="D73" s="8"/>
       <c r="E73" s="3"/>
-    </row>
-    <row r="74" spans="2:5">
+      <c r="P73" s="8"/>
+      <c r="S73" s="8"/>
+    </row>
+    <row r="74" spans="2:19">
       <c r="B74" s="1">
         <v>70</v>
       </c>
+      <c r="D74" s="8"/>
       <c r="E74" s="3"/>
-    </row>
-    <row r="75" spans="2:5">
+      <c r="P74" s="8"/>
+      <c r="S74" s="8"/>
+    </row>
+    <row r="75" spans="2:19">
       <c r="B75" s="1">
         <v>71</v>
       </c>
+      <c r="D75" s="8"/>
       <c r="E75" s="3"/>
-    </row>
-    <row r="76" spans="2:5">
+      <c r="P75" s="8"/>
+      <c r="S75" s="8"/>
+    </row>
+    <row r="76" spans="2:19">
       <c r="B76" s="1">
         <v>72</v>
       </c>
+      <c r="D76" s="8"/>
       <c r="E76" s="3"/>
-    </row>
-    <row r="77" spans="2:5">
+      <c r="P76" s="8"/>
+      <c r="S76" s="8"/>
+    </row>
+    <row r="77" spans="2:19">
       <c r="B77" s="1">
         <v>73</v>
       </c>
+      <c r="D77" s="8"/>
       <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="2:5">
+      <c r="P77" s="8"/>
+      <c r="S77" s="8"/>
+    </row>
+    <row r="78" spans="2:19">
       <c r="B78" s="1">
         <v>74</v>
       </c>
+      <c r="D78" s="8"/>
       <c r="E78" s="3"/>
-    </row>
-    <row r="79" spans="2:5">
+      <c r="P78" s="8"/>
+      <c r="S78" s="8"/>
+    </row>
+    <row r="79" spans="2:19">
       <c r="B79" s="1">
         <v>75</v>
       </c>
+      <c r="D79" s="8"/>
       <c r="E79" s="3"/>
-    </row>
-    <row r="80" spans="2:5">
+      <c r="P79" s="8"/>
+      <c r="S79" s="8"/>
+    </row>
+    <row r="80" spans="2:19">
       <c r="B80" s="1">
         <v>76</v>
       </c>
+      <c r="D80" s="8"/>
       <c r="E80" s="3"/>
-    </row>
-    <row r="81" spans="2:5">
+      <c r="P80" s="8"/>
+      <c r="S80" s="8"/>
+    </row>
+    <row r="81" spans="2:19">
       <c r="B81" s="1">
         <v>77</v>
       </c>
+      <c r="D81" s="8"/>
       <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="2:5">
+      <c r="P81" s="8"/>
+      <c r="S81" s="8"/>
+    </row>
+    <row r="82" spans="2:19">
       <c r="B82" s="1">
         <v>78</v>
       </c>
+      <c r="D82" s="8"/>
       <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="2:5">
+      <c r="P82" s="8"/>
+      <c r="S82" s="8"/>
+    </row>
+    <row r="83" spans="2:19">
       <c r="B83" s="1">
         <v>79</v>
       </c>
+      <c r="D83" s="8"/>
       <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="2:5">
+      <c r="P83" s="8"/>
+      <c r="S83" s="8"/>
+    </row>
+    <row r="84" spans="2:19">
       <c r="B84" s="1">
         <v>80</v>
       </c>
+      <c r="D84" s="8"/>
       <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="2:5">
+      <c r="P84" s="8"/>
+      <c r="S84" s="8"/>
+    </row>
+    <row r="85" spans="2:19">
       <c r="B85" s="1">
         <v>81</v>
       </c>
+      <c r="D85" s="8"/>
       <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="2:5">
+      <c r="P85" s="8"/>
+      <c r="S85" s="8"/>
+    </row>
+    <row r="86" spans="2:19">
       <c r="B86" s="1">
         <v>82</v>
       </c>
+      <c r="D86" s="8"/>
       <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="2:5">
+      <c r="P86" s="8"/>
+      <c r="S86" s="8"/>
+    </row>
+    <row r="87" spans="2:19">
       <c r="B87" s="1">
         <v>83</v>
       </c>
+      <c r="D87" s="8"/>
       <c r="E87" s="3"/>
-    </row>
-    <row r="88" spans="2:5">
+      <c r="P87" s="8"/>
+      <c r="S87" s="8"/>
+    </row>
+    <row r="88" spans="2:19">
       <c r="B88" s="1">
         <v>84</v>
       </c>
+      <c r="D88" s="8"/>
       <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="2:5">
+      <c r="P88" s="8"/>
+      <c r="S88" s="8"/>
+    </row>
+    <row r="89" spans="2:19">
       <c r="B89" s="1">
         <v>85</v>
       </c>
+      <c r="D89" s="8"/>
       <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="2:5">
+      <c r="P89" s="8"/>
+      <c r="S89" s="8"/>
+    </row>
+    <row r="90" spans="2:19">
       <c r="B90" s="1">
         <v>86</v>
       </c>
+      <c r="D90" s="8"/>
       <c r="E90" s="3"/>
-    </row>
-    <row r="91" spans="2:5">
+      <c r="P90" s="8"/>
+      <c r="S90" s="8"/>
+    </row>
+    <row r="91" spans="2:19">
       <c r="B91" s="1">
         <v>87</v>
       </c>
+      <c r="D91" s="8"/>
       <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="2:5">
+      <c r="P91" s="8"/>
+      <c r="S91" s="8"/>
+    </row>
+    <row r="92" spans="2:19">
       <c r="B92" s="1">
         <v>88</v>
       </c>
+      <c r="D92" s="8"/>
       <c r="E92" s="3"/>
-    </row>
-    <row r="93" spans="2:5">
+      <c r="P92" s="8"/>
+      <c r="S92" s="8"/>
+    </row>
+    <row r="93" spans="2:19">
       <c r="B93" s="1">
         <v>89</v>
       </c>
+      <c r="D93" s="8"/>
       <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="2:5">
+      <c r="P93" s="8"/>
+      <c r="S93" s="8"/>
+    </row>
+    <row r="94" spans="2:19">
       <c r="B94" s="1">
         <v>90</v>
       </c>
+      <c r="D94" s="8"/>
       <c r="E94" s="3"/>
-    </row>
-    <row r="95" spans="2:5">
+      <c r="P94" s="8"/>
+      <c r="S94" s="8"/>
+    </row>
+    <row r="95" spans="2:19">
       <c r="B95" s="1">
         <v>91</v>
       </c>
+      <c r="D95" s="8"/>
       <c r="E95" s="3"/>
-    </row>
-    <row r="96" spans="2:5">
+      <c r="P95" s="8"/>
+      <c r="S95" s="8"/>
+    </row>
+    <row r="96" spans="2:19">
       <c r="B96" s="1">
         <v>92</v>
       </c>
+      <c r="D96" s="8"/>
       <c r="E96" s="3"/>
-    </row>
-    <row r="97" spans="2:5">
+      <c r="P96" s="8"/>
+      <c r="S96" s="8"/>
+    </row>
+    <row r="97" spans="2:19">
       <c r="B97" s="1">
         <v>93</v>
       </c>
+      <c r="D97" s="8"/>
       <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="2:5">
+      <c r="P97" s="8"/>
+      <c r="S97" s="8"/>
+    </row>
+    <row r="98" spans="2:19">
       <c r="B98" s="1">
         <v>94</v>
       </c>
+      <c r="D98" s="8"/>
       <c r="E98" s="3"/>
-    </row>
-    <row r="99" spans="2:5">
+      <c r="P98" s="8"/>
+      <c r="S98" s="8"/>
+    </row>
+    <row r="99" spans="2:19">
       <c r="B99" s="1">
         <v>95</v>
       </c>
+      <c r="D99" s="8"/>
       <c r="E99" s="3"/>
-    </row>
-    <row r="100" spans="2:5">
+      <c r="P99" s="8"/>
+      <c r="S99" s="8"/>
+    </row>
+    <row r="100" spans="2:19">
       <c r="B100" s="1">
         <v>96</v>
       </c>
+      <c r="D100" s="8"/>
       <c r="E100" s="3"/>
-    </row>
-    <row r="101" spans="2:5">
+      <c r="P100" s="8"/>
+      <c r="S100" s="8"/>
+    </row>
+    <row r="101" spans="2:19">
       <c r="B101" s="1">
         <v>97</v>
       </c>
+      <c r="D101" s="8"/>
       <c r="E101" s="3"/>
-    </row>
-    <row r="102" spans="2:5">
+      <c r="P101" s="8"/>
+      <c r="S101" s="8"/>
+    </row>
+    <row r="102" spans="2:19">
       <c r="B102" s="1">
         <v>98</v>
       </c>
+      <c r="D102" s="8"/>
       <c r="E102" s="3"/>
-    </row>
-    <row r="103" spans="2:5">
+      <c r="P102" s="8"/>
+      <c r="S102" s="8"/>
+    </row>
+    <row r="103" spans="2:19">
       <c r="B103" s="1">
         <v>99</v>
       </c>
+      <c r="D103" s="8"/>
       <c r="E103" s="3"/>
-    </row>
-    <row r="104" spans="2:5">
+      <c r="P103" s="8"/>
+      <c r="S103" s="8"/>
+    </row>
+    <row r="104" spans="2:19">
       <c r="B104" s="1">
         <v>100</v>
       </c>
+      <c r="D104" s="8"/>
       <c r="E104" s="3"/>
-    </row>
-    <row r="105" spans="2:5">
+      <c r="P104" s="8"/>
+      <c r="S104" s="8"/>
+    </row>
+    <row r="105" spans="2:19">
       <c r="B105" s="1">
         <v>101</v>
       </c>
+      <c r="D105" s="8"/>
       <c r="E105" s="3"/>
-    </row>
-    <row r="106" spans="2:5">
+      <c r="P105" s="8"/>
+      <c r="S105" s="8"/>
+    </row>
+    <row r="106" spans="2:19">
       <c r="B106" s="1">
         <v>102</v>
       </c>
+      <c r="D106" s="8"/>
       <c r="E106" s="3"/>
-    </row>
-    <row r="107" spans="2:5">
+      <c r="P106" s="8"/>
+      <c r="S106" s="8"/>
+    </row>
+    <row r="107" spans="2:19">
       <c r="B107" s="1">
         <v>103</v>
       </c>
+      <c r="D107" s="8"/>
       <c r="E107" s="3"/>
-    </row>
-    <row r="108" spans="2:5">
+      <c r="P107" s="8"/>
+      <c r="S107" s="8"/>
+    </row>
+    <row r="108" spans="2:19">
       <c r="B108" s="1">
         <v>104</v>
       </c>
+      <c r="D108" s="8"/>
       <c r="E108" s="3"/>
-    </row>
-    <row r="109" spans="2:5">
+      <c r="P108" s="8"/>
+      <c r="S108" s="8"/>
+    </row>
+    <row r="109" spans="2:19">
       <c r="B109" s="1">
         <v>105</v>
       </c>
+      <c r="D109" s="8"/>
       <c r="E109" s="3"/>
-    </row>
-    <row r="110" spans="2:5">
+      <c r="P109" s="8"/>
+      <c r="S109" s="8"/>
+    </row>
+    <row r="110" spans="2:19">
       <c r="B110" s="1">
         <v>106</v>
       </c>
+      <c r="D110" s="8"/>
       <c r="E110" s="3"/>
-    </row>
-    <row r="111" spans="2:5">
+      <c r="P110" s="8"/>
+      <c r="S110" s="8"/>
+    </row>
+    <row r="111" spans="2:19">
       <c r="B111" s="1">
         <v>107</v>
       </c>
+      <c r="D111" s="8"/>
       <c r="E111" s="3"/>
-    </row>
-    <row r="112" spans="2:5">
+      <c r="P111" s="8"/>
+      <c r="S111" s="8"/>
+    </row>
+    <row r="112" spans="2:19">
       <c r="B112" s="1">
         <v>108</v>
       </c>
+      <c r="D112" s="8"/>
       <c r="E112" s="3"/>
-    </row>
-    <row r="113" spans="2:5">
+      <c r="P112" s="8"/>
+      <c r="S112" s="8"/>
+    </row>
+    <row r="113" spans="2:19">
       <c r="B113" s="1">
         <v>109</v>
       </c>
+      <c r="D113" s="8"/>
       <c r="E113" s="3"/>
-    </row>
-    <row r="114" spans="2:5">
+      <c r="P113" s="8"/>
+      <c r="S113" s="8"/>
+    </row>
+    <row r="114" spans="2:19">
       <c r="B114" s="1">
         <v>110</v>
       </c>
+      <c r="D114" s="8"/>
       <c r="E114" s="3"/>
-    </row>
-    <row r="115" spans="2:5">
+      <c r="P114" s="8"/>
+      <c r="S114" s="8"/>
+    </row>
+    <row r="115" spans="2:19">
       <c r="B115" s="1">
         <v>111</v>
       </c>
+      <c r="D115" s="8"/>
       <c r="E115" s="3"/>
-    </row>
-    <row r="116" spans="2:5">
+      <c r="P115" s="8"/>
+      <c r="S115" s="8"/>
+    </row>
+    <row r="116" spans="2:19">
       <c r="B116" s="1">
         <v>112</v>
       </c>
+      <c r="D116" s="8"/>
       <c r="E116" s="3"/>
-    </row>
-    <row r="117" spans="2:5">
+      <c r="P116" s="8"/>
+      <c r="S116" s="8"/>
+    </row>
+    <row r="117" spans="2:19">
       <c r="B117" s="1">
         <v>113</v>
       </c>
+      <c r="D117" s="8"/>
       <c r="E117" s="3"/>
-    </row>
-    <row r="118" spans="2:5">
+      <c r="P117" s="8"/>
+      <c r="S117" s="8"/>
+    </row>
+    <row r="118" spans="2:19">
       <c r="B118" s="1">
         <v>114</v>
       </c>
+      <c r="D118" s="8"/>
       <c r="E118" s="3"/>
-    </row>
-    <row r="119" spans="2:5">
+      <c r="P118" s="8"/>
+      <c r="S118" s="8"/>
+    </row>
+    <row r="119" spans="2:19">
       <c r="B119" s="1">
         <v>115</v>
       </c>
+      <c r="D119" s="8"/>
       <c r="E119" s="3"/>
-    </row>
-    <row r="120" spans="2:5">
+      <c r="P119" s="8"/>
+      <c r="S119" s="8"/>
+    </row>
+    <row r="120" spans="2:19">
       <c r="B120" s="1">
         <v>116</v>
       </c>
+      <c r="D120" s="8"/>
       <c r="E120" s="3"/>
-    </row>
-    <row r="121" spans="2:5">
+      <c r="P120" s="8"/>
+      <c r="S120" s="8"/>
+    </row>
+    <row r="121" spans="2:19">
       <c r="B121" s="1">
         <v>117</v>
       </c>
+      <c r="D121" s="8"/>
       <c r="E121" s="3"/>
-    </row>
-    <row r="122" spans="2:5">
+      <c r="P121" s="8"/>
+      <c r="S121" s="8"/>
+    </row>
+    <row r="122" spans="2:19">
       <c r="B122" s="1">
         <v>118</v>
       </c>
+      <c r="D122" s="8"/>
       <c r="E122" s="3"/>
-    </row>
-    <row r="123" spans="2:5">
+      <c r="P122" s="8"/>
+      <c r="S122" s="8"/>
+    </row>
+    <row r="123" spans="2:19">
       <c r="B123" s="1">
         <v>119</v>
       </c>
+      <c r="D123" s="8"/>
       <c r="E123" s="3"/>
-    </row>
-    <row r="124" spans="2:5">
+      <c r="P123" s="8"/>
+      <c r="S123" s="8"/>
+    </row>
+    <row r="124" spans="2:19">
       <c r="B124" s="1">
         <v>120</v>
       </c>
+      <c r="D124" s="8"/>
       <c r="E124" s="3"/>
-    </row>
-    <row r="125" spans="2:5">
+      <c r="P124" s="8"/>
+      <c r="S124" s="8"/>
+    </row>
+    <row r="125" spans="2:19">
       <c r="B125" s="1">
         <v>121</v>
       </c>
+      <c r="D125" s="8"/>
       <c r="E125" s="3"/>
-    </row>
-    <row r="126" spans="2:5">
+      <c r="P125" s="8"/>
+      <c r="S125" s="8"/>
+    </row>
+    <row r="126" spans="2:19">
       <c r="B126" s="1">
         <v>122</v>
       </c>
+      <c r="D126" s="8"/>
       <c r="E126" s="3"/>
-    </row>
-    <row r="127" spans="2:5">
+      <c r="P126" s="8"/>
+      <c r="S126" s="8"/>
+    </row>
+    <row r="127" spans="2:19">
       <c r="B127" s="1">
         <v>123</v>
       </c>
+      <c r="D127" s="8"/>
       <c r="E127" s="3"/>
-    </row>
-    <row r="128" spans="2:5">
+      <c r="P127" s="8"/>
+      <c r="S127" s="8"/>
+    </row>
+    <row r="128" spans="2:19">
       <c r="B128" s="1">
         <v>124</v>
       </c>
+      <c r="D128" s="8"/>
       <c r="E128" s="3"/>
-    </row>
-    <row r="129" spans="2:5">
+      <c r="P128" s="8"/>
+      <c r="S128" s="8"/>
+    </row>
+    <row r="129" spans="2:19">
       <c r="B129" s="1">
         <v>125</v>
       </c>
+      <c r="D129" s="8"/>
       <c r="E129" s="3"/>
-    </row>
-    <row r="130" spans="2:5">
+      <c r="P129" s="8"/>
+      <c r="S129" s="8"/>
+    </row>
+    <row r="130" spans="2:19">
       <c r="B130" s="1">
         <v>126</v>
       </c>
+      <c r="D130" s="8"/>
       <c r="E130" s="3"/>
-    </row>
-    <row r="131" spans="2:5">
+      <c r="P130" s="8"/>
+      <c r="S130" s="8"/>
+    </row>
+    <row r="131" spans="2:19">
       <c r="B131" s="1">
         <v>127</v>
       </c>
+      <c r="D131" s="8"/>
       <c r="E131" s="3"/>
-    </row>
-    <row r="132" spans="2:5">
+      <c r="P131" s="8"/>
+      <c r="S131" s="8"/>
+    </row>
+    <row r="132" spans="2:19">
       <c r="B132" s="1">
         <v>128</v>
       </c>
+      <c r="D132" s="8"/>
       <c r="E132" s="3"/>
-    </row>
-    <row r="133" spans="2:5">
+      <c r="P132" s="8"/>
+      <c r="S132" s="8"/>
+    </row>
+    <row r="133" spans="2:19">
       <c r="B133" s="1">
         <v>129</v>
       </c>
+      <c r="D133" s="8"/>
       <c r="E133" s="3"/>
-    </row>
-    <row r="134" spans="2:5">
+      <c r="P133" s="8"/>
+      <c r="S133" s="8"/>
+    </row>
+    <row r="134" spans="2:19">
       <c r="B134" s="1">
         <v>130</v>
       </c>
+      <c r="D134" s="8"/>
       <c r="E134" s="3"/>
-    </row>
-    <row r="135" spans="2:5">
+      <c r="P134" s="8"/>
+      <c r="S134" s="8"/>
+    </row>
+    <row r="135" spans="2:19">
       <c r="B135" s="1">
         <v>131</v>
       </c>
+      <c r="D135" s="8"/>
       <c r="E135" s="3"/>
-    </row>
-    <row r="136" spans="2:5">
+      <c r="P135" s="8"/>
+      <c r="S135" s="8"/>
+    </row>
+    <row r="136" spans="2:19">
       <c r="B136" s="1">
         <v>132</v>
       </c>
+      <c r="D136" s="8"/>
       <c r="E136" s="3"/>
-    </row>
-    <row r="137" spans="2:5">
+      <c r="P136" s="8"/>
+      <c r="S136" s="8"/>
+    </row>
+    <row r="137" spans="2:19">
       <c r="B137" s="1">
         <v>133</v>
       </c>
+      <c r="D137" s="8"/>
       <c r="E137" s="3"/>
-    </row>
-    <row r="138" spans="2:5">
+      <c r="P137" s="8"/>
+      <c r="S137" s="8"/>
+    </row>
+    <row r="138" spans="2:19">
       <c r="B138" s="1">
         <v>134</v>
       </c>
+      <c r="D138" s="8"/>
       <c r="E138" s="3"/>
-    </row>
-    <row r="139" spans="2:5">
+      <c r="P138" s="8"/>
+      <c r="S138" s="8"/>
+    </row>
+    <row r="139" spans="2:19">
       <c r="B139" s="1">
         <v>135</v>
       </c>
+      <c r="D139" s="8"/>
       <c r="E139" s="3"/>
-    </row>
-    <row r="140" spans="2:5">
+      <c r="P139" s="8"/>
+      <c r="S139" s="8"/>
+    </row>
+    <row r="140" spans="2:19">
       <c r="B140" s="1">
         <v>136</v>
       </c>
+      <c r="D140" s="8"/>
       <c r="E140" s="3"/>
-    </row>
-    <row r="141" spans="2:5">
+      <c r="P140" s="8"/>
+      <c r="S140" s="8"/>
+    </row>
+    <row r="141" spans="2:19">
       <c r="B141" s="1">
         <v>137</v>
       </c>
+      <c r="D141" s="8"/>
       <c r="E141" s="3"/>
-    </row>
-    <row r="142" spans="2:5">
+      <c r="P141" s="8"/>
+      <c r="S141" s="8"/>
+    </row>
+    <row r="142" spans="2:19">
       <c r="B142" s="1">
         <v>138</v>
       </c>
+      <c r="D142" s="8"/>
       <c r="E142" s="3"/>
-    </row>
-    <row r="143" spans="2:5">
+      <c r="P142" s="8"/>
+      <c r="S142" s="8"/>
+    </row>
+    <row r="143" spans="2:19">
       <c r="B143" s="1">
         <v>139</v>
       </c>
+      <c r="D143" s="8"/>
       <c r="E143" s="3"/>
-    </row>
-    <row r="144" spans="2:5">
+      <c r="P143" s="8"/>
+      <c r="S143" s="8"/>
+    </row>
+    <row r="144" spans="2:19">
       <c r="B144" s="1">
         <v>140</v>
       </c>
+      <c r="D144" s="8"/>
       <c r="E144" s="3"/>
-    </row>
-    <row r="145" spans="2:5">
+      <c r="P144" s="8"/>
+      <c r="S144" s="8"/>
+    </row>
+    <row r="145" spans="2:19">
       <c r="B145" s="1">
         <v>141</v>
       </c>
+      <c r="D145" s="8"/>
       <c r="E145" s="3"/>
-    </row>
-    <row r="146" spans="2:5">
+      <c r="P145" s="8"/>
+      <c r="S145" s="8"/>
+    </row>
+    <row r="146" spans="2:19">
       <c r="B146" s="1">
         <v>142</v>
       </c>
+      <c r="D146" s="8"/>
       <c r="E146" s="3"/>
-    </row>
-    <row r="147" spans="2:5">
+      <c r="P146" s="8"/>
+      <c r="S146" s="8"/>
+    </row>
+    <row r="147" spans="2:19">
       <c r="B147" s="1">
         <v>143</v>
       </c>
+      <c r="D147" s="8"/>
       <c r="E147" s="3"/>
-    </row>
-    <row r="148" spans="2:5">
+      <c r="P147" s="8"/>
+      <c r="S147" s="8"/>
+    </row>
+    <row r="148" spans="2:19">
       <c r="B148" s="1">
         <v>144</v>
       </c>
+      <c r="D148" s="8"/>
       <c r="E148" s="3"/>
-    </row>
-    <row r="149" spans="2:5">
+      <c r="P148" s="8"/>
+      <c r="S148" s="8"/>
+    </row>
+    <row r="149" spans="2:19">
       <c r="B149" s="1">
         <v>145</v>
       </c>
+      <c r="D149" s="8"/>
       <c r="E149" s="3"/>
-    </row>
-    <row r="150" spans="2:5">
+      <c r="P149" s="8"/>
+      <c r="S149" s="8"/>
+    </row>
+    <row r="150" spans="2:19">
       <c r="B150" s="1">
         <v>146</v>
       </c>
+      <c r="D150" s="8"/>
       <c r="E150" s="3"/>
-    </row>
-    <row r="151" spans="2:5">
+      <c r="P150" s="8"/>
+      <c r="S150" s="8"/>
+    </row>
+    <row r="151" spans="2:19">
       <c r="B151" s="1">
         <v>147</v>
       </c>
+      <c r="D151" s="8"/>
       <c r="E151" s="3"/>
-    </row>
-    <row r="152" spans="2:5">
+      <c r="P151" s="8"/>
+      <c r="S151" s="8"/>
+    </row>
+    <row r="152" spans="2:19">
       <c r="B152" s="1">
         <v>148</v>
       </c>
+      <c r="D152" s="8"/>
       <c r="E152" s="3"/>
-    </row>
-    <row r="153" spans="2:5">
+      <c r="P152" s="8"/>
+      <c r="S152" s="8"/>
+    </row>
+    <row r="153" spans="2:19">
       <c r="B153" s="1">
         <v>149</v>
       </c>
+      <c r="D153" s="8"/>
       <c r="E153" s="3"/>
-    </row>
-    <row r="154" spans="2:5">
+      <c r="P153" s="8"/>
+      <c r="S153" s="8"/>
+    </row>
+    <row r="154" spans="2:19">
       <c r="B154" s="1">
         <v>150</v>
       </c>
+      <c r="D154" s="8"/>
       <c r="E154" s="3"/>
-    </row>
-    <row r="155" spans="2:5">
+      <c r="P154" s="8"/>
+      <c r="S154" s="8"/>
+    </row>
+    <row r="155" spans="2:19">
       <c r="B155" s="1">
         <v>151</v>
       </c>
+      <c r="D155" s="8"/>
       <c r="E155" s="3"/>
-    </row>
-    <row r="156" spans="2:5">
+      <c r="P155" s="8"/>
+      <c r="S155" s="8"/>
+    </row>
+    <row r="156" spans="2:19">
       <c r="B156" s="1">
         <v>152</v>
       </c>
+      <c r="D156" s="8"/>
       <c r="E156" s="3"/>
-    </row>
-    <row r="157" spans="2:5">
+      <c r="P156" s="8"/>
+      <c r="S156" s="8"/>
+    </row>
+    <row r="157" spans="2:19">
       <c r="B157" s="1">
         <v>153</v>
       </c>
+      <c r="D157" s="8"/>
       <c r="E157" s="3"/>
-    </row>
-    <row r="158" spans="2:5">
+      <c r="P157" s="8"/>
+      <c r="S157" s="8"/>
+    </row>
+    <row r="158" spans="2:19">
       <c r="B158" s="1">
         <v>154</v>
       </c>
+      <c r="D158" s="8"/>
       <c r="E158" s="3"/>
-    </row>
-    <row r="159" spans="2:5">
+      <c r="P158" s="8"/>
+      <c r="S158" s="8"/>
+    </row>
+    <row r="159" spans="2:19">
       <c r="B159" s="1">
         <v>155</v>
       </c>
+      <c r="D159" s="8"/>
       <c r="E159" s="3"/>
-    </row>
-    <row r="160" spans="2:5">
+      <c r="P159" s="8"/>
+      <c r="S159" s="8"/>
+    </row>
+    <row r="160" spans="2:19">
       <c r="B160" s="1">
         <v>156</v>
       </c>
+      <c r="D160" s="8"/>
       <c r="E160" s="3"/>
-    </row>
-    <row r="161" spans="2:5">
+      <c r="P160" s="8"/>
+      <c r="S160" s="8"/>
+    </row>
+    <row r="161" spans="2:19">
       <c r="B161" s="1">
         <v>157</v>
       </c>
+      <c r="D161" s="8"/>
       <c r="E161" s="3"/>
-    </row>
-    <row r="162" spans="2:5">
+      <c r="P161" s="8"/>
+      <c r="S161" s="8"/>
+    </row>
+    <row r="162" spans="2:19">
       <c r="B162" s="1">
         <v>158</v>
       </c>
+      <c r="D162" s="8"/>
       <c r="E162" s="3"/>
-    </row>
-    <row r="163" spans="2:5">
+      <c r="P162" s="8"/>
+      <c r="S162" s="8"/>
+    </row>
+    <row r="163" spans="2:19">
       <c r="B163" s="1">
         <v>159</v>
       </c>
+      <c r="D163" s="8"/>
       <c r="E163" s="3"/>
-    </row>
-    <row r="164" spans="2:5">
+      <c r="P163" s="8"/>
+      <c r="S163" s="8"/>
+    </row>
+    <row r="164" spans="2:19">
       <c r="B164" s="1">
         <v>160</v>
       </c>
+      <c r="D164" s="8"/>
       <c r="E164" s="3"/>
-    </row>
-    <row r="165" spans="2:5">
+      <c r="P164" s="8"/>
+      <c r="S164" s="8"/>
+    </row>
+    <row r="165" spans="2:19">
       <c r="B165" s="1">
         <v>161</v>
       </c>
+      <c r="D165" s="8"/>
       <c r="E165" s="3"/>
-    </row>
-    <row r="166" spans="2:5">
+      <c r="P165" s="8"/>
+      <c r="S165" s="8"/>
+    </row>
+    <row r="166" spans="2:19">
       <c r="B166" s="1">
         <v>162</v>
       </c>
+      <c r="D166" s="8"/>
       <c r="E166" s="3"/>
-    </row>
-    <row r="167" spans="2:5">
+      <c r="P166" s="8"/>
+      <c r="S166" s="8"/>
+    </row>
+    <row r="167" spans="2:19">
       <c r="B167" s="1">
         <v>163</v>
       </c>
+      <c r="D167" s="8"/>
       <c r="E167" s="3"/>
-    </row>
-    <row r="168" spans="2:5">
+      <c r="P167" s="8"/>
+      <c r="S167" s="8"/>
+    </row>
+    <row r="168" spans="2:19">
       <c r="B168" s="1">
         <v>164</v>
       </c>
+      <c r="D168" s="8"/>
       <c r="E168" s="3"/>
-    </row>
-    <row r="169" spans="2:5">
+      <c r="P168" s="8"/>
+      <c r="S168" s="8"/>
+    </row>
+    <row r="169" spans="2:19">
       <c r="B169" s="1">
         <v>165</v>
       </c>
+      <c r="D169" s="8"/>
       <c r="E169" s="3"/>
-    </row>
-    <row r="170" spans="2:5">
+      <c r="P169" s="8"/>
+      <c r="S169" s="8"/>
+    </row>
+    <row r="170" spans="2:19">
       <c r="B170" s="1">
         <v>166</v>
       </c>
+      <c r="D170" s="8"/>
       <c r="E170" s="3"/>
-    </row>
-    <row r="171" spans="2:5">
+      <c r="P170" s="8"/>
+      <c r="S170" s="8"/>
+    </row>
+    <row r="171" spans="2:19">
       <c r="B171" s="1">
         <v>167</v>
       </c>
+      <c r="D171" s="8"/>
       <c r="E171" s="3"/>
-    </row>
-    <row r="172" spans="2:5">
+      <c r="P171" s="8"/>
+      <c r="S171" s="8"/>
+    </row>
+    <row r="172" spans="2:19">
       <c r="B172" s="1">
         <v>168</v>
       </c>
+      <c r="D172" s="8"/>
       <c r="E172" s="3"/>
-    </row>
-    <row r="173" spans="2:5">
+      <c r="P172" s="8"/>
+      <c r="S172" s="8"/>
+    </row>
+    <row r="173" spans="2:19">
       <c r="B173" s="1">
         <v>169</v>
       </c>
+      <c r="D173" s="8"/>
       <c r="E173" s="3"/>
-    </row>
-    <row r="174" spans="2:5">
+      <c r="P173" s="8"/>
+      <c r="S173" s="8"/>
+    </row>
+    <row r="174" spans="2:19">
       <c r="B174" s="1">
         <v>170</v>
       </c>
+      <c r="D174" s="8"/>
       <c r="E174" s="3"/>
-    </row>
-    <row r="175" spans="2:5">
+      <c r="P174" s="8"/>
+      <c r="S174" s="8"/>
+    </row>
+    <row r="175" spans="2:19">
       <c r="B175" s="1">
         <v>171</v>
       </c>
+      <c r="D175" s="8"/>
       <c r="E175" s="3"/>
-    </row>
-    <row r="176" spans="2:5">
+      <c r="P175" s="8"/>
+      <c r="S175" s="8"/>
+    </row>
+    <row r="176" spans="2:19">
       <c r="B176" s="1">
         <v>172</v>
       </c>
+      <c r="D176" s="8"/>
       <c r="E176" s="3"/>
-    </row>
-    <row r="177" spans="2:5">
+      <c r="P176" s="8"/>
+      <c r="S176" s="8"/>
+    </row>
+    <row r="177" spans="2:19">
       <c r="B177" s="1">
         <v>173</v>
       </c>
+      <c r="D177" s="8"/>
       <c r="E177" s="3"/>
-    </row>
-    <row r="178" spans="2:5">
+      <c r="P177" s="8"/>
+      <c r="S177" s="8"/>
+    </row>
+    <row r="178" spans="2:19">
       <c r="B178" s="1">
         <v>174</v>
       </c>
+      <c r="D178" s="8"/>
       <c r="E178" s="3"/>
-    </row>
-    <row r="179" spans="2:5">
+      <c r="P178" s="8"/>
+      <c r="S178" s="8"/>
+    </row>
+    <row r="179" spans="2:19">
       <c r="B179" s="1">
         <v>175</v>
       </c>
+      <c r="D179" s="8"/>
       <c r="E179" s="3"/>
-    </row>
-    <row r="180" spans="2:5">
+      <c r="P179" s="8"/>
+      <c r="S179" s="8"/>
+    </row>
+    <row r="180" spans="2:19">
       <c r="B180" s="1">
         <v>176</v>
       </c>
+      <c r="D180" s="8"/>
       <c r="E180" s="3"/>
-    </row>
-    <row r="181" spans="2:5">
+      <c r="P180" s="8"/>
+      <c r="S180" s="8"/>
+    </row>
+    <row r="181" spans="2:19">
       <c r="B181" s="1">
         <v>177</v>
       </c>
+      <c r="D181" s="8"/>
       <c r="E181" s="3"/>
-    </row>
-    <row r="182" spans="2:5">
+      <c r="P181" s="8"/>
+      <c r="S181" s="8"/>
+    </row>
+    <row r="182" spans="2:19">
       <c r="B182" s="1">
         <v>178</v>
       </c>
+      <c r="D182" s="8"/>
       <c r="E182" s="3"/>
-    </row>
-    <row r="183" spans="2:5">
+      <c r="P182" s="8"/>
+      <c r="S182" s="8"/>
+    </row>
+    <row r="183" spans="2:19">
       <c r="B183" s="1">
         <v>179</v>
       </c>
+      <c r="D183" s="8"/>
       <c r="E183" s="3"/>
-    </row>
-    <row r="184" spans="2:5">
+      <c r="P183" s="8"/>
+      <c r="S183" s="8"/>
+    </row>
+    <row r="184" spans="2:19">
       <c r="B184" s="1">
         <v>180</v>
       </c>
+      <c r="D184" s="8"/>
       <c r="E184" s="3"/>
-    </row>
-    <row r="185" spans="2:5">
+      <c r="P184" s="8"/>
+      <c r="S184" s="8"/>
+    </row>
+    <row r="185" spans="2:19">
       <c r="B185" s="1">
         <v>181</v>
       </c>
+      <c r="D185" s="8"/>
       <c r="E185" s="3"/>
-    </row>
-    <row r="186" spans="2:5">
+      <c r="P185" s="8"/>
+      <c r="S185" s="8"/>
+    </row>
+    <row r="186" spans="2:19">
       <c r="B186" s="1">
         <v>182</v>
       </c>
+      <c r="D186" s="8"/>
       <c r="E186" s="3"/>
-    </row>
-    <row r="187" spans="2:5">
+      <c r="P186" s="8"/>
+      <c r="S186" s="8"/>
+    </row>
+    <row r="187" spans="2:19">
       <c r="B187" s="1">
         <v>183</v>
       </c>
+      <c r="D187" s="8"/>
       <c r="E187" s="3"/>
-    </row>
-    <row r="188" spans="2:5">
+      <c r="P187" s="8"/>
+      <c r="S187" s="8"/>
+    </row>
+    <row r="188" spans="2:19">
       <c r="B188" s="1">
         <v>184</v>
       </c>
+      <c r="D188" s="8"/>
       <c r="E188" s="3"/>
-    </row>
-    <row r="189" spans="2:5">
+      <c r="P188" s="8"/>
+      <c r="S188" s="8"/>
+    </row>
+    <row r="189" spans="2:19">
       <c r="B189" s="1">
         <v>185</v>
       </c>
+      <c r="D189" s="8"/>
       <c r="E189" s="3"/>
-    </row>
-    <row r="190" spans="2:5">
+      <c r="P189" s="8"/>
+      <c r="S189" s="8"/>
+    </row>
+    <row r="190" spans="2:19">
       <c r="B190" s="1">
         <v>186</v>
       </c>
+      <c r="D190" s="8"/>
       <c r="E190" s="3"/>
-    </row>
-    <row r="191" spans="2:5">
+      <c r="P190" s="8"/>
+      <c r="S190" s="8"/>
+    </row>
+    <row r="191" spans="2:19">
       <c r="B191" s="1">
         <v>187</v>
       </c>
+      <c r="D191" s="8"/>
       <c r="E191" s="3"/>
-    </row>
-    <row r="192" spans="2:5">
+      <c r="P191" s="8"/>
+      <c r="S191" s="8"/>
+    </row>
+    <row r="192" spans="2:19">
       <c r="B192" s="1">
         <v>188</v>
       </c>
+      <c r="D192" s="8"/>
       <c r="E192" s="3"/>
-    </row>
-    <row r="193" spans="2:5">
+      <c r="P192" s="8"/>
+      <c r="S192" s="8"/>
+    </row>
+    <row r="193" spans="2:19">
       <c r="B193" s="1">
         <v>189</v>
       </c>
+      <c r="D193" s="8"/>
       <c r="E193" s="3"/>
-    </row>
-    <row r="194" spans="2:5">
+      <c r="P193" s="8"/>
+      <c r="S193" s="8"/>
+    </row>
+    <row r="194" spans="2:19">
       <c r="B194" s="1">
         <v>190</v>
       </c>
+      <c r="D194" s="8"/>
       <c r="E194" s="3"/>
-    </row>
-    <row r="195" spans="2:5">
+      <c r="P194" s="8"/>
+      <c r="S194" s="8"/>
+    </row>
+    <row r="195" spans="2:19">
       <c r="B195" s="1">
         <v>191</v>
       </c>
+      <c r="D195" s="8"/>
       <c r="E195" s="3"/>
-    </row>
-    <row r="196" spans="2:5">
+      <c r="P195" s="8"/>
+      <c r="S195" s="8"/>
+    </row>
+    <row r="196" spans="2:19">
       <c r="B196" s="1">
         <v>192</v>
       </c>
+      <c r="D196" s="8"/>
       <c r="E196" s="3"/>
-    </row>
-    <row r="197" spans="2:5">
+      <c r="P196" s="8"/>
+      <c r="S196" s="8"/>
+    </row>
+    <row r="197" spans="2:19">
       <c r="B197" s="1">
         <v>193</v>
       </c>
+      <c r="D197" s="8"/>
       <c r="E197" s="3"/>
-    </row>
-    <row r="198" spans="2:5">
+      <c r="P197" s="8"/>
+      <c r="S197" s="8"/>
+    </row>
+    <row r="198" spans="2:19">
       <c r="B198" s="1">
         <v>194</v>
       </c>
+      <c r="D198" s="8"/>
       <c r="E198" s="3"/>
-    </row>
-    <row r="199" spans="2:5">
+      <c r="P198" s="8"/>
+      <c r="S198" s="8"/>
+    </row>
+    <row r="199" spans="2:19">
       <c r="B199" s="1">
         <v>195</v>
       </c>
+      <c r="D199" s="8"/>
       <c r="E199" s="3"/>
-    </row>
-    <row r="200" spans="2:5">
+      <c r="P199" s="8"/>
+      <c r="S199" s="8"/>
+    </row>
+    <row r="200" spans="2:19">
       <c r="B200" s="1">
         <v>196</v>
       </c>
+      <c r="D200" s="8"/>
       <c r="E200" s="3"/>
-    </row>
-    <row r="201" spans="2:5">
+      <c r="P200" s="8"/>
+      <c r="S200" s="8"/>
+    </row>
+    <row r="201" spans="2:19">
       <c r="B201" s="1">
         <v>197</v>
       </c>
+      <c r="D201" s="8"/>
       <c r="E201" s="3"/>
-    </row>
-    <row r="202" spans="2:5">
+      <c r="P201" s="8"/>
+      <c r="S201" s="8"/>
+    </row>
+    <row r="202" spans="2:19">
       <c r="B202" s="1">
         <v>198</v>
       </c>
+      <c r="D202" s="8"/>
       <c r="E202" s="3"/>
-    </row>
-    <row r="203" spans="2:5">
+      <c r="P202" s="8"/>
+      <c r="S202" s="8"/>
+    </row>
+    <row r="203" spans="2:19">
       <c r="B203" s="1">
         <v>199</v>
       </c>
+      <c r="D203" s="8"/>
       <c r="E203" s="3"/>
-    </row>
-    <row r="204" spans="2:5">
+      <c r="P203" s="8"/>
+      <c r="S203" s="8"/>
+    </row>
+    <row r="204" spans="2:19">
       <c r="B204" s="1">
         <v>200</v>
       </c>
+      <c r="D204" s="8"/>
       <c r="E204" s="3"/>
-    </row>
-    <row r="205" spans="2:5">
+      <c r="P204" s="8"/>
+      <c r="S204" s="8"/>
+    </row>
+    <row r="205" spans="2:19">
       <c r="B205" s="1">
         <v>201</v>
       </c>
+      <c r="D205" s="8"/>
       <c r="E205" s="3"/>
-    </row>
-    <row r="206" spans="2:5">
+      <c r="P205" s="8"/>
+      <c r="S205" s="8"/>
+    </row>
+    <row r="206" spans="2:19">
       <c r="B206" s="1">
         <v>202</v>
       </c>
+      <c r="D206" s="8"/>
       <c r="E206" s="3"/>
-    </row>
-    <row r="207" spans="2:5">
+      <c r="P206" s="8"/>
+      <c r="S206" s="8"/>
+    </row>
+    <row r="207" spans="2:19">
       <c r="B207" s="1">
         <v>203</v>
       </c>
+      <c r="D207" s="8"/>
       <c r="E207" s="3"/>
-    </row>
-    <row r="208" spans="2:5">
+      <c r="P207" s="8"/>
+      <c r="S207" s="8"/>
+    </row>
+    <row r="208" spans="2:19">
       <c r="B208" s="1">
         <v>204</v>
       </c>
+      <c r="D208" s="8"/>
       <c r="E208" s="3"/>
-    </row>
-    <row r="209" spans="2:5">
+      <c r="P208" s="8"/>
+      <c r="S208" s="8"/>
+    </row>
+    <row r="209" spans="2:19">
       <c r="B209" s="1">
         <v>205</v>
       </c>
+      <c r="D209" s="8"/>
       <c r="E209" s="3"/>
-    </row>
-    <row r="210" spans="2:5">
+      <c r="P209" s="8"/>
+      <c r="S209" s="8"/>
+    </row>
+    <row r="210" spans="2:19">
       <c r="B210" s="1">
         <v>206</v>
       </c>
+      <c r="D210" s="8"/>
       <c r="E210" s="3"/>
-    </row>
-    <row r="211" spans="2:5">
+      <c r="P210" s="8"/>
+      <c r="S210" s="8"/>
+    </row>
+    <row r="211" spans="2:19">
       <c r="B211" s="1">
         <v>207</v>
       </c>
+      <c r="D211" s="8"/>
       <c r="E211" s="3"/>
-    </row>
-    <row r="212" spans="2:5">
+      <c r="P211" s="8"/>
+      <c r="S211" s="8"/>
+    </row>
+    <row r="212" spans="2:19">
       <c r="B212" s="1">
         <v>208</v>
       </c>
+      <c r="D212" s="8"/>
       <c r="E212" s="3"/>
-    </row>
-    <row r="213" spans="2:5">
+      <c r="P212" s="8"/>
+      <c r="S212" s="8"/>
+    </row>
+    <row r="213" spans="2:19">
       <c r="B213" s="1">
         <v>209</v>
       </c>
+      <c r="D213" s="8"/>
       <c r="E213" s="3"/>
-    </row>
-    <row r="214" spans="2:5">
+      <c r="P213" s="8"/>
+      <c r="S213" s="8"/>
+    </row>
+    <row r="214" spans="2:19">
       <c r="B214" s="1">
         <v>210</v>
       </c>
+      <c r="D214" s="8"/>
       <c r="E214" s="3"/>
-    </row>
-    <row r="215" spans="2:5">
+      <c r="P214" s="8"/>
+      <c r="S214" s="8"/>
+    </row>
+    <row r="215" spans="2:19">
       <c r="B215" s="1">
         <v>211</v>
       </c>
+      <c r="D215" s="8"/>
       <c r="E215" s="3"/>
-    </row>
-    <row r="216" spans="2:5">
+      <c r="P215" s="8"/>
+      <c r="S215" s="8"/>
+    </row>
+    <row r="216" spans="2:19">
       <c r="B216" s="1">
         <v>212</v>
       </c>
+      <c r="D216" s="8"/>
       <c r="E216" s="3"/>
-    </row>
-    <row r="217" spans="2:5">
+      <c r="P216" s="8"/>
+      <c r="S216" s="8"/>
+    </row>
+    <row r="217" spans="2:19">
       <c r="B217" s="1">
         <v>213</v>
       </c>
+      <c r="D217" s="8"/>
       <c r="E217" s="3"/>
-    </row>
-    <row r="218" spans="2:5">
+      <c r="P217" s="8"/>
+      <c r="S217" s="8"/>
+    </row>
+    <row r="218" spans="2:19">
       <c r="B218" s="1">
         <v>214</v>
       </c>
+      <c r="D218" s="8"/>
       <c r="E218" s="3"/>
-    </row>
-    <row r="219" spans="2:5">
+      <c r="P218" s="8"/>
+      <c r="S218" s="8"/>
+    </row>
+    <row r="219" spans="2:19">
       <c r="B219" s="1">
         <v>215</v>
       </c>
+      <c r="D219" s="8"/>
       <c r="E219" s="3"/>
-    </row>
-    <row r="220" spans="2:5">
+      <c r="P219" s="8"/>
+      <c r="S219" s="8"/>
+    </row>
+    <row r="220" spans="2:19">
       <c r="B220" s="1">
         <v>216</v>
       </c>
+      <c r="D220" s="8"/>
       <c r="E220" s="3"/>
-    </row>
-    <row r="221" spans="2:5">
+      <c r="P220" s="8"/>
+      <c r="S220" s="8"/>
+    </row>
+    <row r="221" spans="2:19">
       <c r="B221" s="1">
         <v>217</v>
       </c>
+      <c r="D221" s="8"/>
       <c r="E221" s="3"/>
-    </row>
-    <row r="222" spans="2:5">
+      <c r="P221" s="8"/>
+      <c r="S221" s="8"/>
+    </row>
+    <row r="222" spans="2:19">
       <c r="B222" s="1">
         <v>218</v>
       </c>
+      <c r="D222" s="8"/>
       <c r="E222" s="3"/>
-    </row>
-    <row r="223" spans="2:5">
+      <c r="P222" s="8"/>
+      <c r="S222" s="8"/>
+    </row>
+    <row r="223" spans="2:19">
       <c r="B223" s="1">
         <v>219</v>
       </c>
+      <c r="D223" s="8"/>
       <c r="E223" s="3"/>
-    </row>
-    <row r="224" spans="2:5">
+      <c r="P223" s="8"/>
+      <c r="S223" s="8"/>
+    </row>
+    <row r="224" spans="2:19">
       <c r="B224" s="1">
         <v>220</v>
       </c>
+      <c r="D224" s="8"/>
       <c r="E224" s="3"/>
-    </row>
-    <row r="225" spans="2:5">
+      <c r="P224" s="8"/>
+      <c r="S224" s="8"/>
+    </row>
+    <row r="225" spans="2:19">
       <c r="B225" s="1">
         <v>221</v>
       </c>
+      <c r="D225" s="8"/>
       <c r="E225" s="3"/>
-    </row>
-    <row r="226" spans="2:5">
+      <c r="P225" s="8"/>
+      <c r="S225" s="8"/>
+    </row>
+    <row r="226" spans="2:19">
       <c r="B226" s="1">
         <v>222</v>
       </c>
+      <c r="D226" s="8"/>
       <c r="E226" s="3"/>
-    </row>
-    <row r="227" spans="2:5">
+      <c r="P226" s="8"/>
+      <c r="S226" s="8"/>
+    </row>
+    <row r="227" spans="2:19">
       <c r="B227" s="1">
         <v>223</v>
       </c>
+      <c r="D227" s="8"/>
       <c r="E227" s="3"/>
-    </row>
-    <row r="228" spans="2:5">
+      <c r="P227" s="8"/>
+      <c r="S227" s="8"/>
+    </row>
+    <row r="228" spans="2:19">
       <c r="B228" s="1">
         <v>224</v>
       </c>
+      <c r="D228" s="8"/>
       <c r="E228" s="3"/>
-    </row>
-    <row r="229" spans="2:5">
+      <c r="P228" s="8"/>
+      <c r="S228" s="8"/>
+    </row>
+    <row r="229" spans="2:19">
       <c r="B229" s="1">
         <v>225</v>
       </c>
+      <c r="D229" s="8"/>
       <c r="E229" s="3"/>
-    </row>
-    <row r="230" spans="2:5">
+      <c r="P229" s="8"/>
+      <c r="S229" s="8"/>
+    </row>
+    <row r="230" spans="2:19">
       <c r="B230" s="1">
         <v>226</v>
       </c>
+      <c r="D230" s="8"/>
       <c r="E230" s="3"/>
-    </row>
-    <row r="231" spans="2:5">
+      <c r="P230" s="8"/>
+      <c r="S230" s="8"/>
+    </row>
+    <row r="231" spans="2:19">
       <c r="B231" s="1">
         <v>227</v>
       </c>
+      <c r="D231" s="8"/>
       <c r="E231" s="3"/>
-    </row>
-    <row r="232" spans="2:5">
+      <c r="P231" s="8"/>
+      <c r="S231" s="8"/>
+    </row>
+    <row r="232" spans="2:19">
       <c r="B232" s="1">
         <v>228</v>
       </c>
+      <c r="D232" s="8"/>
       <c r="E232" s="3"/>
-    </row>
-    <row r="233" spans="2:5">
+      <c r="P232" s="8"/>
+      <c r="S232" s="8"/>
+    </row>
+    <row r="233" spans="2:19">
       <c r="B233" s="1">
         <v>229</v>
       </c>
+      <c r="D233" s="8"/>
       <c r="E233" s="3"/>
-    </row>
-    <row r="234" spans="2:5">
+      <c r="P233" s="8"/>
+      <c r="S233" s="8"/>
+    </row>
+    <row r="234" spans="2:19">
       <c r="B234" s="1">
         <v>230</v>
       </c>
+      <c r="D234" s="8"/>
       <c r="E234" s="3"/>
-    </row>
-    <row r="235" spans="2:5">
+      <c r="P234" s="8"/>
+      <c r="S234" s="8"/>
+    </row>
+    <row r="235" spans="2:19">
       <c r="B235" s="1">
         <v>231</v>
       </c>
+      <c r="D235" s="8"/>
       <c r="E235" s="3"/>
-    </row>
-    <row r="236" spans="2:5">
+      <c r="P235" s="8"/>
+      <c r="S235" s="8"/>
+    </row>
+    <row r="236" spans="2:19">
       <c r="B236" s="1">
         <v>232</v>
       </c>
+      <c r="D236" s="8"/>
       <c r="E236" s="3"/>
-    </row>
-    <row r="237" spans="2:5">
+      <c r="P236" s="8"/>
+      <c r="S236" s="8"/>
+    </row>
+    <row r="237" spans="2:19">
       <c r="B237" s="1">
         <v>233</v>
       </c>
+      <c r="D237" s="8"/>
       <c r="E237" s="3"/>
-    </row>
-    <row r="238" spans="2:5">
+      <c r="P237" s="8"/>
+      <c r="S237" s="8"/>
+    </row>
+    <row r="238" spans="2:19">
       <c r="B238" s="1">
         <v>234</v>
       </c>
+      <c r="D238" s="8"/>
       <c r="E238" s="3"/>
-    </row>
-    <row r="239" spans="2:5">
+      <c r="P238" s="8"/>
+      <c r="S238" s="8"/>
+    </row>
+    <row r="239" spans="2:19">
       <c r="B239" s="1">
         <v>235</v>
       </c>
+      <c r="D239" s="8"/>
       <c r="E239" s="3"/>
-    </row>
-    <row r="240" spans="2:5">
+      <c r="P239" s="8"/>
+      <c r="S239" s="8"/>
+    </row>
+    <row r="240" spans="2:19">
       <c r="B240" s="1">
         <v>236</v>
       </c>
+      <c r="D240" s="8"/>
       <c r="E240" s="3"/>
-    </row>
-    <row r="241" spans="2:5">
+      <c r="P240" s="8"/>
+      <c r="S240" s="8"/>
+    </row>
+    <row r="241" spans="2:19">
       <c r="B241" s="1">
         <v>237</v>
       </c>
+      <c r="D241" s="8"/>
       <c r="E241" s="3"/>
-    </row>
-    <row r="242" spans="2:5">
+      <c r="P241" s="8"/>
+      <c r="S241" s="8"/>
+    </row>
+    <row r="242" spans="2:19">
       <c r="B242" s="1">
         <v>238</v>
       </c>
+      <c r="D242" s="8"/>
       <c r="E242" s="3"/>
-    </row>
-    <row r="243" spans="2:5">
+      <c r="P242" s="8"/>
+      <c r="S242" s="8"/>
+    </row>
+    <row r="243" spans="2:19">
       <c r="B243" s="1">
         <v>239</v>
       </c>
+      <c r="D243" s="8"/>
       <c r="E243" s="3"/>
-    </row>
-    <row r="244" spans="2:5">
+      <c r="P243" s="8"/>
+      <c r="S243" s="8"/>
+    </row>
+    <row r="244" spans="2:19">
       <c r="B244" s="1">
         <v>240</v>
       </c>
+      <c r="D244" s="8"/>
       <c r="E244" s="3"/>
-    </row>
-    <row r="245" spans="2:5">
+      <c r="P244" s="8"/>
+      <c r="S244" s="8"/>
+    </row>
+    <row r="245" spans="2:19">
       <c r="B245" s="1">
         <v>241</v>
       </c>
+      <c r="D245" s="8"/>
       <c r="E245" s="3"/>
-    </row>
-    <row r="246" spans="2:5">
+      <c r="P245" s="8"/>
+      <c r="S245" s="8"/>
+    </row>
+    <row r="246" spans="2:19">
       <c r="B246" s="1">
         <v>242</v>
       </c>
+      <c r="D246" s="8"/>
       <c r="E246" s="3"/>
-    </row>
-    <row r="247" spans="2:5">
+      <c r="P246" s="8"/>
+      <c r="S246" s="8"/>
+    </row>
+    <row r="247" spans="2:19">
       <c r="B247" s="1">
         <v>243</v>
       </c>
+      <c r="D247" s="8"/>
       <c r="E247" s="3"/>
-    </row>
-    <row r="248" spans="2:5">
+      <c r="P247" s="8"/>
+      <c r="S247" s="8"/>
+    </row>
+    <row r="248" spans="2:19">
       <c r="B248" s="1">
         <v>244</v>
       </c>
+      <c r="D248" s="8"/>
       <c r="E248" s="3"/>
-    </row>
-    <row r="249" spans="2:5">
+      <c r="P248" s="8"/>
+      <c r="S248" s="8"/>
+    </row>
+    <row r="249" spans="2:19">
       <c r="B249" s="1">
         <v>245</v>
       </c>
+      <c r="D249" s="8"/>
       <c r="E249" s="3"/>
-    </row>
-    <row r="250" spans="2:5">
+      <c r="P249" s="8"/>
+      <c r="S249" s="8"/>
+    </row>
+    <row r="250" spans="2:19">
       <c r="B250" s="1">
         <v>246</v>
       </c>
+      <c r="D250" s="8"/>
       <c r="E250" s="3"/>
+      <c r="P250" s="8"/>
+      <c r="S250" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="B3:B4"/>
@@ -2490,8 +3297,12 @@
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:T250">
     <cfRule type="expression" priority="6" stopIfTrue="1">
@@ -2508,23 +3319,6 @@
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="10">
       <formula>AND($P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G43:H43">
-    <cfRule type="expression" priority="16">
-      <formula>$Q44=""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="17">
-      <formula>$Q44&lt;TODAY()</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18">
-      <formula>$Q44-TODAY()=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="19">
-      <formula>AND($Q44-TODAY()&gt;=0, $Q44-TODAY()&lt;=3)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="20">
-      <formula>AND($Q44-TODAY()&gt;=4, $Q44-TODAY()&lt;=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2546,51 +3340,51 @@
   <sheetData>
     <row r="3" spans="2:10" ht="15" customHeight="1"/>
     <row r="4" spans="2:10" ht="15" customHeight="1">
-      <c r="B4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="B4" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="D4" s="15" t="s">
         <v>39</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:10">
       <c r="B6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J6" t="s">
         <v>27</v>
@@ -2598,79 +3392,79 @@
     </row>
     <row r="7" spans="2:10">
       <c r="B7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="B8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="2:10">
       <c r="B9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="2:10">
       <c r="D10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="2:10">
       <c r="F11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="2:10">
       <c r="J12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="2:10">
       <c r="J13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD9F9D88-3BCD-4657-974B-93AD070076B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF529B44-9809-4F79-BD5D-85034AFF73E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requisições 2026" sheetId="1" r:id="rId1"/>
@@ -439,6 +439,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -451,41 +481,11 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -517,7 +517,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -525,34 +525,6 @@
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -906,40 +878,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="23"/>
-      <c r="K1" s="24" t="s">
+      <c r="J1" s="33"/>
+      <c r="K1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="24"/>
+      <c r="L1" s="34"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" customHeight="1">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
     </row>
     <row r="3" spans="1:20" ht="19.8" customHeight="1">
       <c r="B3" s="28" t="s">
@@ -948,10 +920,10 @@
       <c r="C3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="25"/>
+      <c r="E3" s="27"/>
       <c r="F3" s="28" t="s">
         <v>7</v>
       </c>
@@ -982,17 +954,17 @@
       <c r="O3" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="P3" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="27"/>
+      <c r="Q3" s="26"/>
       <c r="R3" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="S3" s="25" t="s">
+      <c r="S3" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="T3" s="25"/>
+      <c r="T3" s="27"/>
     </row>
     <row r="4" spans="1:20" ht="32.4" customHeight="1">
       <c r="B4" s="28"/>
@@ -3254,53 +3226,58 @@
       <c r="S248" s="12"/>
     </row>
     <row r="249" spans="2:20">
-      <c r="B249" s="31">
+      <c r="B249" s="21">
         <v>245</v>
       </c>
-      <c r="C249" s="31"/>
-      <c r="D249" s="32"/>
-      <c r="E249" s="33"/>
-      <c r="F249" s="31"/>
-      <c r="G249" s="31"/>
-      <c r="H249" s="31"/>
-      <c r="I249" s="31"/>
-      <c r="J249" s="31"/>
-      <c r="K249" s="31"/>
-      <c r="L249" s="31"/>
-      <c r="M249" s="31"/>
-      <c r="N249" s="31"/>
-      <c r="O249" s="31"/>
-      <c r="P249" s="32"/>
-      <c r="Q249" s="33"/>
-      <c r="R249" s="34"/>
-      <c r="S249" s="32"/>
-      <c r="T249" s="33"/>
+      <c r="C249" s="21"/>
+      <c r="D249" s="22"/>
+      <c r="E249" s="23"/>
+      <c r="F249" s="21"/>
+      <c r="G249" s="21"/>
+      <c r="H249" s="21"/>
+      <c r="I249" s="21"/>
+      <c r="J249" s="21"/>
+      <c r="K249" s="21"/>
+      <c r="L249" s="21"/>
+      <c r="M249" s="21"/>
+      <c r="N249" s="21"/>
+      <c r="O249" s="21"/>
+      <c r="P249" s="22"/>
+      <c r="Q249" s="23"/>
+      <c r="R249" s="24"/>
+      <c r="S249" s="22"/>
+      <c r="T249" s="23"/>
     </row>
     <row r="250" spans="2:20">
-      <c r="B250" s="31">
+      <c r="B250" s="21">
         <v>246</v>
       </c>
-      <c r="C250" s="31"/>
-      <c r="D250" s="32"/>
-      <c r="E250" s="33"/>
-      <c r="F250" s="31"/>
-      <c r="G250" s="31"/>
-      <c r="H250" s="31"/>
-      <c r="I250" s="31"/>
-      <c r="J250" s="31"/>
-      <c r="K250" s="31"/>
-      <c r="L250" s="31"/>
-      <c r="M250" s="31"/>
-      <c r="N250" s="31"/>
-      <c r="O250" s="31"/>
-      <c r="P250" s="32"/>
-      <c r="Q250" s="33"/>
-      <c r="R250" s="34"/>
-      <c r="S250" s="32"/>
-      <c r="T250" s="33"/>
+      <c r="C250" s="21"/>
+      <c r="D250" s="22"/>
+      <c r="E250" s="23"/>
+      <c r="F250" s="21"/>
+      <c r="G250" s="21"/>
+      <c r="H250" s="21"/>
+      <c r="I250" s="21"/>
+      <c r="J250" s="21"/>
+      <c r="K250" s="21"/>
+      <c r="L250" s="21"/>
+      <c r="M250" s="21"/>
+      <c r="N250" s="21"/>
+      <c r="O250" s="21"/>
+      <c r="P250" s="22"/>
+      <c r="Q250" s="23"/>
+      <c r="R250" s="24"/>
+      <c r="S250" s="22"/>
+      <c r="T250" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="D3:E3"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="B3:B4"/>
@@ -3316,21 +3293,16 @@
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="R3:R4"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
-    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:T250">
     <cfRule type="expression" dxfId="7" priority="7">
       <formula>AND($P5&lt;&gt;"", $P5&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>AND($P5&lt;&gt;"", $P5-TODAY()&gt;=0, $P5-TODAY()&lt;=2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9">
-      <formula>AND($P5&lt;&gt;"", $P5-TODAY()&gt;=1, $P5-TODAY()&lt;=3)</formula>
+    <cfRule type="expression" dxfId="4" priority="9">
+      <formula>AND($P5&lt;&gt;"", $P5-TODAY()&gt;=1, $P5-TODAY()&lt;=4)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="10">
       <formula>AND($P5&lt;&gt;"", $P5-TODAY()&gt;=4, $P5-TODAY()&lt;=7)</formula>
